--- a/public/01.계약서.xlsx
+++ b/public/01.계약서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eBroAgent\drive_mirror\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3523208-BF0C-4BB7-9BA9-D8E397EA85B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79AC892-0BB1-47C6-99EF-64B118ED7EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E72163E-9728-43C2-B59D-2067775552E8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9E72163E-9728-43C2-B59D-2067775552E8}"/>
   </bookViews>
   <sheets>
     <sheet name="계약서 " sheetId="13" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="368">
   <si>
     <t>계약일자</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -432,10 +432,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>{옵션}</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>{소계}</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -2691,10 +2687,6 @@
   </si>
   <si>
     <t>차량번호</t>
-  </si>
-  <si>
-    <t>{차량번호}</t>
-    <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
     <t>제조년도</t>
@@ -2976,11 +2968,30 @@
   </si>
   <si>
     <t>{관리번호}</t>
+    <phoneticPr fontId="50" type="noConversion"/>
+  </si>
+  <si>
+    <t>{관리번호}
+{제조번호}</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>장비 번호</t>
+    <t xml:space="preserve">관리번호
+(S/N)
+</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(유상옵션)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>(수량) / {단위}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{단가}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5414,7 +5425,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="287">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5545,6 +5556,78 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="95" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="99" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="100" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="101" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="102" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="103" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="104" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="93" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="26" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="53" fillId="0" borderId="93" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="53" fillId="0" borderId="94" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="53" fillId="0" borderId="26" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6123,75 +6206,6 @@
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="50" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="99" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="100" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="101" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="102" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="103" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="104" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="47" borderId="93" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="47" borderId="26" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="53" fillId="0" borderId="93" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="53" fillId="0" borderId="94" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="53" fillId="0" borderId="26" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -7245,231 +7259,231 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
       <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="77"/>
       <c r="P2" s="2"/>
     </row>
     <row r="3" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="83"/>
       <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="83"/>
       <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="65"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="86"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="89"/>
       <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="74"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="77"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="101"/>
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="78"/>
-      <c r="K7" s="78"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
       <c r="P7" s="2"/>
     </row>
     <row r="8" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="90" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="70"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="94"/>
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A9" s="79"/>
+      <c r="A9" s="103"/>
       <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="70"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="93"/>
+      <c r="K9" s="94"/>
       <c r="P9" s="2"/>
     </row>
     <row r="10" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A10" s="79"/>
+      <c r="A10" s="103"/>
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="80"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="82"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="106"/>
       <c r="P10" s="2"/>
     </row>
     <row r="11" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A11" s="67"/>
+      <c r="A11" s="91"/>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="83"/>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="85"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="109"/>
       <c r="P11" s="2"/>
     </row>
     <row r="12" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="90" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="70"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="94"/>
       <c r="P12" s="2"/>
     </row>
     <row r="13" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A13" s="67"/>
+      <c r="A13" s="91"/>
       <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="70"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="93"/>
+      <c r="K13" s="94"/>
       <c r="P13" s="2"/>
     </row>
     <row r="14" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
@@ -7479,19 +7493,19 @@
       <c r="R14" s="4"/>
     </row>
     <row r="15" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="96"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="96"/>
+      <c r="H15" s="96"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="96"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -7501,19 +7515,19 @@
       <c r="R15" s="4"/>
     </row>
     <row r="16" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="89"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="89"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="89"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="89"/>
-      <c r="J16" s="89"/>
-      <c r="K16" s="89"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="113"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="113"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -7523,123 +7537,123 @@
       <c r="R16" s="4"/>
     </row>
     <row r="17" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A17" s="73" t="s">
+      <c r="A17" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="74"/>
-      <c r="C17" s="89" t="s">
+      <c r="B17" s="98"/>
+      <c r="C17" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="89"/>
-      <c r="E17" s="89"/>
-      <c r="F17" s="89"/>
-      <c r="G17" s="89"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="89"/>
-      <c r="J17" s="89"/>
-      <c r="K17" s="89"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
     </row>
     <row r="18" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A18" s="73"/>
-      <c r="B18" s="74"/>
-      <c r="C18" s="95" t="s">
+      <c r="A18" s="97"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="96"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="97"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="121"/>
     </row>
     <row r="19" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A19" s="86" t="s">
+      <c r="A19" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="87"/>
-      <c r="C19" s="88" t="s">
+      <c r="B19" s="111"/>
+      <c r="C19" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
+      <c r="D19" s="112"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="112"/>
     </row>
     <row r="20" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A20" s="86" t="s">
+      <c r="A20" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="87"/>
-      <c r="C20" s="88" t="s">
+      <c r="B20" s="111"/>
+      <c r="C20" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="88"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="88"/>
-      <c r="I20" s="88"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
+      <c r="D20" s="112"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="112"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="112"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="112"/>
     </row>
     <row r="21" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A21" s="86" t="s">
+      <c r="A21" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="87"/>
-      <c r="C21" s="89"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="89"/>
-      <c r="K21" s="89"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="113"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="113"/>
     </row>
     <row r="22" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A22" s="73" t="s">
+      <c r="A22" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="74"/>
-      <c r="C22" s="90" t="s">
+      <c r="B22" s="98"/>
+      <c r="C22" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="91"/>
-      <c r="E22" s="92" t="s">
+      <c r="D22" s="115"/>
+      <c r="E22" s="116" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="93"/>
-      <c r="G22" s="93"/>
-      <c r="H22" s="93"/>
-      <c r="I22" s="93"/>
-      <c r="J22" s="93"/>
-      <c r="K22" s="94"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="118"/>
     </row>
     <row r="23" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="74"/>
-      <c r="C23" s="98" t="s">
+      <c r="B23" s="98"/>
+      <c r="C23" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="99"/>
-      <c r="E23" s="92" t="s">
+      <c r="D23" s="123"/>
+      <c r="E23" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="93"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="93"/>
-      <c r="I23" s="93"/>
-      <c r="J23" s="93"/>
-      <c r="K23" s="94"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="118"/>
     </row>
     <row r="24" spans="1:16" ht="12" customHeight="1">
       <c r="P24" s="5"/>
@@ -7648,32 +7662,32 @@
       <c r="P25" s="5"/>
     </row>
     <row r="26" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="100" t="s">
+      <c r="A26" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="100"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="100"/>
-      <c r="F26" s="100"/>
-      <c r="G26" s="100"/>
-      <c r="H26" s="100"/>
-      <c r="I26" s="100"/>
-      <c r="J26" s="100"/>
-      <c r="K26" s="100"/>
+      <c r="B26" s="124"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="124"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="124"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="124"/>
+      <c r="I26" s="124"/>
+      <c r="J26" s="124"/>
+      <c r="K26" s="124"/>
     </row>
     <row r="27" spans="1:16" s="6" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A27" s="100"/>
-      <c r="B27" s="100"/>
-      <c r="C27" s="100"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="100"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="100"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="100"/>
+      <c r="A27" s="124"/>
+      <c r="B27" s="124"/>
+      <c r="C27" s="124"/>
+      <c r="D27" s="124"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="124"/>
+      <c r="G27" s="124"/>
+      <c r="H27" s="124"/>
+      <c r="I27" s="124"/>
+      <c r="J27" s="124"/>
+      <c r="K27" s="124"/>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
@@ -7681,19 +7695,19 @@
       <c r="P27" s="7"/>
     </row>
     <row r="28" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A28" s="101" t="s">
+      <c r="A28" s="125" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="101"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="101"/>
-      <c r="H28" s="101"/>
-      <c r="I28" s="101"/>
-      <c r="J28" s="101"/>
-      <c r="K28" s="101"/>
+      <c r="B28" s="125"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
+      <c r="I28" s="125"/>
+      <c r="J28" s="125"/>
+      <c r="K28" s="125"/>
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
@@ -7719,29 +7733,29 @@
       <c r="P29" s="7"/>
     </row>
     <row r="30" spans="1:16" s="6" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A30" s="102" t="s">
+      <c r="A30" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="103"/>
+      <c r="B30" s="127"/>
       <c r="C30" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="108" t="s">
+      <c r="D30" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="109"/>
-      <c r="F30" s="110"/>
-      <c r="G30" s="111" t="s">
+      <c r="E30" s="133"/>
+      <c r="F30" s="134"/>
+      <c r="G30" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="H30" s="103"/>
+      <c r="H30" s="127"/>
       <c r="I30" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="J30" s="114" t="s">
+      <c r="J30" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K30" s="115"/>
+      <c r="K30" s="139"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
@@ -7749,93 +7763,93 @@
       <c r="P30" s="7"/>
     </row>
     <row r="31" spans="1:16" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A31" s="104"/>
-      <c r="B31" s="105"/>
+      <c r="A31" s="128"/>
+      <c r="B31" s="129"/>
       <c r="C31" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="D31" s="116" t="s">
+      <c r="D31" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="117"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="112"/>
-      <c r="H31" s="105"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="142"/>
+      <c r="G31" s="136"/>
+      <c r="H31" s="129"/>
       <c r="I31" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="J31" s="116" t="s">
+      <c r="J31" s="140" t="s">
         <v>80</v>
       </c>
-      <c r="K31" s="118"/>
+      <c r="K31" s="142"/>
       <c r="P31" s="8"/>
     </row>
     <row r="32" spans="1:16" s="6" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A32" s="106"/>
-      <c r="B32" s="107"/>
+      <c r="A32" s="130"/>
+      <c r="B32" s="131"/>
       <c r="C32" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="129" t="s">
+      <c r="D32" s="153" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="130"/>
-      <c r="F32" s="131"/>
-      <c r="G32" s="113"/>
-      <c r="H32" s="107"/>
+      <c r="E32" s="154"/>
+      <c r="F32" s="155"/>
+      <c r="G32" s="137"/>
+      <c r="H32" s="131"/>
       <c r="I32" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="J32" s="132" t="s">
+      <c r="J32" s="156" t="s">
         <v>81</v>
       </c>
-      <c r="K32" s="133"/>
+      <c r="K32" s="157"/>
       <c r="P32" s="8"/>
     </row>
     <row r="33" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A33" s="134" t="s">
+      <c r="A33" s="158" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="134"/>
-      <c r="C33" s="135"/>
-      <c r="D33" s="135"/>
-      <c r="E33" s="135"/>
-      <c r="F33" s="135"/>
-      <c r="G33" s="135"/>
-      <c r="H33" s="135"/>
-      <c r="I33" s="135"/>
-      <c r="J33" s="135"/>
-      <c r="K33" s="135"/>
+      <c r="B33" s="158"/>
+      <c r="C33" s="159"/>
+      <c r="D33" s="159"/>
+      <c r="E33" s="159"/>
+      <c r="F33" s="159"/>
+      <c r="G33" s="159"/>
+      <c r="H33" s="159"/>
+      <c r="I33" s="159"/>
+      <c r="J33" s="159"/>
+      <c r="K33" s="159"/>
       <c r="P33" s="8"/>
     </row>
     <row r="34" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1">
-      <c r="A34" s="136"/>
-      <c r="B34" s="136"/>
-      <c r="C34" s="136"/>
-      <c r="D34" s="136"/>
-      <c r="E34" s="136"/>
-      <c r="F34" s="136"/>
-      <c r="G34" s="136"/>
-      <c r="H34" s="136"/>
-      <c r="I34" s="136"/>
-      <c r="J34" s="136"/>
-      <c r="K34" s="136"/>
+      <c r="A34" s="160"/>
+      <c r="B34" s="160"/>
+      <c r="C34" s="160"/>
+      <c r="D34" s="160"/>
+      <c r="E34" s="160"/>
+      <c r="F34" s="160"/>
+      <c r="G34" s="160"/>
+      <c r="H34" s="160"/>
+      <c r="I34" s="160"/>
+      <c r="J34" s="160"/>
+      <c r="K34" s="160"/>
       <c r="P34" s="8"/>
     </row>
     <row r="35" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A35" s="137" t="s">
+      <c r="A35" s="161" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="137"/>
-      <c r="C35" s="137"/>
-      <c r="D35" s="137"/>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="137"/>
-      <c r="H35" s="137"/>
-      <c r="I35" s="137"/>
-      <c r="J35" s="137"/>
-      <c r="K35" s="137"/>
+      <c r="B35" s="161"/>
+      <c r="C35" s="161"/>
+      <c r="D35" s="161"/>
+      <c r="E35" s="161"/>
+      <c r="F35" s="161"/>
+      <c r="G35" s="161"/>
+      <c r="H35" s="161"/>
+      <c r="I35" s="161"/>
+      <c r="J35" s="161"/>
+      <c r="K35" s="161"/>
       <c r="P35" s="8"/>
     </row>
     <row r="36" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
@@ -7853,61 +7867,61 @@
       <c r="P36" s="8"/>
     </row>
     <row r="37" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A37" s="119" t="s">
+      <c r="A37" s="143" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="120"/>
-      <c r="C37" s="121" t="s">
+      <c r="B37" s="144"/>
+      <c r="C37" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="D37" s="122"/>
-      <c r="E37" s="122"/>
-      <c r="F37" s="122"/>
-      <c r="G37" s="121" t="s">
+      <c r="D37" s="146"/>
+      <c r="E37" s="146"/>
+      <c r="F37" s="146"/>
+      <c r="G37" s="145" t="s">
         <v>69</v>
       </c>
-      <c r="H37" s="123"/>
-      <c r="I37" s="124" t="s">
-        <v>93</v>
-      </c>
-      <c r="J37" s="125"/>
-      <c r="K37" s="126"/>
+      <c r="H37" s="147"/>
+      <c r="I37" s="148" t="s">
+        <v>92</v>
+      </c>
+      <c r="J37" s="149"/>
+      <c r="K37" s="150"/>
     </row>
     <row r="38" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A38" s="127" t="s">
+      <c r="A38" s="151" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="128"/>
-      <c r="C38" s="138" t="s">
+      <c r="B38" s="152"/>
+      <c r="C38" s="162" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="139"/>
-      <c r="E38" s="139"/>
-      <c r="F38" s="139"/>
-      <c r="G38" s="139"/>
-      <c r="H38" s="139"/>
-      <c r="I38" s="139"/>
-      <c r="J38" s="139"/>
-      <c r="K38" s="140"/>
+      <c r="D38" s="163"/>
+      <c r="E38" s="163"/>
+      <c r="F38" s="163"/>
+      <c r="G38" s="163"/>
+      <c r="H38" s="163"/>
+      <c r="I38" s="163"/>
+      <c r="J38" s="163"/>
+      <c r="K38" s="164"/>
       <c r="M38" s="12"/>
     </row>
     <row r="39" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A39" s="141" t="s">
+      <c r="A39" s="165" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="128"/>
+      <c r="B39" s="152"/>
       <c r="C39" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="144" t="s">
+      <c r="D39" s="168" t="s">
         <v>80</v>
       </c>
-      <c r="E39" s="144"/>
-      <c r="F39" s="144"/>
-      <c r="G39" s="144" t="s">
+      <c r="E39" s="168"/>
+      <c r="F39" s="168"/>
+      <c r="G39" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="H39" s="144"/>
+      <c r="H39" s="168"/>
       <c r="I39" s="25"/>
       <c r="J39" s="26" t="s">
         <v>32</v>
@@ -7917,75 +7931,75 @@
       <c r="N39" s="11"/>
     </row>
     <row r="40" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A40" s="127"/>
-      <c r="B40" s="128"/>
+      <c r="A40" s="151"/>
+      <c r="B40" s="152"/>
       <c r="C40" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D40" s="145"/>
-      <c r="E40" s="145"/>
-      <c r="F40" s="145"/>
-      <c r="G40" s="144" t="s">
+      <c r="D40" s="169"/>
+      <c r="E40" s="169"/>
+      <c r="F40" s="169"/>
+      <c r="G40" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="144"/>
-      <c r="I40" s="144"/>
-      <c r="J40" s="144"/>
-      <c r="K40" s="146"/>
+      <c r="H40" s="168"/>
+      <c r="I40" s="168"/>
+      <c r="J40" s="168"/>
+      <c r="K40" s="170"/>
     </row>
     <row r="41" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A41" s="142"/>
-      <c r="B41" s="143"/>
+      <c r="A41" s="166"/>
+      <c r="B41" s="167"/>
       <c r="C41" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="147" t="s">
+      <c r="D41" s="171" t="s">
         <v>85</v>
       </c>
-      <c r="E41" s="147"/>
-      <c r="F41" s="147"/>
-      <c r="G41" s="147" t="s">
+      <c r="E41" s="171"/>
+      <c r="F41" s="171"/>
+      <c r="G41" s="171" t="s">
         <v>9</v>
       </c>
-      <c r="H41" s="147"/>
-      <c r="I41" s="147" t="s">
+      <c r="H41" s="171"/>
+      <c r="I41" s="171" t="s">
         <v>86</v>
       </c>
-      <c r="J41" s="147"/>
-      <c r="K41" s="148"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="172"/>
     </row>
     <row r="42" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A42" s="155"/>
-      <c r="B42" s="155"/>
-      <c r="C42" s="155"/>
-      <c r="D42" s="155"/>
-      <c r="E42" s="155"/>
-      <c r="F42" s="155"/>
-      <c r="G42" s="155"/>
-      <c r="H42" s="155"/>
-      <c r="I42" s="155"/>
-      <c r="J42" s="155"/>
-      <c r="K42" s="155"/>
+      <c r="A42" s="179"/>
+      <c r="B42" s="179"/>
+      <c r="C42" s="179"/>
+      <c r="D42" s="179"/>
+      <c r="E42" s="179"/>
+      <c r="F42" s="179"/>
+      <c r="G42" s="179"/>
+      <c r="H42" s="179"/>
+      <c r="I42" s="179"/>
+      <c r="J42" s="179"/>
+      <c r="K42" s="179"/>
     </row>
     <row r="43" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A43" s="156" t="s">
+      <c r="A43" s="180" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="157"/>
+      <c r="B43" s="181"/>
       <c r="C43" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="E43" s="157" t="s">
+      <c r="D43" s="48" t="s">
+        <v>364</v>
+      </c>
+      <c r="E43" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="F43" s="120"/>
-      <c r="G43" s="120" t="s">
+      <c r="F43" s="144"/>
+      <c r="G43" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="H43" s="120"/>
+      <c r="H43" s="144"/>
       <c r="I43" s="30" t="s">
         <v>74</v>
       </c>
@@ -7998,485 +8012,487 @@
       <c r="P43" s="8"/>
     </row>
     <row r="44" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A44" s="153" t="s">
+      <c r="A44" s="177" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="154"/>
+      <c r="B44" s="178"/>
       <c r="C44" s="26" t="s">
         <v>88</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>364</v>
-      </c>
-      <c r="E44" s="149" t="s">
+        <v>363</v>
+      </c>
+      <c r="E44" s="173" t="s">
         <v>89</v>
       </c>
-      <c r="F44" s="150"/>
-      <c r="G44" s="151" t="s">
-        <v>92</v>
-      </c>
-      <c r="H44" s="152"/>
-      <c r="I44" s="164" t="s">
+      <c r="F44" s="174"/>
+      <c r="G44" s="175" t="s">
+        <v>91</v>
+      </c>
+      <c r="H44" s="176"/>
+      <c r="I44" s="188" t="s">
         <v>73</v>
       </c>
-      <c r="J44" s="158" t="s">
+      <c r="J44" s="182" t="s">
         <v>90</v>
       </c>
-      <c r="K44" s="161" t="s">
+      <c r="K44" s="185" t="s">
         <v>40</v>
       </c>
       <c r="P44" s="8"/>
     </row>
     <row r="45" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A45" s="153"/>
-      <c r="B45" s="154"/>
-      <c r="C45" s="26"/>
+      <c r="A45" s="177" t="s">
+        <v>365</v>
+      </c>
+      <c r="B45" s="178"/>
+      <c r="C45" s="26" t="s">
+        <v>366</v>
+      </c>
       <c r="D45" s="32"/>
-      <c r="E45" s="149"/>
-      <c r="F45" s="150"/>
-      <c r="G45" s="151"/>
-      <c r="H45" s="152"/>
-      <c r="I45" s="165"/>
-      <c r="J45" s="159"/>
-      <c r="K45" s="162"/>
+      <c r="E45" s="173" t="s">
+        <v>367</v>
+      </c>
+      <c r="F45" s="174"/>
+      <c r="G45" s="175" t="s">
+        <v>91</v>
+      </c>
+      <c r="H45" s="176"/>
+      <c r="I45" s="189"/>
+      <c r="J45" s="183"/>
+      <c r="K45" s="186"/>
       <c r="P45" s="8"/>
     </row>
     <row r="46" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A46" s="153"/>
-      <c r="B46" s="154"/>
+      <c r="A46" s="177"/>
+      <c r="B46" s="178"/>
       <c r="C46" s="26"/>
       <c r="D46" s="32"/>
-      <c r="E46" s="149"/>
-      <c r="F46" s="150"/>
-      <c r="G46" s="151"/>
-      <c r="H46" s="152"/>
-      <c r="I46" s="165"/>
-      <c r="J46" s="159"/>
-      <c r="K46" s="162"/>
+      <c r="E46" s="173"/>
+      <c r="F46" s="174"/>
+      <c r="G46" s="175"/>
+      <c r="H46" s="176"/>
+      <c r="I46" s="189"/>
+      <c r="J46" s="183"/>
+      <c r="K46" s="186"/>
       <c r="P46" s="8"/>
     </row>
     <row r="47" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A47" s="153"/>
-      <c r="B47" s="154"/>
+      <c r="A47" s="177"/>
+      <c r="B47" s="178"/>
       <c r="C47" s="26"/>
       <c r="D47" s="32"/>
-      <c r="E47" s="149"/>
-      <c r="F47" s="150"/>
-      <c r="G47" s="151"/>
-      <c r="H47" s="152"/>
-      <c r="I47" s="165"/>
-      <c r="J47" s="159"/>
-      <c r="K47" s="162"/>
+      <c r="E47" s="173"/>
+      <c r="F47" s="174"/>
+      <c r="G47" s="175"/>
+      <c r="H47" s="176"/>
+      <c r="I47" s="189"/>
+      <c r="J47" s="183"/>
+      <c r="K47" s="186"/>
       <c r="P47" s="8"/>
     </row>
     <row r="48" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A48" s="153"/>
-      <c r="B48" s="154"/>
+      <c r="A48" s="177"/>
+      <c r="B48" s="178"/>
       <c r="C48" s="26"/>
       <c r="D48" s="32"/>
-      <c r="E48" s="149"/>
-      <c r="F48" s="150"/>
-      <c r="G48" s="151"/>
-      <c r="H48" s="152"/>
-      <c r="I48" s="165"/>
-      <c r="J48" s="159"/>
-      <c r="K48" s="162"/>
+      <c r="E48" s="173"/>
+      <c r="F48" s="174"/>
+      <c r="G48" s="175"/>
+      <c r="H48" s="176"/>
+      <c r="I48" s="189"/>
+      <c r="J48" s="183"/>
+      <c r="K48" s="186"/>
       <c r="P48" s="8"/>
     </row>
     <row r="49" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A49" s="153"/>
-      <c r="B49" s="154"/>
+      <c r="A49" s="177"/>
+      <c r="B49" s="178"/>
       <c r="C49" s="26"/>
       <c r="D49" s="32"/>
-      <c r="E49" s="149"/>
-      <c r="F49" s="150"/>
-      <c r="G49" s="151"/>
-      <c r="H49" s="152"/>
-      <c r="I49" s="165"/>
-      <c r="J49" s="159"/>
-      <c r="K49" s="162"/>
+      <c r="E49" s="173"/>
+      <c r="F49" s="174"/>
+      <c r="G49" s="175"/>
+      <c r="H49" s="176"/>
+      <c r="I49" s="189"/>
+      <c r="J49" s="183"/>
+      <c r="K49" s="186"/>
       <c r="P49" s="8"/>
     </row>
     <row r="50" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A50" s="153"/>
-      <c r="B50" s="154"/>
+      <c r="A50" s="177"/>
+      <c r="B50" s="178"/>
       <c r="C50" s="26"/>
       <c r="D50" s="32"/>
-      <c r="E50" s="149"/>
-      <c r="F50" s="150"/>
-      <c r="G50" s="151"/>
-      <c r="H50" s="152"/>
-      <c r="I50" s="165"/>
-      <c r="J50" s="159"/>
-      <c r="K50" s="162"/>
+      <c r="E50" s="173"/>
+      <c r="F50" s="174"/>
+      <c r="G50" s="175"/>
+      <c r="H50" s="176"/>
+      <c r="I50" s="189"/>
+      <c r="J50" s="183"/>
+      <c r="K50" s="186"/>
       <c r="P50" s="8"/>
     </row>
     <row r="51" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A51" s="153"/>
-      <c r="B51" s="154"/>
+      <c r="A51" s="177"/>
+      <c r="B51" s="178"/>
       <c r="C51" s="26"/>
       <c r="D51" s="32"/>
-      <c r="E51" s="149"/>
-      <c r="F51" s="150"/>
-      <c r="G51" s="151"/>
-      <c r="H51" s="152"/>
-      <c r="I51" s="165"/>
-      <c r="J51" s="159"/>
-      <c r="K51" s="162"/>
+      <c r="E51" s="173"/>
+      <c r="F51" s="174"/>
+      <c r="G51" s="175"/>
+      <c r="H51" s="176"/>
+      <c r="I51" s="189"/>
+      <c r="J51" s="183"/>
+      <c r="K51" s="186"/>
       <c r="P51" s="8"/>
     </row>
     <row r="52" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A52" s="153"/>
-      <c r="B52" s="154"/>
+      <c r="A52" s="177"/>
+      <c r="B52" s="178"/>
       <c r="C52" s="26"/>
       <c r="D52" s="32"/>
-      <c r="E52" s="149"/>
-      <c r="F52" s="150"/>
-      <c r="G52" s="151"/>
-      <c r="H52" s="152"/>
-      <c r="I52" s="165"/>
-      <c r="J52" s="159"/>
-      <c r="K52" s="162"/>
+      <c r="E52" s="173"/>
+      <c r="F52" s="174"/>
+      <c r="G52" s="175"/>
+      <c r="H52" s="176"/>
+      <c r="I52" s="189"/>
+      <c r="J52" s="183"/>
+      <c r="K52" s="186"/>
       <c r="P52" s="8"/>
     </row>
     <row r="53" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A53" s="153"/>
-      <c r="B53" s="154"/>
+      <c r="A53" s="177"/>
+      <c r="B53" s="178"/>
       <c r="C53" s="26"/>
       <c r="D53" s="32"/>
-      <c r="E53" s="149"/>
-      <c r="F53" s="150"/>
-      <c r="G53" s="151"/>
-      <c r="H53" s="152"/>
-      <c r="I53" s="165"/>
-      <c r="J53" s="159"/>
-      <c r="K53" s="162"/>
+      <c r="E53" s="173"/>
+      <c r="F53" s="174"/>
+      <c r="G53" s="175"/>
+      <c r="H53" s="176"/>
+      <c r="I53" s="189"/>
+      <c r="J53" s="183"/>
+      <c r="K53" s="186"/>
       <c r="P53" s="8"/>
     </row>
     <row r="54" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A54" s="153"/>
-      <c r="B54" s="154"/>
-      <c r="C54" s="33">
-        <v>0</v>
-      </c>
+      <c r="A54" s="177"/>
+      <c r="B54" s="178"/>
+      <c r="C54" s="33"/>
       <c r="D54" s="32"/>
-      <c r="E54" s="149"/>
-      <c r="F54" s="150"/>
-      <c r="G54" s="151"/>
-      <c r="H54" s="152"/>
-      <c r="I54" s="165"/>
-      <c r="J54" s="159"/>
-      <c r="K54" s="162"/>
+      <c r="E54" s="173"/>
+      <c r="F54" s="174"/>
+      <c r="G54" s="175"/>
+      <c r="H54" s="176"/>
+      <c r="I54" s="189"/>
+      <c r="J54" s="183"/>
+      <c r="K54" s="186"/>
       <c r="P54" s="8"/>
     </row>
     <row r="55" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A55" s="153"/>
-      <c r="B55" s="154"/>
-      <c r="C55" s="24">
-        <v>0</v>
-      </c>
+      <c r="A55" s="177"/>
+      <c r="B55" s="178"/>
+      <c r="C55" s="24"/>
       <c r="D55" s="32"/>
-      <c r="E55" s="149"/>
-      <c r="F55" s="150"/>
-      <c r="G55" s="151"/>
-      <c r="H55" s="152"/>
-      <c r="I55" s="166"/>
-      <c r="J55" s="160"/>
-      <c r="K55" s="163"/>
-      <c r="N55" s="167"/>
-      <c r="O55" s="167"/>
-      <c r="P55" s="167"/>
-      <c r="Q55" s="167"/>
-      <c r="R55" s="167"/>
-      <c r="S55" s="167"/>
-      <c r="T55" s="167"/>
+      <c r="E55" s="173"/>
+      <c r="F55" s="174"/>
+      <c r="G55" s="175"/>
+      <c r="H55" s="176"/>
+      <c r="I55" s="190"/>
+      <c r="J55" s="184"/>
+      <c r="K55" s="187"/>
+      <c r="N55" s="191"/>
+      <c r="O55" s="191"/>
+      <c r="P55" s="191"/>
+      <c r="Q55" s="191"/>
+      <c r="R55" s="191"/>
+      <c r="S55" s="191"/>
+      <c r="T55" s="191"/>
     </row>
     <row r="56" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A56" s="168" t="s">
+      <c r="A56" s="192" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="169"/>
-      <c r="C56" s="170" t="s">
+      <c r="B56" s="193"/>
+      <c r="C56" s="194" t="s">
+        <v>357</v>
+      </c>
+      <c r="D56" s="195"/>
+      <c r="E56" s="195"/>
+      <c r="F56" s="195"/>
+      <c r="G56" s="195"/>
+      <c r="H56" s="195"/>
+      <c r="I56" s="195"/>
+      <c r="J56" s="195"/>
+      <c r="K56" s="196"/>
+      <c r="P56" s="8"/>
+    </row>
+    <row r="57" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
+      <c r="A57" s="216" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="217"/>
+      <c r="C57" s="194"/>
+      <c r="D57" s="195"/>
+      <c r="E57" s="195"/>
+      <c r="F57" s="195"/>
+      <c r="G57" s="195"/>
+      <c r="H57" s="195"/>
+      <c r="I57" s="195"/>
+      <c r="J57" s="195"/>
+      <c r="K57" s="196"/>
+      <c r="M57" s="9"/>
+    </row>
+    <row r="58" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
+      <c r="A58" s="216"/>
+      <c r="B58" s="217"/>
+      <c r="C58" s="194"/>
+      <c r="D58" s="195"/>
+      <c r="E58" s="195"/>
+      <c r="F58" s="195"/>
+      <c r="G58" s="195"/>
+      <c r="H58" s="195"/>
+      <c r="I58" s="195"/>
+      <c r="J58" s="195"/>
+      <c r="K58" s="196"/>
+    </row>
+    <row r="59" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
+      <c r="A59" s="218" t="s">
+        <v>71</v>
+      </c>
+      <c r="B59" s="219"/>
+      <c r="C59" s="220" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" s="221"/>
+      <c r="E59" s="221"/>
+      <c r="F59" s="221"/>
+      <c r="G59" s="221"/>
+      <c r="H59" s="221"/>
+      <c r="I59" s="221"/>
+      <c r="J59" s="221"/>
+      <c r="K59" s="222"/>
+    </row>
+    <row r="60" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
+      <c r="A60" s="223" t="s">
+        <v>21</v>
+      </c>
+      <c r="B60" s="224"/>
+      <c r="C60" s="220" t="s">
         <v>359</v>
       </c>
-      <c r="D56" s="171"/>
-      <c r="E56" s="171"/>
-      <c r="F56" s="171"/>
-      <c r="G56" s="171"/>
-      <c r="H56" s="171"/>
-      <c r="I56" s="171"/>
-      <c r="J56" s="171"/>
-      <c r="K56" s="172"/>
-      <c r="P56" s="8"/>
-    </row>
-    <row r="57" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A57" s="192" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="193"/>
-      <c r="C57" s="170" t="s">
-        <v>91</v>
-      </c>
-      <c r="D57" s="171"/>
-      <c r="E57" s="171"/>
-      <c r="F57" s="171"/>
-      <c r="G57" s="171"/>
-      <c r="H57" s="171"/>
-      <c r="I57" s="171"/>
-      <c r="J57" s="171"/>
-      <c r="K57" s="172"/>
-      <c r="M57" s="9"/>
-    </row>
-    <row r="58" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A58" s="192"/>
-      <c r="B58" s="193"/>
-      <c r="C58" s="170"/>
-      <c r="D58" s="171"/>
-      <c r="E58" s="171"/>
-      <c r="F58" s="171"/>
-      <c r="G58" s="171"/>
-      <c r="H58" s="171"/>
-      <c r="I58" s="171"/>
-      <c r="J58" s="171"/>
-      <c r="K58" s="172"/>
-    </row>
-    <row r="59" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A59" s="194" t="s">
-        <v>71</v>
-      </c>
-      <c r="B59" s="195"/>
-      <c r="C59" s="196" t="s">
-        <v>77</v>
-      </c>
-      <c r="D59" s="197"/>
-      <c r="E59" s="197"/>
-      <c r="F59" s="197"/>
-      <c r="G59" s="197"/>
-      <c r="H59" s="197"/>
-      <c r="I59" s="197"/>
-      <c r="J59" s="197"/>
-      <c r="K59" s="198"/>
-    </row>
-    <row r="60" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A60" s="199" t="s">
-        <v>21</v>
-      </c>
-      <c r="B60" s="200"/>
-      <c r="C60" s="196" t="s">
-        <v>361</v>
-      </c>
-      <c r="D60" s="197"/>
-      <c r="E60" s="197"/>
-      <c r="F60" s="197"/>
-      <c r="G60" s="197"/>
-      <c r="H60" s="197"/>
-      <c r="I60" s="197"/>
-      <c r="J60" s="197"/>
-      <c r="K60" s="198"/>
+      <c r="D60" s="221"/>
+      <c r="E60" s="221"/>
+      <c r="F60" s="221"/>
+      <c r="G60" s="221"/>
+      <c r="H60" s="221"/>
+      <c r="I60" s="221"/>
+      <c r="J60" s="221"/>
+      <c r="K60" s="222"/>
     </row>
     <row r="61" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A61" s="201"/>
-      <c r="B61" s="202"/>
-      <c r="C61" s="203"/>
-      <c r="D61" s="204"/>
-      <c r="E61" s="204"/>
-      <c r="F61" s="204"/>
-      <c r="G61" s="204"/>
-      <c r="H61" s="204"/>
-      <c r="I61" s="204"/>
-      <c r="J61" s="204"/>
-      <c r="K61" s="205"/>
+      <c r="A61" s="225"/>
+      <c r="B61" s="226"/>
+      <c r="C61" s="227"/>
+      <c r="D61" s="228"/>
+      <c r="E61" s="228"/>
+      <c r="F61" s="228"/>
+      <c r="G61" s="228"/>
+      <c r="H61" s="228"/>
+      <c r="I61" s="228"/>
+      <c r="J61" s="228"/>
+      <c r="K61" s="229"/>
     </row>
     <row r="62" spans="1:20" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A62" s="136"/>
-      <c r="B62" s="136"/>
-      <c r="C62" s="136"/>
-      <c r="D62" s="136"/>
-      <c r="E62" s="136"/>
-      <c r="F62" s="136"/>
-      <c r="G62" s="136"/>
-      <c r="H62" s="136"/>
-      <c r="I62" s="136"/>
-      <c r="J62" s="136"/>
-      <c r="K62" s="136"/>
+      <c r="A62" s="160"/>
+      <c r="B62" s="160"/>
+      <c r="C62" s="160"/>
+      <c r="D62" s="160"/>
+      <c r="E62" s="160"/>
+      <c r="F62" s="160"/>
+      <c r="G62" s="160"/>
+      <c r="H62" s="160"/>
+      <c r="I62" s="160"/>
+      <c r="J62" s="160"/>
+      <c r="K62" s="160"/>
       <c r="P62" s="8"/>
     </row>
     <row r="63" spans="1:20" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="173" t="s">
+      <c r="A63" s="197" t="s">
         <v>43</v>
       </c>
-      <c r="B63" s="174"/>
-      <c r="C63" s="181" t="s">
+      <c r="B63" s="198"/>
+      <c r="C63" s="205" t="s">
         <v>78</v>
       </c>
-      <c r="D63" s="182"/>
-      <c r="E63" s="182"/>
-      <c r="F63" s="182"/>
-      <c r="G63" s="182"/>
-      <c r="H63" s="182"/>
-      <c r="I63" s="182"/>
-      <c r="J63" s="182"/>
-      <c r="K63" s="183"/>
+      <c r="D63" s="206"/>
+      <c r="E63" s="206"/>
+      <c r="F63" s="206"/>
+      <c r="G63" s="206"/>
+      <c r="H63" s="206"/>
+      <c r="I63" s="206"/>
+      <c r="J63" s="206"/>
+      <c r="K63" s="207"/>
       <c r="P63" s="8"/>
     </row>
     <row r="64" spans="1:20" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="175"/>
-      <c r="B64" s="176"/>
-      <c r="C64" s="184" t="s">
+      <c r="A64" s="199"/>
+      <c r="B64" s="200"/>
+      <c r="C64" s="208" t="s">
         <v>44</v>
       </c>
-      <c r="D64" s="185"/>
-      <c r="E64" s="185"/>
-      <c r="F64" s="185"/>
-      <c r="G64" s="185"/>
-      <c r="H64" s="185"/>
-      <c r="I64" s="185"/>
-      <c r="J64" s="185"/>
-      <c r="K64" s="186"/>
+      <c r="D64" s="209"/>
+      <c r="E64" s="209"/>
+      <c r="F64" s="209"/>
+      <c r="G64" s="209"/>
+      <c r="H64" s="209"/>
+      <c r="I64" s="209"/>
+      <c r="J64" s="209"/>
+      <c r="K64" s="210"/>
       <c r="P64" s="8"/>
     </row>
     <row r="65" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="175"/>
-      <c r="B65" s="176"/>
-      <c r="C65" s="187" t="s">
+      <c r="A65" s="199"/>
+      <c r="B65" s="200"/>
+      <c r="C65" s="211" t="s">
         <v>45</v>
       </c>
-      <c r="D65" s="187"/>
-      <c r="E65" s="187"/>
-      <c r="F65" s="187"/>
-      <c r="G65" s="187"/>
-      <c r="H65" s="187"/>
-      <c r="I65" s="187"/>
-      <c r="J65" s="187"/>
-      <c r="K65" s="188"/>
+      <c r="D65" s="211"/>
+      <c r="E65" s="211"/>
+      <c r="F65" s="211"/>
+      <c r="G65" s="211"/>
+      <c r="H65" s="211"/>
+      <c r="I65" s="211"/>
+      <c r="J65" s="211"/>
+      <c r="K65" s="212"/>
       <c r="P65" s="8"/>
     </row>
     <row r="66" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="177"/>
-      <c r="B66" s="178"/>
-      <c r="C66" s="187" t="s">
+      <c r="A66" s="201"/>
+      <c r="B66" s="202"/>
+      <c r="C66" s="211" t="s">
         <v>46</v>
       </c>
-      <c r="D66" s="187"/>
-      <c r="E66" s="187"/>
-      <c r="F66" s="187"/>
-      <c r="G66" s="187"/>
-      <c r="H66" s="187"/>
-      <c r="I66" s="187"/>
-      <c r="J66" s="187"/>
-      <c r="K66" s="188"/>
+      <c r="D66" s="211"/>
+      <c r="E66" s="211"/>
+      <c r="F66" s="211"/>
+      <c r="G66" s="211"/>
+      <c r="H66" s="211"/>
+      <c r="I66" s="211"/>
+      <c r="J66" s="211"/>
+      <c r="K66" s="212"/>
       <c r="P66" s="8"/>
     </row>
     <row r="67" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A67" s="179"/>
-      <c r="B67" s="180"/>
-      <c r="C67" s="189" t="s">
+      <c r="A67" s="203"/>
+      <c r="B67" s="204"/>
+      <c r="C67" s="213" t="s">
         <v>47</v>
       </c>
-      <c r="D67" s="190"/>
-      <c r="E67" s="190"/>
-      <c r="F67" s="190"/>
-      <c r="G67" s="190"/>
-      <c r="H67" s="190"/>
-      <c r="I67" s="190"/>
-      <c r="J67" s="190"/>
-      <c r="K67" s="191"/>
+      <c r="D67" s="214"/>
+      <c r="E67" s="214"/>
+      <c r="F67" s="214"/>
+      <c r="G67" s="214"/>
+      <c r="H67" s="214"/>
+      <c r="I67" s="214"/>
+      <c r="J67" s="214"/>
+      <c r="K67" s="215"/>
       <c r="P67" s="8"/>
     </row>
     <row r="68" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A68" s="136"/>
-      <c r="B68" s="136"/>
-      <c r="C68" s="136"/>
-      <c r="D68" s="136"/>
-      <c r="E68" s="136"/>
-      <c r="F68" s="136"/>
-      <c r="G68" s="136"/>
-      <c r="H68" s="136"/>
-      <c r="I68" s="136"/>
-      <c r="J68" s="136"/>
-      <c r="K68" s="136"/>
+      <c r="A68" s="160"/>
+      <c r="B68" s="160"/>
+      <c r="C68" s="160"/>
+      <c r="D68" s="160"/>
+      <c r="E68" s="160"/>
+      <c r="F68" s="160"/>
+      <c r="G68" s="160"/>
+      <c r="H68" s="160"/>
+      <c r="I68" s="160"/>
+      <c r="J68" s="160"/>
+      <c r="K68" s="160"/>
     </row>
     <row r="69" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A69" s="224" t="s">
+      <c r="A69" s="248" t="s">
         <v>48</v>
       </c>
-      <c r="B69" s="225"/>
-      <c r="C69" s="226" t="s">
+      <c r="B69" s="249"/>
+      <c r="C69" s="250" t="s">
         <v>76</v>
       </c>
-      <c r="D69" s="226"/>
-      <c r="E69" s="226"/>
-      <c r="F69" s="226"/>
-      <c r="G69" s="226"/>
-      <c r="H69" s="226"/>
-      <c r="I69" s="226"/>
-      <c r="J69" s="226"/>
-      <c r="K69" s="227"/>
+      <c r="D69" s="250"/>
+      <c r="E69" s="250"/>
+      <c r="F69" s="250"/>
+      <c r="G69" s="250"/>
+      <c r="H69" s="250"/>
+      <c r="I69" s="250"/>
+      <c r="J69" s="250"/>
+      <c r="K69" s="251"/>
       <c r="P69" s="8"/>
     </row>
     <row r="70" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A70" s="136"/>
-      <c r="B70" s="136"/>
-      <c r="C70" s="136"/>
-      <c r="D70" s="136"/>
-      <c r="E70" s="136"/>
-      <c r="F70" s="136"/>
-      <c r="G70" s="136"/>
-      <c r="H70" s="136"/>
-      <c r="I70" s="136"/>
-      <c r="J70" s="136"/>
-      <c r="K70" s="136"/>
+      <c r="A70" s="160"/>
+      <c r="B70" s="160"/>
+      <c r="C70" s="160"/>
+      <c r="D70" s="160"/>
+      <c r="E70" s="160"/>
+      <c r="F70" s="160"/>
+      <c r="G70" s="160"/>
+      <c r="H70" s="160"/>
+      <c r="I70" s="160"/>
+      <c r="J70" s="160"/>
+      <c r="K70" s="160"/>
     </row>
     <row r="71" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="228" t="s">
+      <c r="A71" s="252" t="s">
         <v>49</v>
       </c>
-      <c r="B71" s="229"/>
-      <c r="C71" s="232" t="s">
+      <c r="B71" s="253"/>
+      <c r="C71" s="256" t="s">
         <v>50</v>
       </c>
-      <c r="D71" s="232"/>
-      <c r="E71" s="232"/>
-      <c r="F71" s="232"/>
-      <c r="G71" s="232"/>
-      <c r="H71" s="232"/>
-      <c r="I71" s="232"/>
-      <c r="J71" s="232"/>
-      <c r="K71" s="233"/>
+      <c r="D71" s="256"/>
+      <c r="E71" s="256"/>
+      <c r="F71" s="256"/>
+      <c r="G71" s="256"/>
+      <c r="H71" s="256"/>
+      <c r="I71" s="256"/>
+      <c r="J71" s="256"/>
+      <c r="K71" s="257"/>
     </row>
     <row r="72" spans="1:16" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A72" s="230"/>
-      <c r="B72" s="231"/>
-      <c r="C72" s="234" t="s">
+      <c r="A72" s="254"/>
+      <c r="B72" s="255"/>
+      <c r="C72" s="258" t="s">
         <v>51</v>
       </c>
-      <c r="D72" s="234"/>
-      <c r="E72" s="234"/>
-      <c r="F72" s="234"/>
-      <c r="G72" s="234"/>
-      <c r="H72" s="234"/>
-      <c r="I72" s="234"/>
-      <c r="J72" s="234"/>
-      <c r="K72" s="235"/>
+      <c r="D72" s="258"/>
+      <c r="E72" s="258"/>
+      <c r="F72" s="258"/>
+      <c r="G72" s="258"/>
+      <c r="H72" s="258"/>
+      <c r="I72" s="258"/>
+      <c r="J72" s="258"/>
+      <c r="K72" s="259"/>
     </row>
     <row r="73" spans="1:16" s="6" customFormat="1" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A73" s="201"/>
-      <c r="B73" s="202"/>
+      <c r="A73" s="225"/>
+      <c r="B73" s="226"/>
       <c r="C73" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D73" s="236" t="s">
+      <c r="D73" s="260" t="s">
         <v>53</v>
       </c>
-      <c r="E73" s="237"/>
-      <c r="F73" s="238"/>
-      <c r="G73" s="239" t="s">
+      <c r="E73" s="261"/>
+      <c r="F73" s="262"/>
+      <c r="G73" s="263" t="s">
         <v>9</v>
       </c>
-      <c r="H73" s="239"/>
-      <c r="I73" s="239"/>
-      <c r="J73" s="239"/>
-      <c r="K73" s="240"/>
+      <c r="H73" s="263"/>
+      <c r="I73" s="263"/>
+      <c r="J73" s="263"/>
+      <c r="K73" s="264"/>
     </row>
     <row r="74" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
       <c r="A74" s="35"/>
@@ -8492,53 +8508,53 @@
       <c r="K74" s="35"/>
     </row>
     <row r="75" spans="1:16" ht="25.15" customHeight="1">
-      <c r="A75" s="206" t="s">
-        <v>360</v>
-      </c>
-      <c r="B75" s="207"/>
-      <c r="C75" s="207"/>
-      <c r="D75" s="207"/>
-      <c r="E75" s="207"/>
-      <c r="F75" s="207"/>
-      <c r="G75" s="207"/>
-      <c r="H75" s="207"/>
-      <c r="I75" s="207"/>
-      <c r="J75" s="207"/>
-      <c r="K75" s="208"/>
+      <c r="A75" s="230" t="s">
+        <v>358</v>
+      </c>
+      <c r="B75" s="231"/>
+      <c r="C75" s="231"/>
+      <c r="D75" s="231"/>
+      <c r="E75" s="231"/>
+      <c r="F75" s="231"/>
+      <c r="G75" s="231"/>
+      <c r="H75" s="231"/>
+      <c r="I75" s="231"/>
+      <c r="J75" s="231"/>
+      <c r="K75" s="232"/>
     </row>
     <row r="76" spans="1:16" s="6" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A76" s="209" t="s">
-        <v>358</v>
-      </c>
-      <c r="B76" s="210"/>
-      <c r="C76" s="211"/>
-      <c r="D76" s="215" t="s">
+      <c r="A76" s="233" t="s">
+        <v>356</v>
+      </c>
+      <c r="B76" s="234"/>
+      <c r="C76" s="235"/>
+      <c r="D76" s="239" t="s">
         <v>72</v>
       </c>
-      <c r="E76" s="216"/>
-      <c r="F76" s="216"/>
-      <c r="G76" s="216"/>
-      <c r="H76" s="219" t="s">
-        <v>356</v>
-      </c>
-      <c r="I76" s="219"/>
-      <c r="J76" s="221" t="s">
-        <v>357</v>
-      </c>
-      <c r="K76" s="222"/>
+      <c r="E76" s="240"/>
+      <c r="F76" s="240"/>
+      <c r="G76" s="240"/>
+      <c r="H76" s="243" t="s">
+        <v>354</v>
+      </c>
+      <c r="I76" s="243"/>
+      <c r="J76" s="245" t="s">
+        <v>355</v>
+      </c>
+      <c r="K76" s="246"/>
     </row>
     <row r="77" spans="1:16" s="6" customFormat="1" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A77" s="212"/>
-      <c r="B77" s="213"/>
-      <c r="C77" s="214"/>
-      <c r="D77" s="217"/>
-      <c r="E77" s="218"/>
-      <c r="F77" s="218"/>
-      <c r="G77" s="218"/>
-      <c r="H77" s="220"/>
-      <c r="I77" s="220"/>
-      <c r="J77" s="217"/>
-      <c r="K77" s="223"/>
+      <c r="A77" s="236"/>
+      <c r="B77" s="237"/>
+      <c r="C77" s="238"/>
+      <c r="D77" s="241"/>
+      <c r="E77" s="242"/>
+      <c r="F77" s="242"/>
+      <c r="G77" s="242"/>
+      <c r="H77" s="244"/>
+      <c r="I77" s="244"/>
+      <c r="J77" s="241"/>
+      <c r="K77" s="247"/>
     </row>
     <row r="78" spans="1:16">
       <c r="D78" s="5" t="s">
@@ -8743,1327 +8759,1327 @@
   <sheetData>
     <row r="1" spans="2:14" ht="41.25" customHeight="1"/>
     <row r="2" spans="2:14" ht="33.950000000000003" customHeight="1">
-      <c r="B2" s="252" t="s">
+      <c r="B2" s="60" t="s">
+        <v>349</v>
+      </c>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="62"/>
+    </row>
+    <row r="3" spans="2:14" ht="21" customHeight="1">
+      <c r="B3" s="63" t="s">
+        <v>350</v>
+      </c>
+      <c r="C3" s="64"/>
+      <c r="D3" s="65" t="s">
         <v>351</v>
       </c>
-      <c r="C2" s="253"/>
-      <c r="D2" s="253"/>
-      <c r="E2" s="253"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
-      <c r="M2" s="254"/>
-    </row>
-    <row r="3" spans="2:14" ht="21" customHeight="1">
-      <c r="B3" s="255" t="s">
-        <v>352</v>
-      </c>
-      <c r="C3" s="256"/>
-      <c r="D3" s="257" t="s">
-        <v>353</v>
-      </c>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="259"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
       <c r="H3" s="38"/>
       <c r="I3" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="J3" s="260" t="s">
-        <v>354</v>
-      </c>
-      <c r="K3" s="261"/>
-      <c r="L3" s="261"/>
-      <c r="M3" s="261"/>
+        <v>291</v>
+      </c>
+      <c r="J3" s="68" t="s">
+        <v>352</v>
+      </c>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
       <c r="N3" s="40"/>
     </row>
     <row r="4" spans="2:14" ht="21.95" customHeight="1">
       <c r="B4" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="262" t="s">
+      <c r="D4" s="71"/>
+      <c r="E4" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="263"/>
-      <c r="E4" s="262" t="s">
+      <c r="F4" s="71"/>
+      <c r="G4" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="263"/>
-      <c r="G4" s="42" t="s">
+      <c r="H4" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="I4" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="I4" s="262" t="s">
+      <c r="J4" s="71"/>
+      <c r="K4" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="J4" s="263"/>
-      <c r="K4" s="262" t="s">
+      <c r="L4" s="71"/>
+      <c r="M4" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="L4" s="263"/>
-      <c r="M4" s="42" t="s">
+    </row>
+    <row r="5" spans="2:14" ht="21" customHeight="1">
+      <c r="B5" s="55" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="5" spans="2:14" ht="21" customHeight="1">
-      <c r="B5" s="247" t="s">
+      <c r="C5" s="56"/>
+      <c r="D5" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="248"/>
-      <c r="D5" s="42" t="s">
+      <c r="E5" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="F5" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="G5" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="H5" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="247" t="s">
-        <v>107</v>
-      </c>
-      <c r="I5" s="248"/>
+      <c r="I5" s="56"/>
       <c r="J5" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="K5" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="K5" s="42" t="s">
+      <c r="L5" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="L5" s="42" t="s">
+      <c r="M5" s="42" t="s">
         <v>105</v>
-      </c>
-      <c r="M5" s="42" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="21" customHeight="1">
       <c r="B6" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="D6" s="42" t="s">
         <v>109</v>
-      </c>
-      <c r="D6" s="42" t="s">
-        <v>110</v>
       </c>
       <c r="E6" s="42"/>
       <c r="F6" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="G6" s="249" t="s">
+      <c r="H6" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="H6" s="41" t="s">
+      <c r="I6" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="I6" s="41" t="s">
-        <v>114</v>
-      </c>
       <c r="J6" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K6" s="42"/>
       <c r="L6" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="M6" s="57" t="s">
         <v>115</v>
-      </c>
-      <c r="M6" s="249" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="21" customHeight="1">
       <c r="B7" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="D7" s="42" t="s">
         <v>118</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>119</v>
       </c>
       <c r="E7" s="42"/>
       <c r="F7" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G7" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G7" s="58"/>
       <c r="H7" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="I7" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="I7" s="41" t="s">
-        <v>121</v>
-      </c>
       <c r="J7" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K7" s="42"/>
       <c r="L7" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M7" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M7" s="58"/>
     </row>
     <row r="8" spans="2:14" ht="21" customHeight="1">
       <c r="B8" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="41" t="s">
-        <v>123</v>
-      </c>
       <c r="D8" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E8" s="42"/>
       <c r="F8" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="G8" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="G8" s="58"/>
       <c r="H8" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="I8" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="I8" s="41" t="s">
+      <c r="J8" s="42" t="s">
         <v>125</v>
-      </c>
-      <c r="J8" s="42" t="s">
-        <v>126</v>
       </c>
       <c r="K8" s="42"/>
       <c r="L8" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M8" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M8" s="58"/>
     </row>
     <row r="9" spans="2:14" ht="21" customHeight="1">
       <c r="B9" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="C9" s="41" t="s">
-        <v>128</v>
-      </c>
       <c r="D9" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E9" s="42"/>
       <c r="F9" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G9" s="58"/>
       <c r="H9" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="I9" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="J9" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="J9" s="42" t="s">
+      <c r="K9" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="K9" s="42" t="s">
+      <c r="L9" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="L9" s="42" t="s">
-        <v>133</v>
-      </c>
-      <c r="M9" s="250"/>
+      <c r="M9" s="58"/>
     </row>
     <row r="10" spans="2:14" ht="21" customHeight="1">
       <c r="B10" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="41" t="s">
-        <v>135</v>
-      </c>
       <c r="D10" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E10" s="42"/>
       <c r="F10" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G10" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G10" s="58"/>
       <c r="H10" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="I10" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="I10" s="41" t="s">
-        <v>137</v>
-      </c>
       <c r="J10" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K10" s="42"/>
       <c r="L10" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M10" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M10" s="58"/>
     </row>
     <row r="11" spans="2:14" ht="21" customHeight="1">
       <c r="B11" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="C11" s="41" t="s">
-        <v>139</v>
-      </c>
       <c r="D11" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E11" s="42"/>
       <c r="F11" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G11" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G11" s="58"/>
       <c r="H11" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="I11" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="I11" s="41" t="s">
-        <v>141</v>
-      </c>
       <c r="J11" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K11" s="42"/>
       <c r="L11" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M11" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M11" s="58"/>
     </row>
     <row r="12" spans="2:14" ht="21" customHeight="1">
       <c r="B12" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="41" t="s">
-        <v>143</v>
-      </c>
       <c r="D12" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E12" s="42"/>
       <c r="F12" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G12" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G12" s="58"/>
       <c r="H12" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="I12" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="I12" s="41" t="s">
-        <v>145</v>
-      </c>
       <c r="J12" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K12" s="42"/>
       <c r="L12" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M12" s="251"/>
+        <v>114</v>
+      </c>
+      <c r="M12" s="59"/>
     </row>
     <row r="13" spans="2:14" ht="21" customHeight="1">
       <c r="B13" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="C13" s="41" t="s">
-        <v>147</v>
-      </c>
       <c r="D13" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E13" s="42"/>
       <c r="F13" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="G13" s="250"/>
-      <c r="H13" s="247" t="s">
-        <v>148</v>
-      </c>
-      <c r="I13" s="248"/>
+        <v>114</v>
+      </c>
+      <c r="G13" s="58"/>
+      <c r="H13" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="I13" s="56"/>
       <c r="J13" s="42"/>
       <c r="K13" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="L13" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="L13" s="42" t="s">
+      <c r="M13" s="42" t="s">
         <v>105</v>
-      </c>
-      <c r="M13" s="42" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="21" customHeight="1">
       <c r="B14" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="C14" s="41" t="s">
-        <v>150</v>
-      </c>
       <c r="D14" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E14" s="42"/>
       <c r="F14" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G14" s="251"/>
+        <v>110</v>
+      </c>
+      <c r="G14" s="59"/>
       <c r="H14" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="I14" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="I14" s="41" t="s">
-        <v>152</v>
-      </c>
       <c r="J14" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K14" s="42"/>
       <c r="L14" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="M14" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="M14" s="249" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="15" spans="2:14" ht="21" customHeight="1">
-      <c r="B15" s="247" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15" s="248"/>
+      <c r="B15" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="56"/>
       <c r="D15" s="42"/>
       <c r="E15" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="42" t="s">
-        <v>105</v>
-      </c>
       <c r="G15" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="H15" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="H15" s="41" t="s">
+      <c r="I15" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="I15" s="41" t="s">
-        <v>156</v>
-      </c>
       <c r="J15" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K15" s="42"/>
       <c r="L15" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M15" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M15" s="58"/>
     </row>
     <row r="16" spans="2:14" ht="21" customHeight="1">
       <c r="B16" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="C16" s="41" t="s">
-        <v>158</v>
-      </c>
       <c r="D16" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E16" s="42"/>
       <c r="F16" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="G16" s="249" t="s">
-        <v>112</v>
-      </c>
       <c r="H16" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="I16" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="I16" s="41" t="s">
-        <v>160</v>
-      </c>
       <c r="J16" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K16" s="42"/>
       <c r="L16" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M16" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M16" s="58"/>
     </row>
     <row r="17" spans="2:13" ht="21" customHeight="1">
       <c r="B17" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="C17" s="41" t="s">
-        <v>162</v>
-      </c>
       <c r="D17" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E17" s="42"/>
       <c r="F17" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G17" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G17" s="58"/>
       <c r="H17" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="I17" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="I17" s="41" t="s">
-        <v>164</v>
-      </c>
       <c r="J17" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K17" s="42"/>
       <c r="L17" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M17" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M17" s="58"/>
     </row>
     <row r="18" spans="2:13" ht="21" customHeight="1">
       <c r="B18" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="C18" s="41" t="s">
-        <v>166</v>
-      </c>
       <c r="D18" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E18" s="42"/>
       <c r="F18" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G18" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G18" s="58"/>
       <c r="H18" s="41" t="s">
+        <v>166</v>
+      </c>
+      <c r="I18" s="41" t="s">
         <v>167</v>
       </c>
-      <c r="I18" s="41" t="s">
-        <v>168</v>
-      </c>
       <c r="J18" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K18" s="42"/>
       <c r="L18" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M18" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M18" s="58"/>
     </row>
     <row r="19" spans="2:13" ht="21" customHeight="1">
       <c r="B19" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="41" t="s">
-        <v>170</v>
-      </c>
       <c r="D19" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E19" s="42"/>
       <c r="F19" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G19" s="251"/>
+        <v>110</v>
+      </c>
+      <c r="G19" s="59"/>
       <c r="H19" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="I19" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="I19" s="41" t="s">
-        <v>172</v>
-      </c>
       <c r="J19" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K19" s="42"/>
       <c r="L19" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M19" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M19" s="58"/>
     </row>
     <row r="20" spans="2:13" ht="21" customHeight="1">
-      <c r="B20" s="247" t="s">
-        <v>173</v>
-      </c>
-      <c r="C20" s="248"/>
+      <c r="B20" s="55" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" s="56"/>
       <c r="D20" s="42"/>
       <c r="E20" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="F20" s="42" t="s">
-        <v>105</v>
-      </c>
       <c r="G20" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H20" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="I20" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="I20" s="41" t="s">
-        <v>175</v>
-      </c>
       <c r="J20" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K20" s="42"/>
       <c r="L20" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="M20" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="M20" s="58"/>
     </row>
     <row r="21" spans="2:13" ht="21" customHeight="1">
       <c r="B21" s="41" t="s">
+        <v>175</v>
+      </c>
+      <c r="C21" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="C21" s="41" t="s">
-        <v>177</v>
-      </c>
       <c r="D21" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E21" s="42"/>
       <c r="F21" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="G21" s="249" t="s">
-        <v>112</v>
-      </c>
       <c r="H21" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="I21" s="41" t="s">
         <v>178</v>
       </c>
-      <c r="I21" s="41" t="s">
-        <v>179</v>
-      </c>
       <c r="J21" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K21" s="42"/>
       <c r="L21" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M21" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M21" s="58"/>
     </row>
     <row r="22" spans="2:13" ht="21" customHeight="1">
       <c r="B22" s="41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E22" s="42"/>
       <c r="F22" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G22" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G22" s="58"/>
       <c r="H22" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="I22" s="41" t="s">
         <v>181</v>
       </c>
-      <c r="I22" s="41" t="s">
-        <v>182</v>
-      </c>
       <c r="J22" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K22" s="42"/>
       <c r="L22" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M22" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M22" s="58"/>
     </row>
     <row r="23" spans="2:13" ht="21" customHeight="1">
       <c r="B23" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="C23" s="41" t="s">
         <v>183</v>
       </c>
-      <c r="C23" s="41" t="s">
-        <v>184</v>
-      </c>
       <c r="D23" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E23" s="42"/>
       <c r="F23" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G23" s="58"/>
       <c r="H23" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="I23" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="I23" s="41" t="s">
-        <v>186</v>
-      </c>
       <c r="J23" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M23" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M23" s="58"/>
     </row>
     <row r="24" spans="2:13" ht="21" customHeight="1">
       <c r="B24" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="C24" s="41" t="s">
-        <v>188</v>
-      </c>
       <c r="D24" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E24" s="42"/>
       <c r="F24" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G24" s="251"/>
+        <v>110</v>
+      </c>
+      <c r="G24" s="59"/>
       <c r="H24" s="41" t="s">
+        <v>188</v>
+      </c>
+      <c r="I24" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="I24" s="41" t="s">
-        <v>190</v>
-      </c>
       <c r="J24" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M24" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M24" s="58"/>
     </row>
     <row r="25" spans="2:13" ht="21" customHeight="1">
-      <c r="B25" s="247" t="s">
-        <v>191</v>
-      </c>
-      <c r="C25" s="248"/>
+      <c r="B25" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="C25" s="56"/>
       <c r="D25" s="42"/>
       <c r="E25" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="42" t="s">
-        <v>105</v>
-      </c>
       <c r="G25" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H25" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="I25" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="I25" s="41" t="s">
-        <v>193</v>
-      </c>
       <c r="J25" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K25" s="42"/>
       <c r="L25" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M25" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M25" s="58"/>
     </row>
     <row r="26" spans="2:13" ht="21" customHeight="1">
       <c r="B26" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="C26" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="C26" s="41" t="s">
-        <v>195</v>
-      </c>
       <c r="D26" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E26" s="42"/>
       <c r="F26" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="G26" s="249" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="G26" s="57" t="s">
+        <v>111</v>
       </c>
       <c r="H26" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="I26" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="I26" s="41" t="s">
-        <v>197</v>
-      </c>
       <c r="J26" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K26" s="42"/>
       <c r="L26" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M26" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M26" s="58"/>
     </row>
     <row r="27" spans="2:13" ht="21" customHeight="1">
       <c r="B27" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="C27" s="41" t="s">
         <v>198</v>
       </c>
-      <c r="C27" s="41" t="s">
-        <v>199</v>
-      </c>
       <c r="D27" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E27" s="42"/>
       <c r="F27" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G27" s="58"/>
       <c r="H27" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="I27" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="I27" s="41" t="s">
-        <v>201</v>
-      </c>
       <c r="J27" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K27" s="42"/>
       <c r="L27" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M27" s="251"/>
+        <v>114</v>
+      </c>
+      <c r="M27" s="59"/>
     </row>
     <row r="28" spans="2:13" ht="21" customHeight="1">
       <c r="B28" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="C28" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>203</v>
-      </c>
       <c r="D28" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E28" s="42"/>
       <c r="F28" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="G28" s="250"/>
-      <c r="H28" s="247" t="s">
-        <v>204</v>
-      </c>
-      <c r="I28" s="248"/>
+        <v>114</v>
+      </c>
+      <c r="G28" s="58"/>
+      <c r="H28" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="I28" s="56"/>
       <c r="J28" s="42"/>
       <c r="K28" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="L28" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="L28" s="42" t="s">
+      <c r="M28" s="42" t="s">
         <v>105</v>
-      </c>
-      <c r="M28" s="42" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="29" spans="2:13" ht="21" customHeight="1">
       <c r="B29" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>206</v>
-      </c>
       <c r="D29" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E29" s="42"/>
       <c r="F29" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G29" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G29" s="58"/>
       <c r="H29" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="I29" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="I29" s="41" t="s">
-        <v>208</v>
-      </c>
       <c r="J29" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K29" s="42"/>
       <c r="L29" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="M29" s="57" t="s">
         <v>115</v>
-      </c>
-      <c r="M29" s="249" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="30" spans="2:13" ht="21" customHeight="1">
       <c r="B30" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>210</v>
-      </c>
       <c r="D30" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E30" s="42"/>
       <c r="F30" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G30" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G30" s="58"/>
       <c r="H30" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="I30" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="I30" s="41" t="s">
-        <v>212</v>
-      </c>
       <c r="J30" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K30" s="42"/>
       <c r="L30" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M30" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M30" s="58"/>
     </row>
     <row r="31" spans="2:13" ht="21" customHeight="1">
       <c r="B31" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="C31" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>214</v>
-      </c>
       <c r="D31" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E31" s="42"/>
       <c r="F31" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G31" s="58"/>
       <c r="H31" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="I31" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="I31" s="41" t="s">
-        <v>216</v>
-      </c>
       <c r="J31" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K31" s="42"/>
       <c r="L31" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M31" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M31" s="58"/>
     </row>
     <row r="32" spans="2:13" ht="21" customHeight="1">
       <c r="B32" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="C32" s="41" t="s">
-        <v>218</v>
-      </c>
       <c r="D32" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E32" s="42"/>
       <c r="F32" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G32" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G32" s="58"/>
       <c r="H32" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="I32" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="I32" s="41" t="s">
-        <v>220</v>
-      </c>
       <c r="J32" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K32" s="42"/>
       <c r="L32" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="M32" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="M32" s="58"/>
     </row>
     <row r="33" spans="2:13" ht="21" customHeight="1">
       <c r="B33" s="41" t="s">
+        <v>220</v>
+      </c>
+      <c r="C33" s="41" t="s">
         <v>221</v>
       </c>
-      <c r="C33" s="41" t="s">
-        <v>222</v>
-      </c>
       <c r="D33" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E33" s="42"/>
       <c r="F33" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G33" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G33" s="58"/>
       <c r="H33" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="I33" s="41" t="s">
         <v>223</v>
       </c>
-      <c r="I33" s="41" t="s">
-        <v>224</v>
-      </c>
       <c r="J33" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K33" s="42"/>
       <c r="L33" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M33" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M33" s="58"/>
     </row>
     <row r="34" spans="2:13" ht="21" customHeight="1">
       <c r="B34" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="C34" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="C34" s="41" t="s">
-        <v>226</v>
-      </c>
       <c r="D34" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E34" s="42"/>
       <c r="F34" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G34" s="251"/>
+        <v>110</v>
+      </c>
+      <c r="G34" s="59"/>
       <c r="H34" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="I34" s="41" t="s">
         <v>227</v>
       </c>
-      <c r="I34" s="41" t="s">
-        <v>228</v>
-      </c>
       <c r="J34" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K34" s="42"/>
       <c r="L34" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M34" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M34" s="58"/>
     </row>
     <row r="35" spans="2:13" ht="21" customHeight="1">
-      <c r="B35" s="247" t="s">
-        <v>107</v>
-      </c>
-      <c r="C35" s="248"/>
+      <c r="B35" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" s="56"/>
       <c r="D35" s="42"/>
       <c r="E35" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="F35" s="42" t="s">
-        <v>105</v>
-      </c>
       <c r="G35" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H35" s="41" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I35" s="41" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J35" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K35" s="42"/>
       <c r="L35" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M35" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M35" s="58"/>
     </row>
     <row r="36" spans="2:13" ht="21" customHeight="1">
       <c r="B36" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="C36" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="C36" s="41" t="s">
-        <v>231</v>
-      </c>
       <c r="D36" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E36" s="42"/>
       <c r="F36" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="G36" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="G36" s="249" t="s">
-        <v>112</v>
-      </c>
       <c r="H36" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="I36" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="I36" s="41" t="s">
-        <v>233</v>
-      </c>
       <c r="J36" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K36" s="42"/>
       <c r="L36" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M36" s="251"/>
+        <v>114</v>
+      </c>
+      <c r="M36" s="59"/>
     </row>
     <row r="37" spans="2:13" ht="21" customHeight="1">
       <c r="B37" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="C37" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="41" t="s">
-        <v>235</v>
-      </c>
       <c r="D37" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E37" s="42"/>
       <c r="F37" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="G37" s="250"/>
-      <c r="H37" s="247" t="s">
-        <v>236</v>
-      </c>
-      <c r="I37" s="248"/>
+        <v>114</v>
+      </c>
+      <c r="G37" s="58"/>
+      <c r="H37" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="I37" s="56"/>
       <c r="J37" s="42"/>
       <c r="K37" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="L37" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="L37" s="42" t="s">
+      <c r="M37" s="42" t="s">
         <v>105</v>
-      </c>
-      <c r="M37" s="42" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="38" spans="2:13" ht="21" customHeight="1">
       <c r="B38" s="41" t="s">
+        <v>236</v>
+      </c>
+      <c r="C38" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="C38" s="41" t="s">
-        <v>238</v>
-      </c>
       <c r="D38" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E38" s="42"/>
       <c r="F38" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G38" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G38" s="58"/>
       <c r="H38" s="41" t="s">
+        <v>238</v>
+      </c>
+      <c r="I38" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="I38" s="41" t="s">
-        <v>240</v>
-      </c>
       <c r="J38" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K38" s="42"/>
       <c r="L38" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="M38" s="57" t="s">
         <v>115</v>
-      </c>
-      <c r="M38" s="249" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="39" spans="2:13" ht="21" customHeight="1">
       <c r="B39" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C39" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="41" t="s">
-        <v>242</v>
-      </c>
       <c r="D39" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E39" s="42"/>
       <c r="F39" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G39" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G39" s="58"/>
       <c r="H39" s="41" t="s">
+        <v>242</v>
+      </c>
+      <c r="I39" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="I39" s="41" t="s">
-        <v>244</v>
-      </c>
       <c r="J39" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K39" s="42"/>
       <c r="L39" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M39" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M39" s="58"/>
     </row>
     <row r="40" spans="2:13" ht="21" customHeight="1">
       <c r="B40" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="C40" s="41" t="s">
         <v>245</v>
       </c>
-      <c r="C40" s="41" t="s">
-        <v>246</v>
-      </c>
       <c r="D40" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E40" s="42"/>
       <c r="F40" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G40" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G40" s="58"/>
       <c r="H40" s="41" t="s">
+        <v>246</v>
+      </c>
+      <c r="I40" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="I40" s="41" t="s">
-        <v>248</v>
-      </c>
       <c r="J40" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K40" s="42"/>
       <c r="L40" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M40" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M40" s="58"/>
     </row>
     <row r="41" spans="2:13" ht="21" customHeight="1">
       <c r="B41" s="41" t="s">
+        <v>248</v>
+      </c>
+      <c r="C41" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="C41" s="41" t="s">
-        <v>250</v>
-      </c>
       <c r="D41" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E41" s="42"/>
       <c r="F41" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G41" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G41" s="58"/>
       <c r="H41" s="41" t="s">
+        <v>250</v>
+      </c>
+      <c r="I41" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="I41" s="41" t="s">
-        <v>252</v>
-      </c>
       <c r="J41" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K41" s="42"/>
       <c r="L41" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="M41" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="M41" s="58"/>
     </row>
     <row r="42" spans="2:13" ht="21" customHeight="1">
       <c r="B42" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="C42" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="C42" s="41" t="s">
-        <v>254</v>
-      </c>
       <c r="D42" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E42" s="42"/>
       <c r="F42" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G42" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G42" s="58"/>
       <c r="H42" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="I42" s="41" t="s">
         <v>255</v>
       </c>
-      <c r="I42" s="41" t="s">
-        <v>256</v>
-      </c>
       <c r="J42" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K42" s="42"/>
       <c r="L42" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M42" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M42" s="58"/>
     </row>
     <row r="43" spans="2:13" ht="21" customHeight="1">
       <c r="B43" s="41" t="s">
+        <v>256</v>
+      </c>
+      <c r="C43" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="C43" s="41" t="s">
-        <v>258</v>
-      </c>
       <c r="D43" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E43" s="42"/>
       <c r="F43" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G43" s="250"/>
+        <v>110</v>
+      </c>
+      <c r="G43" s="58"/>
       <c r="H43" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="I43" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="I43" s="41" t="s">
-        <v>260</v>
-      </c>
       <c r="J43" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K43" s="42"/>
       <c r="L43" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M43" s="250"/>
+        <v>114</v>
+      </c>
+      <c r="M43" s="58"/>
     </row>
     <row r="44" spans="2:13" ht="21" customHeight="1">
       <c r="B44" s="41" t="s">
+        <v>260</v>
+      </c>
+      <c r="C44" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="C44" s="41" t="s">
+      <c r="D44" s="42" t="s">
         <v>262</v>
-      </c>
-      <c r="D44" s="42" t="s">
-        <v>263</v>
       </c>
       <c r="E44" s="42"/>
       <c r="F44" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="G44" s="251"/>
+        <v>114</v>
+      </c>
+      <c r="G44" s="59"/>
       <c r="H44" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="I44" s="41" t="s">
         <v>264</v>
       </c>
-      <c r="I44" s="41" t="s">
-        <v>265</v>
-      </c>
       <c r="J44" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K44" s="42"/>
       <c r="L44" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="M44" s="251"/>
+        <v>114</v>
+      </c>
+      <c r="M44" s="59"/>
     </row>
     <row r="45" spans="2:13" ht="21.95" customHeight="1">
-      <c r="B45" s="241" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="242"/>
-      <c r="D45" s="242"/>
-      <c r="E45" s="242"/>
-      <c r="F45" s="242"/>
-      <c r="G45" s="242"/>
-      <c r="H45" s="242"/>
-      <c r="I45" s="242"/>
-      <c r="J45" s="242"/>
-      <c r="K45" s="242"/>
-      <c r="L45" s="242"/>
-      <c r="M45" s="243"/>
+      <c r="B45" s="49" t="s">
+        <v>265</v>
+      </c>
+      <c r="C45" s="50"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="50"/>
+      <c r="G45" s="50"/>
+      <c r="H45" s="50"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="50"/>
+      <c r="K45" s="50"/>
+      <c r="L45" s="50"/>
+      <c r="M45" s="51"/>
     </row>
     <row r="46" spans="2:13" ht="23.1" customHeight="1">
-      <c r="B46" s="244"/>
-      <c r="C46" s="245"/>
-      <c r="D46" s="245"/>
-      <c r="E46" s="245"/>
-      <c r="F46" s="245"/>
-      <c r="G46" s="245"/>
-      <c r="H46" s="245"/>
-      <c r="I46" s="245"/>
-      <c r="J46" s="245"/>
-      <c r="K46" s="245"/>
-      <c r="L46" s="245"/>
-      <c r="M46" s="246"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="53"/>
+      <c r="M46" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -10150,711 +10166,711 @@
     </row>
     <row r="3" spans="2:11" ht="27">
       <c r="B3" s="44" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" s="68" t="s">
         <v>267</v>
       </c>
-      <c r="C3" s="260" t="s">
+      <c r="D3" s="282"/>
+      <c r="E3" s="44" t="s">
         <v>268</v>
       </c>
-      <c r="D3" s="281"/>
-      <c r="E3" s="44" t="s">
+      <c r="F3" s="45" t="s">
         <v>269</v>
       </c>
-      <c r="F3" s="45" t="s">
-        <v>270</v>
-      </c>
-      <c r="G3" s="255" t="s">
-        <v>363</v>
-      </c>
-      <c r="H3" s="256"/>
-      <c r="I3" s="283" t="s">
-        <v>362</v>
-      </c>
-      <c r="J3" s="285"/>
-      <c r="K3" s="284"/>
+      <c r="G3" s="63" t="s">
+        <v>361</v>
+      </c>
+      <c r="H3" s="64"/>
+      <c r="I3" s="284" t="s">
+        <v>360</v>
+      </c>
+      <c r="J3" s="286"/>
+      <c r="K3" s="285"/>
     </row>
     <row r="4" spans="2:11">
       <c r="B4" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" s="284" t="s">
         <v>271</v>
       </c>
-      <c r="C4" s="283" t="s">
+      <c r="D4" s="285"/>
+      <c r="E4" s="44" t="s">
         <v>272</v>
       </c>
-      <c r="D4" s="284"/>
-      <c r="E4" s="44" t="s">
+      <c r="F4" s="45" t="s">
         <v>273</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="G4" s="63" t="s">
         <v>274</v>
       </c>
-      <c r="G4" s="255" t="s">
+      <c r="H4" s="64"/>
+      <c r="I4" s="68" t="s">
         <v>275</v>
       </c>
-      <c r="H4" s="256"/>
-      <c r="I4" s="260" t="s">
-        <v>276</v>
-      </c>
-      <c r="J4" s="261"/>
-      <c r="K4" s="281"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="282"/>
     </row>
     <row r="5" spans="2:11">
       <c r="B5" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="68" t="s">
         <v>277</v>
       </c>
-      <c r="C5" s="260" t="s">
+      <c r="D5" s="282"/>
+      <c r="E5" s="44" t="s">
         <v>278</v>
       </c>
-      <c r="D5" s="281"/>
-      <c r="E5" s="44" t="s">
+      <c r="F5" s="45" t="s">
         <v>279</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="G5" s="63" t="s">
         <v>280</v>
       </c>
-      <c r="G5" s="255" t="s">
+      <c r="H5" s="64"/>
+      <c r="I5" s="68" t="s">
         <v>281</v>
       </c>
-      <c r="H5" s="256"/>
-      <c r="I5" s="260" t="s">
+      <c r="J5" s="282"/>
+      <c r="K5" s="45" t="s">
         <v>282</v>
-      </c>
-      <c r="J5" s="281"/>
-      <c r="K5" s="45" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="26.25" customHeight="1">
       <c r="B6" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="C6" s="284" t="s">
+        <v>362</v>
+      </c>
+      <c r="D6" s="285"/>
+      <c r="E6" s="44" t="s">
         <v>284</v>
       </c>
-      <c r="C6" s="283" t="s">
+      <c r="F6" s="45" t="s">
         <v>285</v>
       </c>
-      <c r="D6" s="284"/>
-      <c r="E6" s="44" t="s">
+      <c r="G6" s="63" t="s">
         <v>286</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="H6" s="64"/>
+      <c r="I6" s="65" t="s">
         <v>287</v>
       </c>
-      <c r="G6" s="255" t="s">
-        <v>288</v>
-      </c>
-      <c r="H6" s="256"/>
-      <c r="I6" s="257" t="s">
-        <v>289</v>
-      </c>
-      <c r="J6" s="261"/>
-      <c r="K6" s="281"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="282"/>
     </row>
     <row r="7" spans="2:11" ht="15.95" customHeight="1">
       <c r="B7" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" s="280" t="s">
+        <v>353</v>
+      </c>
+      <c r="D7" s="281"/>
+      <c r="E7" s="44" t="s">
+        <v>289</v>
+      </c>
+      <c r="F7" s="39" t="s">
         <v>290</v>
       </c>
-      <c r="C7" s="279" t="s">
-        <v>355</v>
-      </c>
-      <c r="D7" s="280"/>
-      <c r="E7" s="44" t="s">
+      <c r="G7" s="63" t="s">
         <v>291</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="H7" s="64"/>
+      <c r="I7" s="68" t="s">
         <v>292</v>
       </c>
-      <c r="G7" s="255" t="s">
-        <v>293</v>
-      </c>
-      <c r="H7" s="256"/>
-      <c r="I7" s="260" t="s">
-        <v>294</v>
-      </c>
-      <c r="J7" s="261"/>
-      <c r="K7" s="281"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="282"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="264"/>
-      <c r="C8" s="265"/>
-      <c r="D8" s="265"/>
-      <c r="E8" s="265"/>
-      <c r="F8" s="265"/>
-      <c r="G8" s="265"/>
-      <c r="H8" s="265"/>
-      <c r="I8" s="265"/>
-      <c r="J8" s="265"/>
-      <c r="K8" s="266"/>
+      <c r="B8" s="265"/>
+      <c r="C8" s="266"/>
+      <c r="D8" s="266"/>
+      <c r="E8" s="266"/>
+      <c r="F8" s="266"/>
+      <c r="G8" s="266"/>
+      <c r="H8" s="266"/>
+      <c r="I8" s="266"/>
+      <c r="J8" s="266"/>
+      <c r="K8" s="267"/>
     </row>
     <row r="9" spans="2:11">
       <c r="B9" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>294</v>
+      </c>
+      <c r="D9" s="283"/>
+      <c r="E9" s="283"/>
+      <c r="F9" s="283"/>
+      <c r="G9" s="283"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="44" t="s">
         <v>295</v>
       </c>
-      <c r="C9" s="255" t="s">
+      <c r="J9" s="63" t="s">
         <v>296</v>
       </c>
-      <c r="D9" s="282"/>
-      <c r="E9" s="282"/>
-      <c r="F9" s="282"/>
-      <c r="G9" s="282"/>
-      <c r="H9" s="256"/>
-      <c r="I9" s="44" t="s">
+      <c r="K9" s="64"/>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" s="265" t="s">
         <v>297</v>
       </c>
-      <c r="J9" s="255" t="s">
+      <c r="C10" s="266"/>
+      <c r="D10" s="266"/>
+      <c r="E10" s="266"/>
+      <c r="F10" s="266"/>
+      <c r="G10" s="266"/>
+      <c r="H10" s="266"/>
+      <c r="I10" s="266"/>
+      <c r="J10" s="266"/>
+      <c r="K10" s="267"/>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="268" t="s">
         <v>298</v>
       </c>
-      <c r="K9" s="256"/>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" s="264" t="s">
+      <c r="C11" s="265" t="s">
         <v>299</v>
       </c>
-      <c r="C10" s="265"/>
-      <c r="D10" s="265"/>
-      <c r="E10" s="265"/>
-      <c r="F10" s="265"/>
-      <c r="G10" s="265"/>
-      <c r="H10" s="265"/>
-      <c r="I10" s="265"/>
-      <c r="J10" s="265"/>
-      <c r="K10" s="266"/>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11" s="267" t="s">
+      <c r="D11" s="266"/>
+      <c r="E11" s="266"/>
+      <c r="F11" s="266"/>
+      <c r="G11" s="266"/>
+      <c r="H11" s="267"/>
+      <c r="I11" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="C11" s="264" t="s">
+      <c r="J11" s="265"/>
+      <c r="K11" s="267"/>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" s="269"/>
+      <c r="C12" s="265" t="s">
         <v>301</v>
       </c>
-      <c r="D11" s="265"/>
-      <c r="E11" s="265"/>
-      <c r="F11" s="265"/>
-      <c r="G11" s="265"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="45" t="s">
+      <c r="D12" s="266"/>
+      <c r="E12" s="266"/>
+      <c r="F12" s="266"/>
+      <c r="G12" s="266"/>
+      <c r="H12" s="267"/>
+      <c r="I12" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="J11" s="264"/>
-      <c r="K11" s="266"/>
-    </row>
-    <row r="12" spans="2:11">
-      <c r="B12" s="268"/>
-      <c r="C12" s="264" t="s">
+      <c r="J12" s="265"/>
+      <c r="K12" s="267"/>
+    </row>
+    <row r="13" spans="2:11" ht="25.5" customHeight="1">
+      <c r="B13" s="270"/>
+      <c r="C13" s="265" t="s">
         <v>303</v>
       </c>
-      <c r="D12" s="265"/>
-      <c r="E12" s="265"/>
-      <c r="F12" s="265"/>
-      <c r="G12" s="265"/>
-      <c r="H12" s="266"/>
-      <c r="I12" s="45" t="s">
+      <c r="D13" s="266"/>
+      <c r="E13" s="266"/>
+      <c r="F13" s="266"/>
+      <c r="G13" s="266"/>
+      <c r="H13" s="267"/>
+      <c r="I13" s="45" t="s">
+        <v>302</v>
+      </c>
+      <c r="J13" s="265"/>
+      <c r="K13" s="267"/>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="B14" s="265" t="s">
         <v>304</v>
       </c>
-      <c r="J12" s="264"/>
-      <c r="K12" s="266"/>
-    </row>
-    <row r="13" spans="2:11" ht="25.5" customHeight="1">
-      <c r="B13" s="269"/>
-      <c r="C13" s="264" t="s">
+      <c r="C14" s="266"/>
+      <c r="D14" s="266"/>
+      <c r="E14" s="266"/>
+      <c r="F14" s="266"/>
+      <c r="G14" s="266"/>
+      <c r="H14" s="266"/>
+      <c r="I14" s="266"/>
+      <c r="J14" s="266"/>
+      <c r="K14" s="267"/>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="268" t="s">
         <v>305</v>
       </c>
-      <c r="D13" s="265"/>
-      <c r="E13" s="265"/>
-      <c r="F13" s="265"/>
-      <c r="G13" s="265"/>
-      <c r="H13" s="266"/>
-      <c r="I13" s="45" t="s">
-        <v>304</v>
-      </c>
-      <c r="J13" s="264"/>
-      <c r="K13" s="266"/>
-    </row>
-    <row r="14" spans="2:11">
-      <c r="B14" s="264" t="s">
+      <c r="C15" s="265" t="s">
         <v>306</v>
       </c>
-      <c r="C14" s="265"/>
-      <c r="D14" s="265"/>
-      <c r="E14" s="265"/>
-      <c r="F14" s="265"/>
-      <c r="G14" s="265"/>
-      <c r="H14" s="265"/>
-      <c r="I14" s="265"/>
-      <c r="J14" s="265"/>
-      <c r="K14" s="266"/>
-    </row>
-    <row r="15" spans="2:11">
-      <c r="B15" s="267" t="s">
+      <c r="D15" s="266"/>
+      <c r="E15" s="266"/>
+      <c r="F15" s="266"/>
+      <c r="G15" s="266"/>
+      <c r="H15" s="267"/>
+      <c r="I15" s="271" t="s">
+        <v>300</v>
+      </c>
+      <c r="J15" s="274"/>
+      <c r="K15" s="275"/>
+    </row>
+    <row r="16" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B16" s="270"/>
+      <c r="C16" s="265" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="264" t="s">
+      <c r="D16" s="266"/>
+      <c r="E16" s="266"/>
+      <c r="F16" s="266"/>
+      <c r="G16" s="266"/>
+      <c r="H16" s="267"/>
+      <c r="I16" s="273"/>
+      <c r="J16" s="278"/>
+      <c r="K16" s="279"/>
+    </row>
+    <row r="17" spans="2:11" ht="18" customHeight="1">
+      <c r="B17" s="268" t="s">
         <v>308</v>
       </c>
-      <c r="D15" s="265"/>
-      <c r="E15" s="265"/>
-      <c r="F15" s="265"/>
-      <c r="G15" s="265"/>
-      <c r="H15" s="266"/>
-      <c r="I15" s="270" t="s">
-        <v>302</v>
-      </c>
-      <c r="J15" s="273"/>
-      <c r="K15" s="274"/>
-    </row>
-    <row r="16" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B16" s="269"/>
-      <c r="C16" s="264" t="s">
+      <c r="C17" s="265" t="s">
         <v>309</v>
       </c>
-      <c r="D16" s="265"/>
-      <c r="E16" s="265"/>
-      <c r="F16" s="265"/>
-      <c r="G16" s="265"/>
-      <c r="H16" s="266"/>
-      <c r="I16" s="272"/>
-      <c r="J16" s="277"/>
-      <c r="K16" s="278"/>
-    </row>
-    <row r="17" spans="2:11" ht="18" customHeight="1">
-      <c r="B17" s="267" t="s">
+      <c r="D17" s="266"/>
+      <c r="E17" s="266"/>
+      <c r="F17" s="266"/>
+      <c r="G17" s="266"/>
+      <c r="H17" s="267"/>
+      <c r="I17" s="271" t="s">
+        <v>300</v>
+      </c>
+      <c r="J17" s="274"/>
+      <c r="K17" s="275"/>
+    </row>
+    <row r="18" spans="2:11" ht="27" customHeight="1">
+      <c r="B18" s="269"/>
+      <c r="C18" s="265" t="s">
         <v>310</v>
       </c>
-      <c r="C17" s="264" t="s">
+      <c r="D18" s="266"/>
+      <c r="E18" s="266"/>
+      <c r="F18" s="266"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="272"/>
+      <c r="J18" s="276"/>
+      <c r="K18" s="277"/>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" s="269"/>
+      <c r="C19" s="265" t="s">
         <v>311</v>
       </c>
-      <c r="D17" s="265"/>
-      <c r="E17" s="265"/>
-      <c r="F17" s="265"/>
-      <c r="G17" s="265"/>
-      <c r="H17" s="266"/>
-      <c r="I17" s="270" t="s">
-        <v>302</v>
-      </c>
-      <c r="J17" s="273"/>
-      <c r="K17" s="274"/>
-    </row>
-    <row r="18" spans="2:11" ht="27" customHeight="1">
-      <c r="B18" s="268"/>
-      <c r="C18" s="264" t="s">
+      <c r="D19" s="266"/>
+      <c r="E19" s="266"/>
+      <c r="F19" s="266"/>
+      <c r="G19" s="266"/>
+      <c r="H19" s="267"/>
+      <c r="I19" s="272"/>
+      <c r="J19" s="276"/>
+      <c r="K19" s="277"/>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" s="270"/>
+      <c r="C20" s="265" t="s">
         <v>312</v>
       </c>
-      <c r="D18" s="265"/>
-      <c r="E18" s="265"/>
-      <c r="F18" s="265"/>
-      <c r="G18" s="265"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="271"/>
-      <c r="J18" s="275"/>
-      <c r="K18" s="276"/>
-    </row>
-    <row r="19" spans="2:11">
-      <c r="B19" s="268"/>
-      <c r="C19" s="264" t="s">
+      <c r="D20" s="266"/>
+      <c r="E20" s="266"/>
+      <c r="F20" s="266"/>
+      <c r="G20" s="266"/>
+      <c r="H20" s="267"/>
+      <c r="I20" s="273"/>
+      <c r="J20" s="278"/>
+      <c r="K20" s="279"/>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" s="265" t="s">
         <v>313</v>
       </c>
-      <c r="D19" s="265"/>
-      <c r="E19" s="265"/>
-      <c r="F19" s="265"/>
-      <c r="G19" s="265"/>
-      <c r="H19" s="266"/>
-      <c r="I19" s="271"/>
-      <c r="J19" s="275"/>
-      <c r="K19" s="276"/>
-    </row>
-    <row r="20" spans="2:11">
-      <c r="B20" s="269"/>
-      <c r="C20" s="264" t="s">
+      <c r="C21" s="266"/>
+      <c r="D21" s="266"/>
+      <c r="E21" s="266"/>
+      <c r="F21" s="266"/>
+      <c r="G21" s="266"/>
+      <c r="H21" s="266"/>
+      <c r="I21" s="266"/>
+      <c r="J21" s="266"/>
+      <c r="K21" s="267"/>
+    </row>
+    <row r="22" spans="2:11" ht="18" customHeight="1">
+      <c r="B22" s="268" t="s">
         <v>314</v>
       </c>
-      <c r="D20" s="265"/>
-      <c r="E20" s="265"/>
-      <c r="F20" s="265"/>
-      <c r="G20" s="265"/>
-      <c r="H20" s="266"/>
-      <c r="I20" s="272"/>
-      <c r="J20" s="277"/>
-      <c r="K20" s="278"/>
-    </row>
-    <row r="21" spans="2:11">
-      <c r="B21" s="264" t="s">
+      <c r="C22" s="265" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="265"/>
-      <c r="D21" s="265"/>
-      <c r="E21" s="265"/>
-      <c r="F21" s="265"/>
-      <c r="G21" s="265"/>
-      <c r="H21" s="265"/>
-      <c r="I21" s="265"/>
-      <c r="J21" s="265"/>
-      <c r="K21" s="266"/>
-    </row>
-    <row r="22" spans="2:11" ht="18" customHeight="1">
-      <c r="B22" s="267" t="s">
+      <c r="D22" s="266"/>
+      <c r="E22" s="266"/>
+      <c r="F22" s="266"/>
+      <c r="G22" s="266"/>
+      <c r="H22" s="267"/>
+      <c r="I22" s="271" t="s">
+        <v>300</v>
+      </c>
+      <c r="J22" s="274"/>
+      <c r="K22" s="275"/>
+    </row>
+    <row r="23" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B23" s="270"/>
+      <c r="C23" s="265" t="s">
         <v>316</v>
       </c>
-      <c r="C22" s="264" t="s">
+      <c r="D23" s="266"/>
+      <c r="E23" s="266"/>
+      <c r="F23" s="266"/>
+      <c r="G23" s="266"/>
+      <c r="H23" s="267"/>
+      <c r="I23" s="273"/>
+      <c r="J23" s="278"/>
+      <c r="K23" s="279"/>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="B24" s="265" t="s">
         <v>317</v>
       </c>
-      <c r="D22" s="265"/>
-      <c r="E22" s="265"/>
-      <c r="F22" s="265"/>
-      <c r="G22" s="265"/>
-      <c r="H22" s="266"/>
-      <c r="I22" s="270" t="s">
-        <v>302</v>
-      </c>
-      <c r="J22" s="273"/>
-      <c r="K22" s="274"/>
-    </row>
-    <row r="23" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B23" s="269"/>
-      <c r="C23" s="264" t="s">
+      <c r="C24" s="266"/>
+      <c r="D24" s="266"/>
+      <c r="E24" s="266"/>
+      <c r="F24" s="266"/>
+      <c r="G24" s="266"/>
+      <c r="H24" s="266"/>
+      <c r="I24" s="266"/>
+      <c r="J24" s="266"/>
+      <c r="K24" s="267"/>
+    </row>
+    <row r="25" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B25" s="268" t="s">
         <v>318</v>
       </c>
-      <c r="D23" s="265"/>
-      <c r="E23" s="265"/>
-      <c r="F23" s="265"/>
-      <c r="G23" s="265"/>
-      <c r="H23" s="266"/>
-      <c r="I23" s="272"/>
-      <c r="J23" s="277"/>
-      <c r="K23" s="278"/>
-    </row>
-    <row r="24" spans="2:11">
-      <c r="B24" s="264" t="s">
+      <c r="C25" s="265" t="s">
         <v>319</v>
       </c>
-      <c r="C24" s="265"/>
-      <c r="D24" s="265"/>
-      <c r="E24" s="265"/>
-      <c r="F24" s="265"/>
-      <c r="G24" s="265"/>
-      <c r="H24" s="265"/>
-      <c r="I24" s="265"/>
-      <c r="J24" s="265"/>
-      <c r="K24" s="266"/>
-    </row>
-    <row r="25" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B25" s="267" t="s">
+      <c r="D25" s="266"/>
+      <c r="E25" s="266"/>
+      <c r="F25" s="266"/>
+      <c r="G25" s="266"/>
+      <c r="H25" s="267"/>
+      <c r="I25" s="271" t="s">
+        <v>300</v>
+      </c>
+      <c r="J25" s="274"/>
+      <c r="K25" s="275"/>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="B26" s="270"/>
+      <c r="C26" s="265" t="s">
         <v>320</v>
       </c>
-      <c r="C25" s="264" t="s">
-        <v>321</v>
-      </c>
-      <c r="D25" s="265"/>
-      <c r="E25" s="265"/>
-      <c r="F25" s="265"/>
-      <c r="G25" s="265"/>
-      <c r="H25" s="266"/>
-      <c r="I25" s="270" t="s">
-        <v>302</v>
-      </c>
-      <c r="J25" s="273"/>
-      <c r="K25" s="274"/>
-    </row>
-    <row r="26" spans="2:11">
-      <c r="B26" s="269"/>
-      <c r="C26" s="264" t="s">
-        <v>322</v>
-      </c>
-      <c r="D26" s="265"/>
-      <c r="E26" s="265"/>
-      <c r="F26" s="265"/>
-      <c r="G26" s="265"/>
-      <c r="H26" s="266"/>
-      <c r="I26" s="272"/>
-      <c r="J26" s="277"/>
-      <c r="K26" s="278"/>
+      <c r="D26" s="266"/>
+      <c r="E26" s="266"/>
+      <c r="F26" s="266"/>
+      <c r="G26" s="266"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="273"/>
+      <c r="J26" s="278"/>
+      <c r="K26" s="279"/>
     </row>
     <row r="27" spans="2:11" ht="15.95" customHeight="1">
       <c r="B27" s="46" t="s">
+        <v>321</v>
+      </c>
+      <c r="C27" s="265" t="s">
+        <v>322</v>
+      </c>
+      <c r="D27" s="266"/>
+      <c r="E27" s="266"/>
+      <c r="F27" s="266"/>
+      <c r="G27" s="266"/>
+      <c r="H27" s="267"/>
+      <c r="I27" s="45" t="s">
+        <v>300</v>
+      </c>
+      <c r="J27" s="265"/>
+      <c r="K27" s="267"/>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="B28" s="265" t="s">
         <v>323</v>
       </c>
-      <c r="C27" s="264" t="s">
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
+      <c r="F28" s="266"/>
+      <c r="G28" s="266"/>
+      <c r="H28" s="266"/>
+      <c r="I28" s="266"/>
+      <c r="J28" s="266"/>
+      <c r="K28" s="267"/>
+    </row>
+    <row r="29" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B29" s="268" t="s">
         <v>324</v>
       </c>
-      <c r="D27" s="265"/>
-      <c r="E27" s="265"/>
-      <c r="F27" s="265"/>
-      <c r="G27" s="265"/>
-      <c r="H27" s="266"/>
-      <c r="I27" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="J27" s="264"/>
-      <c r="K27" s="266"/>
-    </row>
-    <row r="28" spans="2:11">
-      <c r="B28" s="264" t="s">
+      <c r="C29" s="265" t="s">
         <v>325</v>
       </c>
-      <c r="C28" s="265"/>
-      <c r="D28" s="265"/>
-      <c r="E28" s="265"/>
-      <c r="F28" s="265"/>
-      <c r="G28" s="265"/>
-      <c r="H28" s="265"/>
-      <c r="I28" s="265"/>
-      <c r="J28" s="265"/>
-      <c r="K28" s="266"/>
-    </row>
-    <row r="29" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B29" s="267" t="s">
+      <c r="D29" s="266"/>
+      <c r="E29" s="266"/>
+      <c r="F29" s="266"/>
+      <c r="G29" s="266"/>
+      <c r="H29" s="267"/>
+      <c r="I29" s="271" t="s">
+        <v>300</v>
+      </c>
+      <c r="J29" s="274"/>
+      <c r="K29" s="275"/>
+    </row>
+    <row r="30" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B30" s="270"/>
+      <c r="C30" s="265" t="s">
         <v>326</v>
       </c>
-      <c r="C29" s="264" t="s">
+      <c r="D30" s="266"/>
+      <c r="E30" s="266"/>
+      <c r="F30" s="266"/>
+      <c r="G30" s="266"/>
+      <c r="H30" s="267"/>
+      <c r="I30" s="273"/>
+      <c r="J30" s="278"/>
+      <c r="K30" s="279"/>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="265" t="s">
         <v>327</v>
       </c>
-      <c r="D29" s="265"/>
-      <c r="E29" s="265"/>
-      <c r="F29" s="265"/>
-      <c r="G29" s="265"/>
-      <c r="H29" s="266"/>
-      <c r="I29" s="270" t="s">
-        <v>302</v>
-      </c>
-      <c r="J29" s="273"/>
-      <c r="K29" s="274"/>
-    </row>
-    <row r="30" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B30" s="269"/>
-      <c r="C30" s="264" t="s">
+      <c r="C31" s="266"/>
+      <c r="D31" s="266"/>
+      <c r="E31" s="266"/>
+      <c r="F31" s="266"/>
+      <c r="G31" s="266"/>
+      <c r="H31" s="266"/>
+      <c r="I31" s="266"/>
+      <c r="J31" s="266"/>
+      <c r="K31" s="267"/>
+    </row>
+    <row r="32" spans="2:11" ht="28.5" customHeight="1">
+      <c r="B32" s="268" t="s">
         <v>328</v>
       </c>
-      <c r="D30" s="265"/>
-      <c r="E30" s="265"/>
-      <c r="F30" s="265"/>
-      <c r="G30" s="265"/>
-      <c r="H30" s="266"/>
-      <c r="I30" s="272"/>
-      <c r="J30" s="277"/>
-      <c r="K30" s="278"/>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="264" t="s">
+      <c r="C32" s="265" t="s">
         <v>329</v>
       </c>
-      <c r="C31" s="265"/>
-      <c r="D31" s="265"/>
-      <c r="E31" s="265"/>
-      <c r="F31" s="265"/>
-      <c r="G31" s="265"/>
-      <c r="H31" s="265"/>
-      <c r="I31" s="265"/>
-      <c r="J31" s="265"/>
-      <c r="K31" s="266"/>
-    </row>
-    <row r="32" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B32" s="267" t="s">
+      <c r="D32" s="266"/>
+      <c r="E32" s="266"/>
+      <c r="F32" s="266"/>
+      <c r="G32" s="266"/>
+      <c r="H32" s="267"/>
+      <c r="I32" s="271" t="s">
+        <v>300</v>
+      </c>
+      <c r="J32" s="274"/>
+      <c r="K32" s="275"/>
+    </row>
+    <row r="33" spans="2:11" ht="18" customHeight="1">
+      <c r="B33" s="269"/>
+      <c r="C33" s="265" t="s">
         <v>330</v>
       </c>
-      <c r="C32" s="264" t="s">
+      <c r="D33" s="266"/>
+      <c r="E33" s="266"/>
+      <c r="F33" s="266"/>
+      <c r="G33" s="266"/>
+      <c r="H33" s="267"/>
+      <c r="I33" s="272"/>
+      <c r="J33" s="276"/>
+      <c r="K33" s="277"/>
+    </row>
+    <row r="34" spans="2:11" ht="18" customHeight="1">
+      <c r="B34" s="270"/>
+      <c r="C34" s="265" t="s">
         <v>331</v>
       </c>
-      <c r="D32" s="265"/>
-      <c r="E32" s="265"/>
-      <c r="F32" s="265"/>
-      <c r="G32" s="265"/>
-      <c r="H32" s="266"/>
-      <c r="I32" s="270" t="s">
-        <v>302</v>
-      </c>
-      <c r="J32" s="273"/>
-      <c r="K32" s="274"/>
-    </row>
-    <row r="33" spans="2:11" ht="18" customHeight="1">
-      <c r="B33" s="268"/>
-      <c r="C33" s="264" t="s">
+      <c r="D34" s="266"/>
+      <c r="E34" s="266"/>
+      <c r="F34" s="266"/>
+      <c r="G34" s="266"/>
+      <c r="H34" s="267"/>
+      <c r="I34" s="273"/>
+      <c r="J34" s="278"/>
+      <c r="K34" s="279"/>
+    </row>
+    <row r="35" spans="2:11" ht="15.95" customHeight="1">
+      <c r="B35" s="265" t="s">
         <v>332</v>
       </c>
-      <c r="D33" s="265"/>
-      <c r="E33" s="265"/>
-      <c r="F33" s="265"/>
-      <c r="G33" s="265"/>
-      <c r="H33" s="266"/>
-      <c r="I33" s="271"/>
-      <c r="J33" s="275"/>
-      <c r="K33" s="276"/>
-    </row>
-    <row r="34" spans="2:11" ht="18" customHeight="1">
-      <c r="B34" s="269"/>
-      <c r="C34" s="264" t="s">
-        <v>333</v>
-      </c>
-      <c r="D34" s="265"/>
-      <c r="E34" s="265"/>
-      <c r="F34" s="265"/>
-      <c r="G34" s="265"/>
-      <c r="H34" s="266"/>
-      <c r="I34" s="272"/>
-      <c r="J34" s="277"/>
-      <c r="K34" s="278"/>
-    </row>
-    <row r="35" spans="2:11" ht="15.95" customHeight="1">
-      <c r="B35" s="264" t="s">
-        <v>334</v>
-      </c>
-      <c r="C35" s="265"/>
-      <c r="D35" s="265"/>
-      <c r="E35" s="265"/>
-      <c r="F35" s="265"/>
-      <c r="G35" s="265"/>
-      <c r="H35" s="265"/>
-      <c r="I35" s="265"/>
-      <c r="J35" s="265"/>
-      <c r="K35" s="266"/>
+      <c r="C35" s="266"/>
+      <c r="D35" s="266"/>
+      <c r="E35" s="266"/>
+      <c r="F35" s="266"/>
+      <c r="G35" s="266"/>
+      <c r="H35" s="266"/>
+      <c r="I35" s="266"/>
+      <c r="J35" s="266"/>
+      <c r="K35" s="267"/>
     </row>
     <row r="36" spans="2:11" ht="28.5" customHeight="1">
       <c r="B36" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="C36" s="264" t="s">
-        <v>336</v>
-      </c>
-      <c r="D36" s="265"/>
-      <c r="E36" s="265"/>
-      <c r="F36" s="265"/>
-      <c r="G36" s="265"/>
-      <c r="H36" s="266"/>
+        <v>333</v>
+      </c>
+      <c r="C36" s="265" t="s">
+        <v>334</v>
+      </c>
+      <c r="D36" s="266"/>
+      <c r="E36" s="266"/>
+      <c r="F36" s="266"/>
+      <c r="G36" s="266"/>
+      <c r="H36" s="267"/>
       <c r="I36" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="J36" s="264"/>
-      <c r="K36" s="266"/>
+        <v>300</v>
+      </c>
+      <c r="J36" s="265"/>
+      <c r="K36" s="267"/>
     </row>
     <row r="37" spans="2:11" ht="15.95" customHeight="1">
       <c r="B37" s="46" t="s">
-        <v>337</v>
-      </c>
-      <c r="C37" s="264" t="s">
-        <v>338</v>
-      </c>
-      <c r="D37" s="265"/>
-      <c r="E37" s="265"/>
-      <c r="F37" s="265"/>
-      <c r="G37" s="265"/>
-      <c r="H37" s="266"/>
+        <v>335</v>
+      </c>
+      <c r="C37" s="265" t="s">
+        <v>336</v>
+      </c>
+      <c r="D37" s="266"/>
+      <c r="E37" s="266"/>
+      <c r="F37" s="266"/>
+      <c r="G37" s="266"/>
+      <c r="H37" s="267"/>
       <c r="I37" s="45" t="s">
-        <v>304</v>
-      </c>
-      <c r="J37" s="264"/>
-      <c r="K37" s="266"/>
+        <v>302</v>
+      </c>
+      <c r="J37" s="265"/>
+      <c r="K37" s="267"/>
     </row>
     <row r="38" spans="2:11" ht="18" customHeight="1">
       <c r="B38" s="47" t="s">
+        <v>337</v>
+      </c>
+      <c r="C38" s="265" t="s">
+        <v>338</v>
+      </c>
+      <c r="D38" s="266"/>
+      <c r="E38" s="266"/>
+      <c r="F38" s="266"/>
+      <c r="G38" s="266"/>
+      <c r="H38" s="267"/>
+      <c r="I38" s="45" t="s">
+        <v>300</v>
+      </c>
+      <c r="J38" s="265"/>
+      <c r="K38" s="267"/>
+    </row>
+    <row r="39" spans="2:11" ht="15.95" customHeight="1">
+      <c r="B39" s="265" t="s">
         <v>339</v>
       </c>
-      <c r="C38" s="264" t="s">
-        <v>340</v>
-      </c>
-      <c r="D38" s="265"/>
-      <c r="E38" s="265"/>
-      <c r="F38" s="265"/>
-      <c r="G38" s="265"/>
-      <c r="H38" s="266"/>
-      <c r="I38" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="J38" s="264"/>
-      <c r="K38" s="266"/>
-    </row>
-    <row r="39" spans="2:11" ht="15.95" customHeight="1">
-      <c r="B39" s="264" t="s">
-        <v>341</v>
-      </c>
-      <c r="C39" s="265"/>
-      <c r="D39" s="265"/>
-      <c r="E39" s="265"/>
-      <c r="F39" s="265"/>
-      <c r="G39" s="265"/>
-      <c r="H39" s="265"/>
-      <c r="I39" s="265"/>
-      <c r="J39" s="265"/>
-      <c r="K39" s="266"/>
+      <c r="C39" s="266"/>
+      <c r="D39" s="266"/>
+      <c r="E39" s="266"/>
+      <c r="F39" s="266"/>
+      <c r="G39" s="266"/>
+      <c r="H39" s="266"/>
+      <c r="I39" s="266"/>
+      <c r="J39" s="266"/>
+      <c r="K39" s="267"/>
     </row>
     <row r="40" spans="2:11" ht="21" customHeight="1">
       <c r="B40" s="46" t="s">
-        <v>342</v>
-      </c>
-      <c r="C40" s="264" t="s">
-        <v>343</v>
-      </c>
-      <c r="D40" s="265"/>
-      <c r="E40" s="265"/>
-      <c r="F40" s="265"/>
-      <c r="G40" s="265"/>
-      <c r="H40" s="266"/>
+        <v>340</v>
+      </c>
+      <c r="C40" s="265" t="s">
+        <v>341</v>
+      </c>
+      <c r="D40" s="266"/>
+      <c r="E40" s="266"/>
+      <c r="F40" s="266"/>
+      <c r="G40" s="266"/>
+      <c r="H40" s="267"/>
       <c r="I40" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="J40" s="264"/>
-      <c r="K40" s="266"/>
+        <v>300</v>
+      </c>
+      <c r="J40" s="265"/>
+      <c r="K40" s="267"/>
     </row>
     <row r="41" spans="2:11" ht="28.5" customHeight="1">
       <c r="B41" s="46" t="s">
-        <v>344</v>
-      </c>
-      <c r="C41" s="264" t="s">
-        <v>345</v>
-      </c>
-      <c r="D41" s="265"/>
-      <c r="E41" s="265"/>
-      <c r="F41" s="265"/>
-      <c r="G41" s="265"/>
-      <c r="H41" s="266"/>
+        <v>342</v>
+      </c>
+      <c r="C41" s="265" t="s">
+        <v>343</v>
+      </c>
+      <c r="D41" s="266"/>
+      <c r="E41" s="266"/>
+      <c r="F41" s="266"/>
+      <c r="G41" s="266"/>
+      <c r="H41" s="267"/>
       <c r="I41" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="J41" s="264"/>
-      <c r="K41" s="266"/>
+        <v>300</v>
+      </c>
+      <c r="J41" s="265"/>
+      <c r="K41" s="267"/>
     </row>
     <row r="42" spans="2:11" ht="18.95" customHeight="1">
       <c r="B42" s="46" t="s">
-        <v>346</v>
-      </c>
-      <c r="C42" s="264" t="s">
-        <v>347</v>
-      </c>
-      <c r="D42" s="265"/>
-      <c r="E42" s="265"/>
-      <c r="F42" s="265"/>
-      <c r="G42" s="265"/>
-      <c r="H42" s="266"/>
+        <v>344</v>
+      </c>
+      <c r="C42" s="265" t="s">
+        <v>345</v>
+      </c>
+      <c r="D42" s="266"/>
+      <c r="E42" s="266"/>
+      <c r="F42" s="266"/>
+      <c r="G42" s="266"/>
+      <c r="H42" s="267"/>
       <c r="I42" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="J42" s="264"/>
-      <c r="K42" s="266"/>
+        <v>300</v>
+      </c>
+      <c r="J42" s="265"/>
+      <c r="K42" s="267"/>
     </row>
     <row r="43" spans="2:11" ht="28.5" customHeight="1">
       <c r="B43" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="C43" s="265" t="s">
+        <v>347</v>
+      </c>
+      <c r="D43" s="266"/>
+      <c r="E43" s="266"/>
+      <c r="F43" s="266"/>
+      <c r="G43" s="266"/>
+      <c r="H43" s="267"/>
+      <c r="I43" s="45" t="s">
+        <v>300</v>
+      </c>
+      <c r="J43" s="265"/>
+      <c r="K43" s="267"/>
+    </row>
+    <row r="44" spans="2:11" ht="50.1" customHeight="1">
+      <c r="B44" s="265" t="s">
         <v>348</v>
       </c>
-      <c r="C43" s="264" t="s">
-        <v>349</v>
-      </c>
-      <c r="D43" s="265"/>
-      <c r="E43" s="265"/>
-      <c r="F43" s="265"/>
-      <c r="G43" s="265"/>
-      <c r="H43" s="266"/>
-      <c r="I43" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="J43" s="264"/>
-      <c r="K43" s="266"/>
-    </row>
-    <row r="44" spans="2:11" ht="50.1" customHeight="1">
-      <c r="B44" s="264" t="s">
-        <v>350</v>
-      </c>
-      <c r="C44" s="265"/>
-      <c r="D44" s="265"/>
-      <c r="E44" s="265"/>
-      <c r="F44" s="265"/>
-      <c r="G44" s="265"/>
-      <c r="H44" s="265"/>
-      <c r="I44" s="265"/>
-      <c r="J44" s="265"/>
-      <c r="K44" s="266"/>
+      <c r="C44" s="266"/>
+      <c r="D44" s="266"/>
+      <c r="E44" s="266"/>
+      <c r="F44" s="266"/>
+      <c r="G44" s="266"/>
+      <c r="H44" s="266"/>
+      <c r="I44" s="266"/>
+      <c r="J44" s="266"/>
+      <c r="K44" s="267"/>
     </row>
     <row r="45" spans="2:11">
       <c r="B45" s="43"/>

--- a/public/01.계약서.xlsx
+++ b/public/01.계약서.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eBroAgent\drive_mirror\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\01.AntiGravity\eBro\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79AC892-0BB1-47C6-99EF-64B118ED7EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9FE7B7-2068-44D9-A810-38E1DAA96C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9E72163E-9728-43C2-B59D-2067775552E8}"/>
   </bookViews>
@@ -2986,11 +2986,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>(수량) / {단위}</t>
+    <t>{단가}</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>{단가}</t>
+    <t>(수량)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -5559,6 +5559,57 @@
     <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="93" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="26" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="53" fillId="0" borderId="93" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="53" fillId="0" borderId="94" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="53" fillId="0" borderId="26" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="99" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5577,60 +5628,570 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="104" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="52" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="27" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="43" fillId="45" borderId="44" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="43" fillId="45" borderId="27" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="76" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="40" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="42" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="72" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="47" borderId="93" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="73" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="47" borderId="26" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="64" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="53" fillId="0" borderId="93" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="81" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="53" fillId="0" borderId="94" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="65" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="53" fillId="0" borderId="26" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="77" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="78" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="82" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="81" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="79" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="80" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="83" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="68" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="69" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="70" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="71" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="8" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="72" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="73" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="64" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="65" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="74" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="75" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="66" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="35" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="49" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="50" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="43" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="60" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="54" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="48" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="41" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="51" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="27" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="47" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="46" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="49" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="50" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="46" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="46" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="44" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="45" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="46" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="61" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="53" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="44" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="46" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="62" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="63" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="66" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="35" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="67" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="60" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="54" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="43" fillId="45" borderId="44" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="43" fillId="45" borderId="27" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="0" xfId="166" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="38" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="46" fillId="45" borderId="54" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="46" fillId="45" borderId="56" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="46" fillId="45" borderId="53" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="55" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="57" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="59" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="54" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="56" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="53" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="45" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="48" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="30" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="45" borderId="22" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="47" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="30" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="50" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="38" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="43" fillId="45" borderId="39" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="43" fillId="45" borderId="40" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="43" fillId="45" borderId="41" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="43" fillId="45" borderId="39" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="43" fillId="45" borderId="40" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="43" fillId="45" borderId="42" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="23" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="25" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="31" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="32" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="36" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="37" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="44" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="45" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="46" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="42" fillId="45" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="11" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="12" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="21" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="28" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="29" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="24" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="5" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="5" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="5" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="6" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="7" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="4" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="4" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="4" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="9" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="9" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="9" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="9" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="9" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="9" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="4" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="10" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="10" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="11" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="176" fontId="7" fillId="4" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -5646,566 +6207,23 @@
     <xf numFmtId="0" fontId="7" fillId="44" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="10" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="10" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="11" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="2" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="2" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="5" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="5" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="5" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="7" fillId="6" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="7" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="9" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="9" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="9" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="9" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="9" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="9" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="42" fillId="45" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="11" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="12" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="21" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="28" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="29" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="52" fillId="0" borderId="93" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="23" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="24" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="25" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="38" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="43" fillId="45" borderId="39" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="43" fillId="45" borderId="40" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="43" fillId="45" borderId="41" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="43" fillId="45" borderId="39" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="43" fillId="45" borderId="40" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="43" fillId="45" borderId="42" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="31" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="32" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="36" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="37" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="44" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="45" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="46" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="45" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="48" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="30" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="43" fillId="45" borderId="22" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="47" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="30" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="50" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="43" fillId="45" borderId="44" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="43" fillId="45" borderId="27" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="43" fillId="45" borderId="44" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="43" fillId="45" borderId="27" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="52" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="27" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="0" xfId="166" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="38" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="46" fillId="45" borderId="54" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="46" fillId="45" borderId="56" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="46" fillId="45" borderId="53" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="55" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="57" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="59" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="54" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="56" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="53" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="60" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="54" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="44" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="45" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="46" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="43" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="60" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="54" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="48" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="41" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="51" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="27" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="47" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="46" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="49" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="50" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="46" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="46" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="61" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="53" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="44" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="46" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="62" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="63" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="64" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="65" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="66" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="35" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="67" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="76" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="40" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="42" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="72" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="73" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="64" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="81" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="65" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="77" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="78" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="82" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="81" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="79" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="80" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="83" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="68" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="69" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="70" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="71" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="8" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="72" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="73" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="10" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="74" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="75" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="66" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="35" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="49" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="50" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -6216,6 +6234,9 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="94" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6228,50 +6249,29 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="99" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="101" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="102" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="104" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="99" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="101" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="105" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="106" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="102" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="104" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="52" fillId="0" borderId="93" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="47" borderId="94" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="172">
@@ -7259,231 +7259,231 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="226" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
+      <c r="B1" s="226"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
       <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="226" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="77"/>
+      <c r="B2" s="226"/>
+      <c r="C2" s="261"/>
+      <c r="D2" s="262"/>
+      <c r="E2" s="262"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="263"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="264"/>
       <c r="P2" s="2"/>
     </row>
     <row r="3" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="226" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="83"/>
+      <c r="B3" s="226"/>
+      <c r="C3" s="248"/>
+      <c r="D3" s="248"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="250"/>
+      <c r="G3" s="250"/>
+      <c r="H3" s="251"/>
+      <c r="I3" s="251"/>
+      <c r="J3" s="252"/>
+      <c r="K3" s="253"/>
       <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="83"/>
+      <c r="B4" s="226"/>
+      <c r="C4" s="248"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="250"/>
+      <c r="G4" s="250"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="253"/>
       <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="89"/>
+      <c r="B5" s="226"/>
+      <c r="C5" s="254"/>
+      <c r="D5" s="254"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="256"/>
+      <c r="G5" s="256"/>
+      <c r="H5" s="257"/>
+      <c r="I5" s="257"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="259"/>
       <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="196" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="100"/>
-      <c r="I6" s="100"/>
-      <c r="J6" s="100"/>
-      <c r="K6" s="101"/>
+      <c r="B6" s="197"/>
+      <c r="C6" s="237"/>
+      <c r="D6" s="238"/>
+      <c r="E6" s="238"/>
+      <c r="F6" s="238"/>
+      <c r="G6" s="238"/>
+      <c r="H6" s="238"/>
+      <c r="I6" s="238"/>
+      <c r="J6" s="238"/>
+      <c r="K6" s="239"/>
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A7" s="72" t="s">
+      <c r="A7" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="72"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="240"/>
+      <c r="D7" s="240"/>
+      <c r="E7" s="240"/>
+      <c r="F7" s="240"/>
+      <c r="G7" s="240"/>
+      <c r="H7" s="240"/>
+      <c r="I7" s="240"/>
+      <c r="J7" s="240"/>
+      <c r="K7" s="240"/>
       <c r="P7" s="2"/>
     </row>
     <row r="8" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A8" s="90" t="s">
+      <c r="A8" s="230" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="92"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="93"/>
-      <c r="K8" s="94"/>
+      <c r="C8" s="232"/>
+      <c r="D8" s="233"/>
+      <c r="E8" s="233"/>
+      <c r="F8" s="233"/>
+      <c r="G8" s="233"/>
+      <c r="H8" s="233"/>
+      <c r="I8" s="233"/>
+      <c r="J8" s="233"/>
+      <c r="K8" s="234"/>
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A9" s="103"/>
+      <c r="A9" s="241"/>
       <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="93"/>
-      <c r="K9" s="94"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="233"/>
+      <c r="E9" s="233"/>
+      <c r="F9" s="233"/>
+      <c r="G9" s="233"/>
+      <c r="H9" s="233"/>
+      <c r="I9" s="233"/>
+      <c r="J9" s="233"/>
+      <c r="K9" s="234"/>
       <c r="P9" s="2"/>
     </row>
     <row r="10" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A10" s="103"/>
+      <c r="A10" s="241"/>
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="104"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="106"/>
+      <c r="C10" s="242"/>
+      <c r="D10" s="243"/>
+      <c r="E10" s="243"/>
+      <c r="F10" s="243"/>
+      <c r="G10" s="243"/>
+      <c r="H10" s="243"/>
+      <c r="I10" s="243"/>
+      <c r="J10" s="243"/>
+      <c r="K10" s="244"/>
       <c r="P10" s="2"/>
     </row>
     <row r="11" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A11" s="91"/>
+      <c r="A11" s="231"/>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="107"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="109"/>
+      <c r="C11" s="245"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
+      <c r="I11" s="246"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="247"/>
       <c r="P11" s="2"/>
     </row>
     <row r="12" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A12" s="90" t="s">
+      <c r="A12" s="230" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="92"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="94"/>
+      <c r="C12" s="232"/>
+      <c r="D12" s="233"/>
+      <c r="E12" s="233"/>
+      <c r="F12" s="233"/>
+      <c r="G12" s="233"/>
+      <c r="H12" s="233"/>
+      <c r="I12" s="233"/>
+      <c r="J12" s="233"/>
+      <c r="K12" s="234"/>
       <c r="P12" s="2"/>
     </row>
     <row r="13" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A13" s="91"/>
+      <c r="A13" s="231"/>
       <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="92"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="93"/>
-      <c r="K13" s="94"/>
+      <c r="C13" s="232"/>
+      <c r="D13" s="233"/>
+      <c r="E13" s="233"/>
+      <c r="F13" s="233"/>
+      <c r="G13" s="233"/>
+      <c r="H13" s="233"/>
+      <c r="I13" s="233"/>
+      <c r="J13" s="233"/>
+      <c r="K13" s="234"/>
       <c r="P13" s="2"/>
     </row>
     <row r="14" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A14" s="72" t="s">
+      <c r="A14" s="226" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="72"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="95"/>
-      <c r="K14" s="95"/>
+      <c r="B14" s="226"/>
+      <c r="C14" s="235"/>
+      <c r="D14" s="235"/>
+      <c r="E14" s="235"/>
+      <c r="F14" s="235"/>
+      <c r="G14" s="235"/>
+      <c r="H14" s="235"/>
+      <c r="I14" s="235"/>
+      <c r="J14" s="235"/>
+      <c r="K14" s="235"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
@@ -7493,19 +7493,19 @@
       <c r="R14" s="4"/>
     </row>
     <row r="15" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A15" s="72" t="s">
+      <c r="A15" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="96"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
+      <c r="B15" s="226"/>
+      <c r="C15" s="236"/>
+      <c r="D15" s="236"/>
+      <c r="E15" s="236"/>
+      <c r="F15" s="236"/>
+      <c r="G15" s="236"/>
+      <c r="H15" s="236"/>
+      <c r="I15" s="236"/>
+      <c r="J15" s="236"/>
+      <c r="K15" s="236"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -7515,19 +7515,19 @@
       <c r="R15" s="4"/>
     </row>
     <row r="16" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A16" s="72" t="s">
+      <c r="A16" s="226" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="72"/>
-      <c r="C16" s="113"/>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="113"/>
-      <c r="G16" s="113"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="113"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="113"/>
+      <c r="B16" s="226"/>
+      <c r="C16" s="223"/>
+      <c r="D16" s="223"/>
+      <c r="E16" s="223"/>
+      <c r="F16" s="223"/>
+      <c r="G16" s="223"/>
+      <c r="H16" s="223"/>
+      <c r="I16" s="223"/>
+      <c r="J16" s="223"/>
+      <c r="K16" s="223"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -7537,123 +7537,123 @@
       <c r="R16" s="4"/>
     </row>
     <row r="17" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A17" s="97" t="s">
+      <c r="A17" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="113" t="s">
+      <c r="B17" s="197"/>
+      <c r="C17" s="223" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="113"/>
-      <c r="G17" s="113"/>
-      <c r="H17" s="113"/>
-      <c r="I17" s="113"/>
-      <c r="J17" s="113"/>
-      <c r="K17" s="113"/>
+      <c r="D17" s="223"/>
+      <c r="E17" s="223"/>
+      <c r="F17" s="223"/>
+      <c r="G17" s="223"/>
+      <c r="H17" s="223"/>
+      <c r="I17" s="223"/>
+      <c r="J17" s="223"/>
+      <c r="K17" s="223"/>
     </row>
     <row r="18" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A18" s="97"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="119" t="s">
+      <c r="A18" s="196"/>
+      <c r="B18" s="197"/>
+      <c r="C18" s="227" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="120"/>
-      <c r="E18" s="120"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="120"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="120"/>
-      <c r="J18" s="120"/>
-      <c r="K18" s="121"/>
+      <c r="D18" s="228"/>
+      <c r="E18" s="228"/>
+      <c r="F18" s="228"/>
+      <c r="G18" s="228"/>
+      <c r="H18" s="228"/>
+      <c r="I18" s="228"/>
+      <c r="J18" s="228"/>
+      <c r="K18" s="229"/>
     </row>
     <row r="19" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="220" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="111"/>
-      <c r="C19" s="112" t="s">
+      <c r="B19" s="221"/>
+      <c r="C19" s="222" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="112"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
+      <c r="D19" s="222"/>
+      <c r="E19" s="222"/>
+      <c r="F19" s="222"/>
+      <c r="G19" s="222"/>
+      <c r="H19" s="222"/>
+      <c r="I19" s="222"/>
+      <c r="J19" s="222"/>
+      <c r="K19" s="222"/>
     </row>
     <row r="20" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="220" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="111"/>
-      <c r="C20" s="112" t="s">
+      <c r="B20" s="221"/>
+      <c r="C20" s="222" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="112"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="112"/>
-      <c r="G20" s="112"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="112"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="112"/>
+      <c r="D20" s="222"/>
+      <c r="E20" s="222"/>
+      <c r="F20" s="222"/>
+      <c r="G20" s="222"/>
+      <c r="H20" s="222"/>
+      <c r="I20" s="222"/>
+      <c r="J20" s="222"/>
+      <c r="K20" s="222"/>
     </row>
     <row r="21" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="220" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="111"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="113"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="113"/>
+      <c r="B21" s="221"/>
+      <c r="C21" s="223"/>
+      <c r="D21" s="223"/>
+      <c r="E21" s="223"/>
+      <c r="F21" s="223"/>
+      <c r="G21" s="223"/>
+      <c r="H21" s="223"/>
+      <c r="I21" s="223"/>
+      <c r="J21" s="223"/>
+      <c r="K21" s="223"/>
     </row>
     <row r="22" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A22" s="97" t="s">
+      <c r="A22" s="196" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="114" t="s">
+      <c r="B22" s="197"/>
+      <c r="C22" s="224" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="115"/>
-      <c r="E22" s="116" t="s">
+      <c r="D22" s="225"/>
+      <c r="E22" s="200" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="117"/>
-      <c r="G22" s="117"/>
-      <c r="H22" s="117"/>
-      <c r="I22" s="117"/>
-      <c r="J22" s="117"/>
-      <c r="K22" s="118"/>
+      <c r="F22" s="201"/>
+      <c r="G22" s="201"/>
+      <c r="H22" s="201"/>
+      <c r="I22" s="201"/>
+      <c r="J22" s="201"/>
+      <c r="K22" s="202"/>
     </row>
     <row r="23" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A23" s="97" t="s">
+      <c r="A23" s="196" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="122" t="s">
+      <c r="B23" s="197"/>
+      <c r="C23" s="198" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="123"/>
-      <c r="E23" s="116" t="s">
+      <c r="D23" s="199"/>
+      <c r="E23" s="200" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="117"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="117"/>
-      <c r="I23" s="117"/>
-      <c r="J23" s="117"/>
-      <c r="K23" s="118"/>
+      <c r="F23" s="201"/>
+      <c r="G23" s="201"/>
+      <c r="H23" s="201"/>
+      <c r="I23" s="201"/>
+      <c r="J23" s="201"/>
+      <c r="K23" s="202"/>
     </row>
     <row r="24" spans="1:16" ht="12" customHeight="1">
       <c r="P24" s="5"/>
@@ -7662,32 +7662,32 @@
       <c r="P25" s="5"/>
     </row>
     <row r="26" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="124" t="s">
+      <c r="A26" s="203" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="124"/>
-      <c r="C26" s="124"/>
-      <c r="D26" s="124"/>
-      <c r="E26" s="124"/>
-      <c r="F26" s="124"/>
-      <c r="G26" s="124"/>
-      <c r="H26" s="124"/>
-      <c r="I26" s="124"/>
-      <c r="J26" s="124"/>
-      <c r="K26" s="124"/>
+      <c r="B26" s="203"/>
+      <c r="C26" s="203"/>
+      <c r="D26" s="203"/>
+      <c r="E26" s="203"/>
+      <c r="F26" s="203"/>
+      <c r="G26" s="203"/>
+      <c r="H26" s="203"/>
+      <c r="I26" s="203"/>
+      <c r="J26" s="203"/>
+      <c r="K26" s="203"/>
     </row>
     <row r="27" spans="1:16" s="6" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A27" s="124"/>
-      <c r="B27" s="124"/>
-      <c r="C27" s="124"/>
-      <c r="D27" s="124"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="124"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="124"/>
-      <c r="I27" s="124"/>
-      <c r="J27" s="124"/>
-      <c r="K27" s="124"/>
+      <c r="A27" s="203"/>
+      <c r="B27" s="203"/>
+      <c r="C27" s="203"/>
+      <c r="D27" s="203"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="203"/>
+      <c r="G27" s="203"/>
+      <c r="H27" s="203"/>
+      <c r="I27" s="203"/>
+      <c r="J27" s="203"/>
+      <c r="K27" s="203"/>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
@@ -7695,19 +7695,19 @@
       <c r="P27" s="7"/>
     </row>
     <row r="28" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A28" s="125" t="s">
+      <c r="A28" s="204" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="125"/>
-      <c r="C28" s="125"/>
-      <c r="D28" s="125"/>
-      <c r="E28" s="125"/>
-      <c r="F28" s="125"/>
-      <c r="G28" s="125"/>
-      <c r="H28" s="125"/>
-      <c r="I28" s="125"/>
-      <c r="J28" s="125"/>
-      <c r="K28" s="125"/>
+      <c r="B28" s="204"/>
+      <c r="C28" s="204"/>
+      <c r="D28" s="204"/>
+      <c r="E28" s="204"/>
+      <c r="F28" s="204"/>
+      <c r="G28" s="204"/>
+      <c r="H28" s="204"/>
+      <c r="I28" s="204"/>
+      <c r="J28" s="204"/>
+      <c r="K28" s="204"/>
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
@@ -7733,29 +7733,29 @@
       <c r="P29" s="7"/>
     </row>
     <row r="30" spans="1:16" s="6" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A30" s="126" t="s">
+      <c r="A30" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="127"/>
+      <c r="B30" s="206"/>
       <c r="C30" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="132" t="s">
+      <c r="D30" s="211" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="133"/>
-      <c r="F30" s="134"/>
-      <c r="G30" s="135" t="s">
+      <c r="E30" s="212"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="214" t="s">
         <v>29</v>
       </c>
-      <c r="H30" s="127"/>
+      <c r="H30" s="206"/>
       <c r="I30" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="J30" s="138" t="s">
+      <c r="J30" s="217" t="s">
         <v>79</v>
       </c>
-      <c r="K30" s="139"/>
+      <c r="K30" s="218"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
@@ -7763,93 +7763,93 @@
       <c r="P30" s="7"/>
     </row>
     <row r="31" spans="1:16" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A31" s="128"/>
-      <c r="B31" s="129"/>
+      <c r="A31" s="207"/>
+      <c r="B31" s="208"/>
       <c r="C31" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="D31" s="140" t="s">
+      <c r="D31" s="183" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="141"/>
-      <c r="F31" s="142"/>
-      <c r="G31" s="136"/>
-      <c r="H31" s="129"/>
+      <c r="E31" s="219"/>
+      <c r="F31" s="184"/>
+      <c r="G31" s="215"/>
+      <c r="H31" s="208"/>
       <c r="I31" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="J31" s="140" t="s">
+      <c r="J31" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="K31" s="142"/>
+      <c r="K31" s="184"/>
       <c r="P31" s="8"/>
     </row>
     <row r="32" spans="1:16" s="6" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A32" s="130"/>
-      <c r="B32" s="131"/>
+      <c r="A32" s="209"/>
+      <c r="B32" s="210"/>
       <c r="C32" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="153" t="s">
+      <c r="D32" s="185" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="154"/>
-      <c r="F32" s="155"/>
-      <c r="G32" s="137"/>
-      <c r="H32" s="131"/>
+      <c r="E32" s="186"/>
+      <c r="F32" s="187"/>
+      <c r="G32" s="216"/>
+      <c r="H32" s="210"/>
       <c r="I32" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="J32" s="156" t="s">
+      <c r="J32" s="188" t="s">
         <v>81</v>
       </c>
-      <c r="K32" s="157"/>
+      <c r="K32" s="189"/>
       <c r="P32" s="8"/>
     </row>
     <row r="33" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A33" s="158" t="s">
+      <c r="A33" s="190" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="158"/>
-      <c r="C33" s="159"/>
-      <c r="D33" s="159"/>
-      <c r="E33" s="159"/>
-      <c r="F33" s="159"/>
-      <c r="G33" s="159"/>
-      <c r="H33" s="159"/>
-      <c r="I33" s="159"/>
-      <c r="J33" s="159"/>
-      <c r="K33" s="159"/>
+      <c r="B33" s="190"/>
+      <c r="C33" s="191"/>
+      <c r="D33" s="191"/>
+      <c r="E33" s="191"/>
+      <c r="F33" s="191"/>
+      <c r="G33" s="191"/>
+      <c r="H33" s="191"/>
+      <c r="I33" s="191"/>
+      <c r="J33" s="191"/>
+      <c r="K33" s="191"/>
       <c r="P33" s="8"/>
     </row>
     <row r="34" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1">
-      <c r="A34" s="160"/>
-      <c r="B34" s="160"/>
-      <c r="C34" s="160"/>
-      <c r="D34" s="160"/>
-      <c r="E34" s="160"/>
-      <c r="F34" s="160"/>
-      <c r="G34" s="160"/>
-      <c r="H34" s="160"/>
-      <c r="I34" s="160"/>
-      <c r="J34" s="160"/>
-      <c r="K34" s="160"/>
+      <c r="A34" s="94"/>
+      <c r="B34" s="94"/>
+      <c r="C34" s="94"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="94"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="94"/>
+      <c r="J34" s="94"/>
+      <c r="K34" s="94"/>
       <c r="P34" s="8"/>
     </row>
     <row r="35" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A35" s="161" t="s">
+      <c r="A35" s="192" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="161"/>
-      <c r="C35" s="161"/>
-      <c r="D35" s="161"/>
-      <c r="E35" s="161"/>
-      <c r="F35" s="161"/>
-      <c r="G35" s="161"/>
-      <c r="H35" s="161"/>
-      <c r="I35" s="161"/>
-      <c r="J35" s="161"/>
-      <c r="K35" s="161"/>
+      <c r="B35" s="192"/>
+      <c r="C35" s="192"/>
+      <c r="D35" s="192"/>
+      <c r="E35" s="192"/>
+      <c r="F35" s="192"/>
+      <c r="G35" s="192"/>
+      <c r="H35" s="192"/>
+      <c r="I35" s="192"/>
+      <c r="J35" s="192"/>
+      <c r="K35" s="192"/>
       <c r="P35" s="8"/>
     </row>
     <row r="36" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
@@ -7867,61 +7867,61 @@
       <c r="P36" s="8"/>
     </row>
     <row r="37" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A37" s="143" t="s">
+      <c r="A37" s="176" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="144"/>
-      <c r="C37" s="145" t="s">
+      <c r="B37" s="156"/>
+      <c r="C37" s="177" t="s">
         <v>82</v>
       </c>
-      <c r="D37" s="146"/>
-      <c r="E37" s="146"/>
-      <c r="F37" s="146"/>
-      <c r="G37" s="145" t="s">
+      <c r="D37" s="178"/>
+      <c r="E37" s="178"/>
+      <c r="F37" s="178"/>
+      <c r="G37" s="177" t="s">
         <v>69</v>
       </c>
-      <c r="H37" s="147"/>
-      <c r="I37" s="148" t="s">
+      <c r="H37" s="179"/>
+      <c r="I37" s="180" t="s">
         <v>92</v>
       </c>
-      <c r="J37" s="149"/>
-      <c r="K37" s="150"/>
+      <c r="J37" s="181"/>
+      <c r="K37" s="182"/>
     </row>
     <row r="38" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A38" s="151" t="s">
+      <c r="A38" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="152"/>
-      <c r="C38" s="162" t="s">
+      <c r="B38" s="167"/>
+      <c r="C38" s="193" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="163"/>
-      <c r="E38" s="163"/>
-      <c r="F38" s="163"/>
-      <c r="G38" s="163"/>
-      <c r="H38" s="163"/>
-      <c r="I38" s="163"/>
-      <c r="J38" s="163"/>
-      <c r="K38" s="164"/>
+      <c r="D38" s="194"/>
+      <c r="E38" s="194"/>
+      <c r="F38" s="194"/>
+      <c r="G38" s="194"/>
+      <c r="H38" s="194"/>
+      <c r="I38" s="194"/>
+      <c r="J38" s="194"/>
+      <c r="K38" s="195"/>
       <c r="M38" s="12"/>
     </row>
     <row r="39" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A39" s="165" t="s">
+      <c r="A39" s="166" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="152"/>
+      <c r="B39" s="167"/>
       <c r="C39" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="168" t="s">
+      <c r="D39" s="171" t="s">
         <v>80</v>
       </c>
-      <c r="E39" s="168"/>
-      <c r="F39" s="168"/>
-      <c r="G39" s="168" t="s">
+      <c r="E39" s="171"/>
+      <c r="F39" s="171"/>
+      <c r="G39" s="171" t="s">
         <v>10</v>
       </c>
-      <c r="H39" s="168"/>
+      <c r="H39" s="171"/>
       <c r="I39" s="25"/>
       <c r="J39" s="26" t="s">
         <v>32</v>
@@ -7931,75 +7931,75 @@
       <c r="N39" s="11"/>
     </row>
     <row r="40" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A40" s="151"/>
-      <c r="B40" s="152"/>
+      <c r="A40" s="168"/>
+      <c r="B40" s="167"/>
       <c r="C40" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D40" s="169"/>
-      <c r="E40" s="169"/>
-      <c r="F40" s="169"/>
-      <c r="G40" s="168" t="s">
+      <c r="D40" s="172"/>
+      <c r="E40" s="172"/>
+      <c r="F40" s="172"/>
+      <c r="G40" s="171" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="168"/>
-      <c r="I40" s="168"/>
-      <c r="J40" s="168"/>
-      <c r="K40" s="170"/>
+      <c r="H40" s="171"/>
+      <c r="I40" s="171"/>
+      <c r="J40" s="171"/>
+      <c r="K40" s="173"/>
     </row>
     <row r="41" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A41" s="166"/>
-      <c r="B41" s="167"/>
+      <c r="A41" s="169"/>
+      <c r="B41" s="170"/>
       <c r="C41" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="171" t="s">
+      <c r="D41" s="174" t="s">
         <v>85</v>
       </c>
-      <c r="E41" s="171"/>
-      <c r="F41" s="171"/>
-      <c r="G41" s="171" t="s">
+      <c r="E41" s="174"/>
+      <c r="F41" s="174"/>
+      <c r="G41" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="H41" s="171"/>
-      <c r="I41" s="171" t="s">
+      <c r="H41" s="174"/>
+      <c r="I41" s="174" t="s">
         <v>86</v>
       </c>
-      <c r="J41" s="171"/>
-      <c r="K41" s="172"/>
+      <c r="J41" s="174"/>
+      <c r="K41" s="175"/>
     </row>
     <row r="42" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A42" s="179"/>
-      <c r="B42" s="179"/>
-      <c r="C42" s="179"/>
-      <c r="D42" s="179"/>
-      <c r="E42" s="179"/>
-      <c r="F42" s="179"/>
-      <c r="G42" s="179"/>
-      <c r="H42" s="179"/>
-      <c r="I42" s="179"/>
-      <c r="J42" s="179"/>
-      <c r="K42" s="179"/>
+      <c r="A42" s="153"/>
+      <c r="B42" s="153"/>
+      <c r="C42" s="153"/>
+      <c r="D42" s="153"/>
+      <c r="E42" s="153"/>
+      <c r="F42" s="153"/>
+      <c r="G42" s="153"/>
+      <c r="H42" s="153"/>
+      <c r="I42" s="153"/>
+      <c r="J42" s="153"/>
+      <c r="K42" s="153"/>
     </row>
     <row r="43" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A43" s="180" t="s">
+      <c r="A43" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="181"/>
+      <c r="B43" s="155"/>
       <c r="C43" s="29" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="48" t="s">
         <v>364</v>
       </c>
-      <c r="E43" s="181" t="s">
+      <c r="E43" s="155" t="s">
         <v>61</v>
       </c>
-      <c r="F43" s="144"/>
-      <c r="G43" s="144" t="s">
+      <c r="F43" s="156"/>
+      <c r="G43" s="156" t="s">
         <v>37</v>
       </c>
-      <c r="H43" s="144"/>
+      <c r="H43" s="156"/>
       <c r="I43" s="30" t="s">
         <v>74</v>
       </c>
@@ -8012,487 +8012,487 @@
       <c r="P43" s="8"/>
     </row>
     <row r="44" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A44" s="177" t="s">
+      <c r="A44" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="178"/>
+      <c r="B44" s="73"/>
       <c r="C44" s="26" t="s">
         <v>88</v>
       </c>
       <c r="D44" s="32" t="s">
         <v>363</v>
       </c>
-      <c r="E44" s="173" t="s">
+      <c r="E44" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="F44" s="174"/>
-      <c r="G44" s="175" t="s">
+      <c r="F44" s="75"/>
+      <c r="G44" s="151" t="s">
         <v>91</v>
       </c>
-      <c r="H44" s="176"/>
-      <c r="I44" s="188" t="s">
+      <c r="H44" s="152"/>
+      <c r="I44" s="163" t="s">
         <v>73</v>
       </c>
-      <c r="J44" s="182" t="s">
+      <c r="J44" s="157" t="s">
         <v>90</v>
       </c>
-      <c r="K44" s="185" t="s">
+      <c r="K44" s="160" t="s">
         <v>40</v>
       </c>
       <c r="P44" s="8"/>
     </row>
     <row r="45" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A45" s="177" t="s">
+      <c r="A45" s="72" t="s">
         <v>365</v>
       </c>
-      <c r="B45" s="178"/>
+      <c r="B45" s="73"/>
       <c r="C45" s="26" t="s">
+        <v>367</v>
+      </c>
+      <c r="D45" s="32"/>
+      <c r="E45" s="74" t="s">
         <v>366</v>
       </c>
-      <c r="D45" s="32"/>
-      <c r="E45" s="173" t="s">
-        <v>367</v>
-      </c>
-      <c r="F45" s="174"/>
-      <c r="G45" s="175" t="s">
+      <c r="F45" s="75"/>
+      <c r="G45" s="151" t="s">
         <v>91</v>
       </c>
-      <c r="H45" s="176"/>
-      <c r="I45" s="189"/>
-      <c r="J45" s="183"/>
-      <c r="K45" s="186"/>
+      <c r="H45" s="152"/>
+      <c r="I45" s="164"/>
+      <c r="J45" s="158"/>
+      <c r="K45" s="161"/>
       <c r="P45" s="8"/>
     </row>
     <row r="46" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A46" s="177"/>
-      <c r="B46" s="178"/>
+      <c r="A46" s="72"/>
+      <c r="B46" s="73"/>
       <c r="C46" s="26"/>
       <c r="D46" s="32"/>
-      <c r="E46" s="173"/>
-      <c r="F46" s="174"/>
-      <c r="G46" s="175"/>
-      <c r="H46" s="176"/>
-      <c r="I46" s="189"/>
-      <c r="J46" s="183"/>
-      <c r="K46" s="186"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="75"/>
+      <c r="G46" s="151"/>
+      <c r="H46" s="152"/>
+      <c r="I46" s="164"/>
+      <c r="J46" s="158"/>
+      <c r="K46" s="161"/>
       <c r="P46" s="8"/>
     </row>
     <row r="47" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A47" s="177"/>
-      <c r="B47" s="178"/>
+      <c r="A47" s="72"/>
+      <c r="B47" s="73"/>
       <c r="C47" s="26"/>
       <c r="D47" s="32"/>
-      <c r="E47" s="173"/>
-      <c r="F47" s="174"/>
-      <c r="G47" s="175"/>
-      <c r="H47" s="176"/>
-      <c r="I47" s="189"/>
-      <c r="J47" s="183"/>
-      <c r="K47" s="186"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="75"/>
+      <c r="G47" s="151"/>
+      <c r="H47" s="152"/>
+      <c r="I47" s="164"/>
+      <c r="J47" s="158"/>
+      <c r="K47" s="161"/>
       <c r="P47" s="8"/>
     </row>
     <row r="48" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A48" s="177"/>
-      <c r="B48" s="178"/>
+      <c r="A48" s="72"/>
+      <c r="B48" s="73"/>
       <c r="C48" s="26"/>
       <c r="D48" s="32"/>
-      <c r="E48" s="173"/>
-      <c r="F48" s="174"/>
-      <c r="G48" s="175"/>
-      <c r="H48" s="176"/>
-      <c r="I48" s="189"/>
-      <c r="J48" s="183"/>
-      <c r="K48" s="186"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="151"/>
+      <c r="H48" s="152"/>
+      <c r="I48" s="164"/>
+      <c r="J48" s="158"/>
+      <c r="K48" s="161"/>
       <c r="P48" s="8"/>
     </row>
     <row r="49" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A49" s="177"/>
-      <c r="B49" s="178"/>
+      <c r="A49" s="72"/>
+      <c r="B49" s="73"/>
       <c r="C49" s="26"/>
       <c r="D49" s="32"/>
-      <c r="E49" s="173"/>
-      <c r="F49" s="174"/>
-      <c r="G49" s="175"/>
-      <c r="H49" s="176"/>
-      <c r="I49" s="189"/>
-      <c r="J49" s="183"/>
-      <c r="K49" s="186"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="75"/>
+      <c r="G49" s="151"/>
+      <c r="H49" s="152"/>
+      <c r="I49" s="164"/>
+      <c r="J49" s="158"/>
+      <c r="K49" s="161"/>
       <c r="P49" s="8"/>
     </row>
     <row r="50" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A50" s="177"/>
-      <c r="B50" s="178"/>
+      <c r="A50" s="72"/>
+      <c r="B50" s="73"/>
       <c r="C50" s="26"/>
       <c r="D50" s="32"/>
-      <c r="E50" s="173"/>
-      <c r="F50" s="174"/>
-      <c r="G50" s="175"/>
-      <c r="H50" s="176"/>
-      <c r="I50" s="189"/>
-      <c r="J50" s="183"/>
-      <c r="K50" s="186"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="75"/>
+      <c r="G50" s="151"/>
+      <c r="H50" s="152"/>
+      <c r="I50" s="164"/>
+      <c r="J50" s="158"/>
+      <c r="K50" s="161"/>
       <c r="P50" s="8"/>
     </row>
     <row r="51" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A51" s="177"/>
-      <c r="B51" s="178"/>
+      <c r="A51" s="72"/>
+      <c r="B51" s="73"/>
       <c r="C51" s="26"/>
       <c r="D51" s="32"/>
-      <c r="E51" s="173"/>
-      <c r="F51" s="174"/>
-      <c r="G51" s="175"/>
-      <c r="H51" s="176"/>
-      <c r="I51" s="189"/>
-      <c r="J51" s="183"/>
-      <c r="K51" s="186"/>
+      <c r="E51" s="74"/>
+      <c r="F51" s="75"/>
+      <c r="G51" s="151"/>
+      <c r="H51" s="152"/>
+      <c r="I51" s="164"/>
+      <c r="J51" s="158"/>
+      <c r="K51" s="161"/>
       <c r="P51" s="8"/>
     </row>
     <row r="52" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A52" s="177"/>
-      <c r="B52" s="178"/>
+      <c r="A52" s="72"/>
+      <c r="B52" s="73"/>
       <c r="C52" s="26"/>
       <c r="D52" s="32"/>
-      <c r="E52" s="173"/>
-      <c r="F52" s="174"/>
-      <c r="G52" s="175"/>
-      <c r="H52" s="176"/>
-      <c r="I52" s="189"/>
-      <c r="J52" s="183"/>
-      <c r="K52" s="186"/>
+      <c r="E52" s="74"/>
+      <c r="F52" s="75"/>
+      <c r="G52" s="151"/>
+      <c r="H52" s="152"/>
+      <c r="I52" s="164"/>
+      <c r="J52" s="158"/>
+      <c r="K52" s="161"/>
       <c r="P52" s="8"/>
     </row>
     <row r="53" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A53" s="177"/>
-      <c r="B53" s="178"/>
+      <c r="A53" s="72"/>
+      <c r="B53" s="73"/>
       <c r="C53" s="26"/>
       <c r="D53" s="32"/>
-      <c r="E53" s="173"/>
-      <c r="F53" s="174"/>
-      <c r="G53" s="175"/>
-      <c r="H53" s="176"/>
-      <c r="I53" s="189"/>
-      <c r="J53" s="183"/>
-      <c r="K53" s="186"/>
+      <c r="E53" s="74"/>
+      <c r="F53" s="75"/>
+      <c r="G53" s="151"/>
+      <c r="H53" s="152"/>
+      <c r="I53" s="164"/>
+      <c r="J53" s="158"/>
+      <c r="K53" s="161"/>
       <c r="P53" s="8"/>
     </row>
     <row r="54" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A54" s="177"/>
-      <c r="B54" s="178"/>
+      <c r="A54" s="72"/>
+      <c r="B54" s="73"/>
       <c r="C54" s="33"/>
       <c r="D54" s="32"/>
-      <c r="E54" s="173"/>
-      <c r="F54" s="174"/>
-      <c r="G54" s="175"/>
-      <c r="H54" s="176"/>
-      <c r="I54" s="189"/>
-      <c r="J54" s="183"/>
-      <c r="K54" s="186"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="75"/>
+      <c r="G54" s="151"/>
+      <c r="H54" s="152"/>
+      <c r="I54" s="164"/>
+      <c r="J54" s="158"/>
+      <c r="K54" s="161"/>
       <c r="P54" s="8"/>
     </row>
     <row r="55" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A55" s="177"/>
-      <c r="B55" s="178"/>
+      <c r="A55" s="72"/>
+      <c r="B55" s="73"/>
       <c r="C55" s="24"/>
       <c r="D55" s="32"/>
-      <c r="E55" s="173"/>
-      <c r="F55" s="174"/>
-      <c r="G55" s="175"/>
-      <c r="H55" s="176"/>
-      <c r="I55" s="190"/>
-      <c r="J55" s="184"/>
-      <c r="K55" s="187"/>
-      <c r="N55" s="191"/>
-      <c r="O55" s="191"/>
-      <c r="P55" s="191"/>
-      <c r="Q55" s="191"/>
-      <c r="R55" s="191"/>
-      <c r="S55" s="191"/>
-      <c r="T55" s="191"/>
+      <c r="E55" s="74"/>
+      <c r="F55" s="75"/>
+      <c r="G55" s="151"/>
+      <c r="H55" s="152"/>
+      <c r="I55" s="165"/>
+      <c r="J55" s="159"/>
+      <c r="K55" s="162"/>
+      <c r="N55" s="148"/>
+      <c r="O55" s="148"/>
+      <c r="P55" s="148"/>
+      <c r="Q55" s="148"/>
+      <c r="R55" s="148"/>
+      <c r="S55" s="148"/>
+      <c r="T55" s="148"/>
     </row>
     <row r="56" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A56" s="192" t="s">
+      <c r="A56" s="149" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="193"/>
-      <c r="C56" s="194" t="s">
+      <c r="B56" s="150"/>
+      <c r="C56" s="135" t="s">
         <v>357</v>
       </c>
-      <c r="D56" s="195"/>
-      <c r="E56" s="195"/>
-      <c r="F56" s="195"/>
-      <c r="G56" s="195"/>
-      <c r="H56" s="195"/>
-      <c r="I56" s="195"/>
-      <c r="J56" s="195"/>
-      <c r="K56" s="196"/>
+      <c r="D56" s="136"/>
+      <c r="E56" s="136"/>
+      <c r="F56" s="136"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="136"/>
+      <c r="J56" s="136"/>
+      <c r="K56" s="137"/>
       <c r="P56" s="8"/>
     </row>
     <row r="57" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A57" s="216" t="s">
+      <c r="A57" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="217"/>
-      <c r="C57" s="194"/>
-      <c r="D57" s="195"/>
-      <c r="E57" s="195"/>
-      <c r="F57" s="195"/>
-      <c r="G57" s="195"/>
-      <c r="H57" s="195"/>
-      <c r="I57" s="195"/>
-      <c r="J57" s="195"/>
-      <c r="K57" s="196"/>
+      <c r="B57" s="134"/>
+      <c r="C57" s="135"/>
+      <c r="D57" s="136"/>
+      <c r="E57" s="136"/>
+      <c r="F57" s="136"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="136"/>
+      <c r="J57" s="136"/>
+      <c r="K57" s="137"/>
       <c r="M57" s="9"/>
     </row>
     <row r="58" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A58" s="216"/>
-      <c r="B58" s="217"/>
-      <c r="C58" s="194"/>
-      <c r="D58" s="195"/>
-      <c r="E58" s="195"/>
-      <c r="F58" s="195"/>
-      <c r="G58" s="195"/>
-      <c r="H58" s="195"/>
-      <c r="I58" s="195"/>
-      <c r="J58" s="195"/>
-      <c r="K58" s="196"/>
+      <c r="A58" s="133"/>
+      <c r="B58" s="134"/>
+      <c r="C58" s="135"/>
+      <c r="D58" s="136"/>
+      <c r="E58" s="136"/>
+      <c r="F58" s="136"/>
+      <c r="G58" s="136"/>
+      <c r="H58" s="136"/>
+      <c r="I58" s="136"/>
+      <c r="J58" s="136"/>
+      <c r="K58" s="137"/>
     </row>
     <row r="59" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A59" s="218" t="s">
+      <c r="A59" s="138" t="s">
         <v>71</v>
       </c>
-      <c r="B59" s="219"/>
-      <c r="C59" s="220" t="s">
+      <c r="B59" s="139"/>
+      <c r="C59" s="140" t="s">
         <v>77</v>
       </c>
-      <c r="D59" s="221"/>
-      <c r="E59" s="221"/>
-      <c r="F59" s="221"/>
-      <c r="G59" s="221"/>
-      <c r="H59" s="221"/>
-      <c r="I59" s="221"/>
-      <c r="J59" s="221"/>
-      <c r="K59" s="222"/>
+      <c r="D59" s="141"/>
+      <c r="E59" s="141"/>
+      <c r="F59" s="141"/>
+      <c r="G59" s="141"/>
+      <c r="H59" s="141"/>
+      <c r="I59" s="141"/>
+      <c r="J59" s="141"/>
+      <c r="K59" s="142"/>
     </row>
     <row r="60" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A60" s="223" t="s">
+      <c r="A60" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="B60" s="224"/>
-      <c r="C60" s="220" t="s">
+      <c r="B60" s="144"/>
+      <c r="C60" s="140" t="s">
         <v>359</v>
       </c>
-      <c r="D60" s="221"/>
-      <c r="E60" s="221"/>
-      <c r="F60" s="221"/>
-      <c r="G60" s="221"/>
-      <c r="H60" s="221"/>
-      <c r="I60" s="221"/>
-      <c r="J60" s="221"/>
-      <c r="K60" s="222"/>
+      <c r="D60" s="141"/>
+      <c r="E60" s="141"/>
+      <c r="F60" s="141"/>
+      <c r="G60" s="141"/>
+      <c r="H60" s="141"/>
+      <c r="I60" s="141"/>
+      <c r="J60" s="141"/>
+      <c r="K60" s="142"/>
     </row>
     <row r="61" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A61" s="225"/>
-      <c r="B61" s="226"/>
-      <c r="C61" s="227"/>
-      <c r="D61" s="228"/>
-      <c r="E61" s="228"/>
-      <c r="F61" s="228"/>
-      <c r="G61" s="228"/>
-      <c r="H61" s="228"/>
-      <c r="I61" s="228"/>
-      <c r="J61" s="228"/>
-      <c r="K61" s="229"/>
+      <c r="A61" s="103"/>
+      <c r="B61" s="104"/>
+      <c r="C61" s="145"/>
+      <c r="D61" s="146"/>
+      <c r="E61" s="146"/>
+      <c r="F61" s="146"/>
+      <c r="G61" s="146"/>
+      <c r="H61" s="146"/>
+      <c r="I61" s="146"/>
+      <c r="J61" s="146"/>
+      <c r="K61" s="147"/>
     </row>
     <row r="62" spans="1:20" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A62" s="160"/>
-      <c r="B62" s="160"/>
-      <c r="C62" s="160"/>
-      <c r="D62" s="160"/>
-      <c r="E62" s="160"/>
-      <c r="F62" s="160"/>
-      <c r="G62" s="160"/>
-      <c r="H62" s="160"/>
-      <c r="I62" s="160"/>
-      <c r="J62" s="160"/>
-      <c r="K62" s="160"/>
+      <c r="A62" s="94"/>
+      <c r="B62" s="94"/>
+      <c r="C62" s="94"/>
+      <c r="D62" s="94"/>
+      <c r="E62" s="94"/>
+      <c r="F62" s="94"/>
+      <c r="G62" s="94"/>
+      <c r="H62" s="94"/>
+      <c r="I62" s="94"/>
+      <c r="J62" s="94"/>
+      <c r="K62" s="94"/>
       <c r="P62" s="8"/>
     </row>
     <row r="63" spans="1:20" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="197" t="s">
+      <c r="A63" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="B63" s="198"/>
-      <c r="C63" s="205" t="s">
+      <c r="B63" s="115"/>
+      <c r="C63" s="122" t="s">
         <v>78</v>
       </c>
-      <c r="D63" s="206"/>
-      <c r="E63" s="206"/>
-      <c r="F63" s="206"/>
-      <c r="G63" s="206"/>
-      <c r="H63" s="206"/>
-      <c r="I63" s="206"/>
-      <c r="J63" s="206"/>
-      <c r="K63" s="207"/>
+      <c r="D63" s="123"/>
+      <c r="E63" s="123"/>
+      <c r="F63" s="123"/>
+      <c r="G63" s="123"/>
+      <c r="H63" s="123"/>
+      <c r="I63" s="123"/>
+      <c r="J63" s="123"/>
+      <c r="K63" s="124"/>
       <c r="P63" s="8"/>
     </row>
     <row r="64" spans="1:20" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="199"/>
-      <c r="B64" s="200"/>
-      <c r="C64" s="208" t="s">
+      <c r="A64" s="116"/>
+      <c r="B64" s="117"/>
+      <c r="C64" s="125" t="s">
         <v>44</v>
       </c>
-      <c r="D64" s="209"/>
-      <c r="E64" s="209"/>
-      <c r="F64" s="209"/>
-      <c r="G64" s="209"/>
-      <c r="H64" s="209"/>
-      <c r="I64" s="209"/>
-      <c r="J64" s="209"/>
-      <c r="K64" s="210"/>
+      <c r="D64" s="126"/>
+      <c r="E64" s="126"/>
+      <c r="F64" s="126"/>
+      <c r="G64" s="126"/>
+      <c r="H64" s="126"/>
+      <c r="I64" s="126"/>
+      <c r="J64" s="126"/>
+      <c r="K64" s="127"/>
       <c r="P64" s="8"/>
     </row>
     <row r="65" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="199"/>
-      <c r="B65" s="200"/>
-      <c r="C65" s="211" t="s">
+      <c r="A65" s="116"/>
+      <c r="B65" s="117"/>
+      <c r="C65" s="128" t="s">
         <v>45</v>
       </c>
-      <c r="D65" s="211"/>
-      <c r="E65" s="211"/>
-      <c r="F65" s="211"/>
-      <c r="G65" s="211"/>
-      <c r="H65" s="211"/>
-      <c r="I65" s="211"/>
-      <c r="J65" s="211"/>
-      <c r="K65" s="212"/>
+      <c r="D65" s="128"/>
+      <c r="E65" s="128"/>
+      <c r="F65" s="128"/>
+      <c r="G65" s="128"/>
+      <c r="H65" s="128"/>
+      <c r="I65" s="128"/>
+      <c r="J65" s="128"/>
+      <c r="K65" s="129"/>
       <c r="P65" s="8"/>
     </row>
     <row r="66" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="201"/>
-      <c r="B66" s="202"/>
-      <c r="C66" s="211" t="s">
+      <c r="A66" s="118"/>
+      <c r="B66" s="119"/>
+      <c r="C66" s="128" t="s">
         <v>46</v>
       </c>
-      <c r="D66" s="211"/>
-      <c r="E66" s="211"/>
-      <c r="F66" s="211"/>
-      <c r="G66" s="211"/>
-      <c r="H66" s="211"/>
-      <c r="I66" s="211"/>
-      <c r="J66" s="211"/>
-      <c r="K66" s="212"/>
+      <c r="D66" s="128"/>
+      <c r="E66" s="128"/>
+      <c r="F66" s="128"/>
+      <c r="G66" s="128"/>
+      <c r="H66" s="128"/>
+      <c r="I66" s="128"/>
+      <c r="J66" s="128"/>
+      <c r="K66" s="129"/>
       <c r="P66" s="8"/>
     </row>
     <row r="67" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A67" s="203"/>
-      <c r="B67" s="204"/>
-      <c r="C67" s="213" t="s">
+      <c r="A67" s="120"/>
+      <c r="B67" s="121"/>
+      <c r="C67" s="130" t="s">
         <v>47</v>
       </c>
-      <c r="D67" s="214"/>
-      <c r="E67" s="214"/>
-      <c r="F67" s="214"/>
-      <c r="G67" s="214"/>
-      <c r="H67" s="214"/>
-      <c r="I67" s="214"/>
-      <c r="J67" s="214"/>
-      <c r="K67" s="215"/>
+      <c r="D67" s="131"/>
+      <c r="E67" s="131"/>
+      <c r="F67" s="131"/>
+      <c r="G67" s="131"/>
+      <c r="H67" s="131"/>
+      <c r="I67" s="131"/>
+      <c r="J67" s="131"/>
+      <c r="K67" s="132"/>
       <c r="P67" s="8"/>
     </row>
     <row r="68" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A68" s="160"/>
-      <c r="B68" s="160"/>
-      <c r="C68" s="160"/>
-      <c r="D68" s="160"/>
-      <c r="E68" s="160"/>
-      <c r="F68" s="160"/>
-      <c r="G68" s="160"/>
-      <c r="H68" s="160"/>
-      <c r="I68" s="160"/>
-      <c r="J68" s="160"/>
-      <c r="K68" s="160"/>
+      <c r="A68" s="94"/>
+      <c r="B68" s="94"/>
+      <c r="C68" s="94"/>
+      <c r="D68" s="94"/>
+      <c r="E68" s="94"/>
+      <c r="F68" s="94"/>
+      <c r="G68" s="94"/>
+      <c r="H68" s="94"/>
+      <c r="I68" s="94"/>
+      <c r="J68" s="94"/>
+      <c r="K68" s="94"/>
     </row>
     <row r="69" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A69" s="248" t="s">
+      <c r="A69" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="B69" s="249"/>
-      <c r="C69" s="250" t="s">
+      <c r="B69" s="96"/>
+      <c r="C69" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="D69" s="250"/>
-      <c r="E69" s="250"/>
-      <c r="F69" s="250"/>
-      <c r="G69" s="250"/>
-      <c r="H69" s="250"/>
-      <c r="I69" s="250"/>
-      <c r="J69" s="250"/>
-      <c r="K69" s="251"/>
+      <c r="D69" s="97"/>
+      <c r="E69" s="97"/>
+      <c r="F69" s="97"/>
+      <c r="G69" s="97"/>
+      <c r="H69" s="97"/>
+      <c r="I69" s="97"/>
+      <c r="J69" s="97"/>
+      <c r="K69" s="98"/>
       <c r="P69" s="8"/>
     </row>
     <row r="70" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A70" s="160"/>
-      <c r="B70" s="160"/>
-      <c r="C70" s="160"/>
-      <c r="D70" s="160"/>
-      <c r="E70" s="160"/>
-      <c r="F70" s="160"/>
-      <c r="G70" s="160"/>
-      <c r="H70" s="160"/>
-      <c r="I70" s="160"/>
-      <c r="J70" s="160"/>
-      <c r="K70" s="160"/>
+      <c r="A70" s="94"/>
+      <c r="B70" s="94"/>
+      <c r="C70" s="94"/>
+      <c r="D70" s="94"/>
+      <c r="E70" s="94"/>
+      <c r="F70" s="94"/>
+      <c r="G70" s="94"/>
+      <c r="H70" s="94"/>
+      <c r="I70" s="94"/>
+      <c r="J70" s="94"/>
+      <c r="K70" s="94"/>
     </row>
     <row r="71" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="252" t="s">
+      <c r="A71" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="B71" s="253"/>
-      <c r="C71" s="256" t="s">
+      <c r="B71" s="100"/>
+      <c r="C71" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="D71" s="256"/>
-      <c r="E71" s="256"/>
-      <c r="F71" s="256"/>
-      <c r="G71" s="256"/>
-      <c r="H71" s="256"/>
-      <c r="I71" s="256"/>
-      <c r="J71" s="256"/>
-      <c r="K71" s="257"/>
+      <c r="D71" s="105"/>
+      <c r="E71" s="105"/>
+      <c r="F71" s="105"/>
+      <c r="G71" s="105"/>
+      <c r="H71" s="105"/>
+      <c r="I71" s="105"/>
+      <c r="J71" s="105"/>
+      <c r="K71" s="106"/>
     </row>
     <row r="72" spans="1:16" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A72" s="254"/>
-      <c r="B72" s="255"/>
-      <c r="C72" s="258" t="s">
+      <c r="A72" s="101"/>
+      <c r="B72" s="102"/>
+      <c r="C72" s="107" t="s">
         <v>51</v>
       </c>
-      <c r="D72" s="258"/>
-      <c r="E72" s="258"/>
-      <c r="F72" s="258"/>
-      <c r="G72" s="258"/>
-      <c r="H72" s="258"/>
-      <c r="I72" s="258"/>
-      <c r="J72" s="258"/>
-      <c r="K72" s="259"/>
+      <c r="D72" s="107"/>
+      <c r="E72" s="107"/>
+      <c r="F72" s="107"/>
+      <c r="G72" s="107"/>
+      <c r="H72" s="107"/>
+      <c r="I72" s="107"/>
+      <c r="J72" s="107"/>
+      <c r="K72" s="108"/>
     </row>
     <row r="73" spans="1:16" s="6" customFormat="1" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A73" s="225"/>
-      <c r="B73" s="226"/>
+      <c r="A73" s="103"/>
+      <c r="B73" s="104"/>
       <c r="C73" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D73" s="260" t="s">
+      <c r="D73" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="E73" s="261"/>
-      <c r="F73" s="262"/>
-      <c r="G73" s="263" t="s">
+      <c r="E73" s="110"/>
+      <c r="F73" s="111"/>
+      <c r="G73" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="H73" s="263"/>
-      <c r="I73" s="263"/>
-      <c r="J73" s="263"/>
-      <c r="K73" s="264"/>
+      <c r="H73" s="112"/>
+      <c r="I73" s="112"/>
+      <c r="J73" s="112"/>
+      <c r="K73" s="113"/>
     </row>
     <row r="74" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
       <c r="A74" s="35"/>
@@ -8508,53 +8508,53 @@
       <c r="K74" s="35"/>
     </row>
     <row r="75" spans="1:16" ht="25.15" customHeight="1">
-      <c r="A75" s="230" t="s">
+      <c r="A75" s="76" t="s">
         <v>358</v>
       </c>
-      <c r="B75" s="231"/>
-      <c r="C75" s="231"/>
-      <c r="D75" s="231"/>
-      <c r="E75" s="231"/>
-      <c r="F75" s="231"/>
-      <c r="G75" s="231"/>
-      <c r="H75" s="231"/>
-      <c r="I75" s="231"/>
-      <c r="J75" s="231"/>
-      <c r="K75" s="232"/>
+      <c r="B75" s="77"/>
+      <c r="C75" s="77"/>
+      <c r="D75" s="77"/>
+      <c r="E75" s="77"/>
+      <c r="F75" s="77"/>
+      <c r="G75" s="77"/>
+      <c r="H75" s="77"/>
+      <c r="I75" s="77"/>
+      <c r="J75" s="77"/>
+      <c r="K75" s="78"/>
     </row>
     <row r="76" spans="1:16" s="6" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A76" s="233" t="s">
+      <c r="A76" s="79" t="s">
         <v>356</v>
       </c>
-      <c r="B76" s="234"/>
-      <c r="C76" s="235"/>
-      <c r="D76" s="239" t="s">
+      <c r="B76" s="80"/>
+      <c r="C76" s="81"/>
+      <c r="D76" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="E76" s="240"/>
-      <c r="F76" s="240"/>
-      <c r="G76" s="240"/>
-      <c r="H76" s="243" t="s">
+      <c r="E76" s="86"/>
+      <c r="F76" s="86"/>
+      <c r="G76" s="86"/>
+      <c r="H76" s="89" t="s">
         <v>354</v>
       </c>
-      <c r="I76" s="243"/>
-      <c r="J76" s="245" t="s">
+      <c r="I76" s="89"/>
+      <c r="J76" s="91" t="s">
         <v>355</v>
       </c>
-      <c r="K76" s="246"/>
+      <c r="K76" s="92"/>
     </row>
     <row r="77" spans="1:16" s="6" customFormat="1" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A77" s="236"/>
-      <c r="B77" s="237"/>
-      <c r="C77" s="238"/>
-      <c r="D77" s="241"/>
-      <c r="E77" s="242"/>
-      <c r="F77" s="242"/>
-      <c r="G77" s="242"/>
-      <c r="H77" s="244"/>
-      <c r="I77" s="244"/>
-      <c r="J77" s="241"/>
-      <c r="K77" s="247"/>
+      <c r="A77" s="82"/>
+      <c r="B77" s="83"/>
+      <c r="C77" s="84"/>
+      <c r="D77" s="87"/>
+      <c r="E77" s="88"/>
+      <c r="F77" s="88"/>
+      <c r="G77" s="88"/>
+      <c r="H77" s="90"/>
+      <c r="I77" s="90"/>
+      <c r="J77" s="87"/>
+      <c r="K77" s="93"/>
     </row>
     <row r="78" spans="1:16">
       <c r="D78" s="5" t="s">
@@ -8563,58 +8563,87 @@
     </row>
   </sheetData>
   <mergeCells count="157">
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="A75:K75"/>
-    <mergeCell ref="A76:C77"/>
-    <mergeCell ref="D76:G77"/>
-    <mergeCell ref="H76:I77"/>
-    <mergeCell ref="J76:K77"/>
-    <mergeCell ref="A68:K68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:K69"/>
-    <mergeCell ref="A70:K70"/>
-    <mergeCell ref="A71:B73"/>
-    <mergeCell ref="C71:K71"/>
-    <mergeCell ref="C72:K72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="A62:K62"/>
-    <mergeCell ref="A63:B67"/>
-    <mergeCell ref="C63:K63"/>
-    <mergeCell ref="C64:K64"/>
-    <mergeCell ref="C65:K65"/>
-    <mergeCell ref="C66:K66"/>
-    <mergeCell ref="C67:K67"/>
-    <mergeCell ref="A57:B58"/>
-    <mergeCell ref="C57:K57"/>
-    <mergeCell ref="C58:K58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C59:K59"/>
-    <mergeCell ref="A60:B61"/>
-    <mergeCell ref="C60:K60"/>
-    <mergeCell ref="C61:K61"/>
-    <mergeCell ref="N55:T55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:K56"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:K2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="C9:K9"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:K21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:K22"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:K17"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:K19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:K23"/>
+    <mergeCell ref="A26:K27"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A30:B32"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:H32"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="C38:K38"/>
+    <mergeCell ref="A39:B41"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:K41"/>
     <mergeCell ref="E50:F50"/>
     <mergeCell ref="G50:H50"/>
     <mergeCell ref="A51:B51"/>
@@ -8639,87 +8668,58 @@
     <mergeCell ref="G47:H47"/>
     <mergeCell ref="G48:H48"/>
     <mergeCell ref="G49:H49"/>
-    <mergeCell ref="A39:B41"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="C38:K38"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:K23"/>
-    <mergeCell ref="A26:K27"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A30:B32"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:H32"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:K20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:K21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:K22"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:K17"/>
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:K19"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="C9:K9"/>
-    <mergeCell ref="C10:K10"/>
-    <mergeCell ref="C11:K11"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="N55:T55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:K56"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="A62:K62"/>
+    <mergeCell ref="A63:B67"/>
+    <mergeCell ref="C63:K63"/>
+    <mergeCell ref="C64:K64"/>
+    <mergeCell ref="C65:K65"/>
+    <mergeCell ref="C66:K66"/>
+    <mergeCell ref="C67:K67"/>
+    <mergeCell ref="A57:B58"/>
+    <mergeCell ref="C57:K57"/>
+    <mergeCell ref="C58:K58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:K59"/>
+    <mergeCell ref="A60:B61"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="C61:K61"/>
+    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A76:C77"/>
+    <mergeCell ref="D76:G77"/>
+    <mergeCell ref="H76:I77"/>
+    <mergeCell ref="J76:K77"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:K69"/>
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A71:B73"/>
+    <mergeCell ref="C71:K71"/>
+    <mergeCell ref="C72:K72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E48:F48"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
@@ -8759,79 +8759,79 @@
   <sheetData>
     <row r="1" spans="2:14" ht="41.25" customHeight="1"/>
     <row r="2" spans="2:14" ht="33.950000000000003" customHeight="1">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="49" t="s">
         <v>349</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="62"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="51"/>
     </row>
     <row r="3" spans="2:14" ht="21" customHeight="1">
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="52" t="s">
         <v>350</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65" t="s">
+      <c r="C3" s="53"/>
+      <c r="D3" s="54" t="s">
         <v>351</v>
       </c>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="67"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="H3" s="38"/>
       <c r="I3" s="37" t="s">
         <v>291</v>
       </c>
-      <c r="J3" s="68" t="s">
+      <c r="J3" s="57" t="s">
         <v>352</v>
       </c>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
       <c r="N3" s="40"/>
     </row>
     <row r="4" spans="2:14" ht="21.95" customHeight="1">
       <c r="B4" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="71"/>
-      <c r="E4" s="70" t="s">
+      <c r="D4" s="60"/>
+      <c r="E4" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="F4" s="71"/>
+      <c r="F4" s="60"/>
       <c r="G4" s="42" t="s">
         <v>96</v>
       </c>
       <c r="H4" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="I4" s="70" t="s">
+      <c r="I4" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="J4" s="71"/>
-      <c r="K4" s="70" t="s">
+      <c r="J4" s="60"/>
+      <c r="K4" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="L4" s="71"/>
+      <c r="L4" s="60"/>
       <c r="M4" s="42" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="21" customHeight="1">
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="56"/>
+      <c r="C5" s="62"/>
       <c r="D5" s="42" t="s">
         <v>102</v>
       </c>
@@ -8844,10 +8844,10 @@
       <c r="G5" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="H5" s="55" t="s">
+      <c r="H5" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="I5" s="56"/>
+      <c r="I5" s="62"/>
       <c r="J5" s="42" t="s">
         <v>102</v>
       </c>
@@ -8875,7 +8875,7 @@
       <c r="F6" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="63" t="s">
         <v>111</v>
       </c>
       <c r="H6" s="41" t="s">
@@ -8891,7 +8891,7 @@
       <c r="L6" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M6" s="57" t="s">
+      <c r="M6" s="63" t="s">
         <v>115</v>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       <c r="F7" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="58"/>
+      <c r="G7" s="64"/>
       <c r="H7" s="41" t="s">
         <v>119</v>
       </c>
@@ -8923,7 +8923,7 @@
       <c r="L7" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M7" s="58"/>
+      <c r="M7" s="64"/>
     </row>
     <row r="8" spans="2:14" ht="21" customHeight="1">
       <c r="B8" s="41" t="s">
@@ -8939,7 +8939,7 @@
       <c r="F8" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G8" s="58"/>
+      <c r="G8" s="64"/>
       <c r="H8" s="41" t="s">
         <v>123</v>
       </c>
@@ -8953,7 +8953,7 @@
       <c r="L8" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M8" s="58"/>
+      <c r="M8" s="64"/>
     </row>
     <row r="9" spans="2:14" ht="21" customHeight="1">
       <c r="B9" s="41" t="s">
@@ -8969,7 +8969,7 @@
       <c r="F9" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G9" s="58"/>
+      <c r="G9" s="64"/>
       <c r="H9" s="41" t="s">
         <v>128</v>
       </c>
@@ -8985,7 +8985,7 @@
       <c r="L9" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="M9" s="58"/>
+      <c r="M9" s="64"/>
     </row>
     <row r="10" spans="2:14" ht="21" customHeight="1">
       <c r="B10" s="41" t="s">
@@ -9001,7 +9001,7 @@
       <c r="F10" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="58"/>
+      <c r="G10" s="64"/>
       <c r="H10" s="41" t="s">
         <v>135</v>
       </c>
@@ -9015,7 +9015,7 @@
       <c r="L10" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M10" s="58"/>
+      <c r="M10" s="64"/>
     </row>
     <row r="11" spans="2:14" ht="21" customHeight="1">
       <c r="B11" s="41" t="s">
@@ -9031,7 +9031,7 @@
       <c r="F11" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="58"/>
+      <c r="G11" s="64"/>
       <c r="H11" s="41" t="s">
         <v>139</v>
       </c>
@@ -9045,7 +9045,7 @@
       <c r="L11" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M11" s="58"/>
+      <c r="M11" s="64"/>
     </row>
     <row r="12" spans="2:14" ht="21" customHeight="1">
       <c r="B12" s="41" t="s">
@@ -9061,7 +9061,7 @@
       <c r="F12" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G12" s="58"/>
+      <c r="G12" s="64"/>
       <c r="H12" s="41" t="s">
         <v>143</v>
       </c>
@@ -9075,7 +9075,7 @@
       <c r="L12" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M12" s="59"/>
+      <c r="M12" s="65"/>
     </row>
     <row r="13" spans="2:14" ht="21" customHeight="1">
       <c r="B13" s="41" t="s">
@@ -9091,11 +9091,11 @@
       <c r="F13" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G13" s="58"/>
-      <c r="H13" s="55" t="s">
+      <c r="G13" s="64"/>
+      <c r="H13" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="I13" s="56"/>
+      <c r="I13" s="62"/>
       <c r="J13" s="42"/>
       <c r="K13" s="42" t="s">
         <v>103</v>
@@ -9121,7 +9121,7 @@
       <c r="F14" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="59"/>
+      <c r="G14" s="65"/>
       <c r="H14" s="41" t="s">
         <v>150</v>
       </c>
@@ -9135,15 +9135,15 @@
       <c r="L14" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M14" s="57" t="s">
+      <c r="M14" s="63" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="21" customHeight="1">
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="C15" s="56"/>
+      <c r="C15" s="62"/>
       <c r="D15" s="42"/>
       <c r="E15" s="42" t="s">
         <v>103</v>
@@ -9167,7 +9167,7 @@
       <c r="L15" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M15" s="58"/>
+      <c r="M15" s="64"/>
     </row>
     <row r="16" spans="2:14" ht="21" customHeight="1">
       <c r="B16" s="41" t="s">
@@ -9183,7 +9183,7 @@
       <c r="F16" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G16" s="57" t="s">
+      <c r="G16" s="63" t="s">
         <v>111</v>
       </c>
       <c r="H16" s="41" t="s">
@@ -9199,7 +9199,7 @@
       <c r="L16" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M16" s="58"/>
+      <c r="M16" s="64"/>
     </row>
     <row r="17" spans="2:13" ht="21" customHeight="1">
       <c r="B17" s="41" t="s">
@@ -9215,7 +9215,7 @@
       <c r="F17" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G17" s="58"/>
+      <c r="G17" s="64"/>
       <c r="H17" s="41" t="s">
         <v>162</v>
       </c>
@@ -9229,7 +9229,7 @@
       <c r="L17" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M17" s="58"/>
+      <c r="M17" s="64"/>
     </row>
     <row r="18" spans="2:13" ht="21" customHeight="1">
       <c r="B18" s="41" t="s">
@@ -9245,7 +9245,7 @@
       <c r="F18" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G18" s="58"/>
+      <c r="G18" s="64"/>
       <c r="H18" s="41" t="s">
         <v>166</v>
       </c>
@@ -9259,7 +9259,7 @@
       <c r="L18" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M18" s="58"/>
+      <c r="M18" s="64"/>
     </row>
     <row r="19" spans="2:13" ht="21" customHeight="1">
       <c r="B19" s="41" t="s">
@@ -9275,7 +9275,7 @@
       <c r="F19" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G19" s="59"/>
+      <c r="G19" s="65"/>
       <c r="H19" s="41" t="s">
         <v>170</v>
       </c>
@@ -9289,13 +9289,13 @@
       <c r="L19" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M19" s="58"/>
+      <c r="M19" s="64"/>
     </row>
     <row r="20" spans="2:13" ht="21" customHeight="1">
-      <c r="B20" s="55" t="s">
+      <c r="B20" s="61" t="s">
         <v>172</v>
       </c>
-      <c r="C20" s="56"/>
+      <c r="C20" s="62"/>
       <c r="D20" s="42"/>
       <c r="E20" s="42" t="s">
         <v>103</v>
@@ -9319,7 +9319,7 @@
       <c r="L20" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="M20" s="58"/>
+      <c r="M20" s="64"/>
     </row>
     <row r="21" spans="2:13" ht="21" customHeight="1">
       <c r="B21" s="41" t="s">
@@ -9335,7 +9335,7 @@
       <c r="F21" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="57" t="s">
+      <c r="G21" s="63" t="s">
         <v>111</v>
       </c>
       <c r="H21" s="41" t="s">
@@ -9351,7 +9351,7 @@
       <c r="L21" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M21" s="58"/>
+      <c r="M21" s="64"/>
     </row>
     <row r="22" spans="2:13" ht="21" customHeight="1">
       <c r="B22" s="41" t="s">
@@ -9367,7 +9367,7 @@
       <c r="F22" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="58"/>
+      <c r="G22" s="64"/>
       <c r="H22" s="41" t="s">
         <v>180</v>
       </c>
@@ -9381,7 +9381,7 @@
       <c r="L22" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M22" s="58"/>
+      <c r="M22" s="64"/>
     </row>
     <row r="23" spans="2:13" ht="21" customHeight="1">
       <c r="B23" s="41" t="s">
@@ -9397,7 +9397,7 @@
       <c r="F23" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="58"/>
+      <c r="G23" s="64"/>
       <c r="H23" s="41" t="s">
         <v>184</v>
       </c>
@@ -9411,7 +9411,7 @@
       <c r="L23" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M23" s="58"/>
+      <c r="M23" s="64"/>
     </row>
     <row r="24" spans="2:13" ht="21" customHeight="1">
       <c r="B24" s="41" t="s">
@@ -9427,7 +9427,7 @@
       <c r="F24" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G24" s="59"/>
+      <c r="G24" s="65"/>
       <c r="H24" s="41" t="s">
         <v>188</v>
       </c>
@@ -9441,13 +9441,13 @@
       <c r="L24" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M24" s="58"/>
+      <c r="M24" s="64"/>
     </row>
     <row r="25" spans="2:13" ht="21" customHeight="1">
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="61" t="s">
         <v>190</v>
       </c>
-      <c r="C25" s="56"/>
+      <c r="C25" s="62"/>
       <c r="D25" s="42"/>
       <c r="E25" s="42" t="s">
         <v>103</v>
@@ -9471,7 +9471,7 @@
       <c r="L25" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M25" s="58"/>
+      <c r="M25" s="64"/>
     </row>
     <row r="26" spans="2:13" ht="21" customHeight="1">
       <c r="B26" s="41" t="s">
@@ -9487,7 +9487,7 @@
       <c r="F26" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G26" s="57" t="s">
+      <c r="G26" s="63" t="s">
         <v>111</v>
       </c>
       <c r="H26" s="41" t="s">
@@ -9503,7 +9503,7 @@
       <c r="L26" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M26" s="58"/>
+      <c r="M26" s="64"/>
     </row>
     <row r="27" spans="2:13" ht="21" customHeight="1">
       <c r="B27" s="41" t="s">
@@ -9519,7 +9519,7 @@
       <c r="F27" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G27" s="58"/>
+      <c r="G27" s="64"/>
       <c r="H27" s="41" t="s">
         <v>199</v>
       </c>
@@ -9533,7 +9533,7 @@
       <c r="L27" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M27" s="59"/>
+      <c r="M27" s="65"/>
     </row>
     <row r="28" spans="2:13" ht="21" customHeight="1">
       <c r="B28" s="41" t="s">
@@ -9549,11 +9549,11 @@
       <c r="F28" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G28" s="58"/>
-      <c r="H28" s="55" t="s">
+      <c r="G28" s="64"/>
+      <c r="H28" s="61" t="s">
         <v>203</v>
       </c>
-      <c r="I28" s="56"/>
+      <c r="I28" s="62"/>
       <c r="J28" s="42"/>
       <c r="K28" s="42" t="s">
         <v>103</v>
@@ -9579,7 +9579,7 @@
       <c r="F29" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G29" s="58"/>
+      <c r="G29" s="64"/>
       <c r="H29" s="41" t="s">
         <v>206</v>
       </c>
@@ -9593,7 +9593,7 @@
       <c r="L29" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M29" s="57" t="s">
+      <c r="M29" s="63" t="s">
         <v>115</v>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       <c r="F30" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G30" s="58"/>
+      <c r="G30" s="64"/>
       <c r="H30" s="41" t="s">
         <v>210</v>
       </c>
@@ -9625,7 +9625,7 @@
       <c r="L30" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M30" s="58"/>
+      <c r="M30" s="64"/>
     </row>
     <row r="31" spans="2:13" ht="21" customHeight="1">
       <c r="B31" s="41" t="s">
@@ -9641,7 +9641,7 @@
       <c r="F31" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G31" s="58"/>
+      <c r="G31" s="64"/>
       <c r="H31" s="41" t="s">
         <v>214</v>
       </c>
@@ -9655,7 +9655,7 @@
       <c r="L31" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M31" s="58"/>
+      <c r="M31" s="64"/>
     </row>
     <row r="32" spans="2:13" ht="21" customHeight="1">
       <c r="B32" s="41" t="s">
@@ -9671,7 +9671,7 @@
       <c r="F32" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G32" s="58"/>
+      <c r="G32" s="64"/>
       <c r="H32" s="41" t="s">
         <v>218</v>
       </c>
@@ -9685,7 +9685,7 @@
       <c r="L32" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="M32" s="58"/>
+      <c r="M32" s="64"/>
     </row>
     <row r="33" spans="2:13" ht="21" customHeight="1">
       <c r="B33" s="41" t="s">
@@ -9701,7 +9701,7 @@
       <c r="F33" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G33" s="58"/>
+      <c r="G33" s="64"/>
       <c r="H33" s="41" t="s">
         <v>222</v>
       </c>
@@ -9715,7 +9715,7 @@
       <c r="L33" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M33" s="58"/>
+      <c r="M33" s="64"/>
     </row>
     <row r="34" spans="2:13" ht="21" customHeight="1">
       <c r="B34" s="41" t="s">
@@ -9731,7 +9731,7 @@
       <c r="F34" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G34" s="59"/>
+      <c r="G34" s="65"/>
       <c r="H34" s="41" t="s">
         <v>226</v>
       </c>
@@ -9745,13 +9745,13 @@
       <c r="L34" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M34" s="58"/>
+      <c r="M34" s="64"/>
     </row>
     <row r="35" spans="2:13" ht="21" customHeight="1">
-      <c r="B35" s="55" t="s">
+      <c r="B35" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="56"/>
+      <c r="C35" s="62"/>
       <c r="D35" s="42"/>
       <c r="E35" s="42" t="s">
         <v>103</v>
@@ -9775,7 +9775,7 @@
       <c r="L35" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M35" s="58"/>
+      <c r="M35" s="64"/>
     </row>
     <row r="36" spans="2:13" ht="21" customHeight="1">
       <c r="B36" s="41" t="s">
@@ -9791,7 +9791,7 @@
       <c r="F36" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G36" s="57" t="s">
+      <c r="G36" s="63" t="s">
         <v>111</v>
       </c>
       <c r="H36" s="41" t="s">
@@ -9807,7 +9807,7 @@
       <c r="L36" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M36" s="59"/>
+      <c r="M36" s="65"/>
     </row>
     <row r="37" spans="2:13" ht="21" customHeight="1">
       <c r="B37" s="41" t="s">
@@ -9823,11 +9823,11 @@
       <c r="F37" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G37" s="58"/>
-      <c r="H37" s="55" t="s">
+      <c r="G37" s="64"/>
+      <c r="H37" s="61" t="s">
         <v>235</v>
       </c>
-      <c r="I37" s="56"/>
+      <c r="I37" s="62"/>
       <c r="J37" s="42"/>
       <c r="K37" s="42" t="s">
         <v>103</v>
@@ -9853,7 +9853,7 @@
       <c r="F38" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G38" s="58"/>
+      <c r="G38" s="64"/>
       <c r="H38" s="41" t="s">
         <v>238</v>
       </c>
@@ -9867,7 +9867,7 @@
       <c r="L38" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M38" s="57" t="s">
+      <c r="M38" s="63" t="s">
         <v>115</v>
       </c>
     </row>
@@ -9885,7 +9885,7 @@
       <c r="F39" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G39" s="58"/>
+      <c r="G39" s="64"/>
       <c r="H39" s="41" t="s">
         <v>242</v>
       </c>
@@ -9899,7 +9899,7 @@
       <c r="L39" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M39" s="58"/>
+      <c r="M39" s="64"/>
     </row>
     <row r="40" spans="2:13" ht="21" customHeight="1">
       <c r="B40" s="41" t="s">
@@ -9915,7 +9915,7 @@
       <c r="F40" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G40" s="58"/>
+      <c r="G40" s="64"/>
       <c r="H40" s="41" t="s">
         <v>246</v>
       </c>
@@ -9929,7 +9929,7 @@
       <c r="L40" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M40" s="58"/>
+      <c r="M40" s="64"/>
     </row>
     <row r="41" spans="2:13" ht="21" customHeight="1">
       <c r="B41" s="41" t="s">
@@ -9945,7 +9945,7 @@
       <c r="F41" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G41" s="58"/>
+      <c r="G41" s="64"/>
       <c r="H41" s="41" t="s">
         <v>250</v>
       </c>
@@ -9959,7 +9959,7 @@
       <c r="L41" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="M41" s="58"/>
+      <c r="M41" s="64"/>
     </row>
     <row r="42" spans="2:13" ht="21" customHeight="1">
       <c r="B42" s="41" t="s">
@@ -9975,7 +9975,7 @@
       <c r="F42" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G42" s="58"/>
+      <c r="G42" s="64"/>
       <c r="H42" s="41" t="s">
         <v>254</v>
       </c>
@@ -9989,7 +9989,7 @@
       <c r="L42" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M42" s="58"/>
+      <c r="M42" s="64"/>
     </row>
     <row r="43" spans="2:13" ht="21" customHeight="1">
       <c r="B43" s="41" t="s">
@@ -10005,7 +10005,7 @@
       <c r="F43" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G43" s="58"/>
+      <c r="G43" s="64"/>
       <c r="H43" s="41" t="s">
         <v>258</v>
       </c>
@@ -10019,7 +10019,7 @@
       <c r="L43" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M43" s="58"/>
+      <c r="M43" s="64"/>
     </row>
     <row r="44" spans="2:13" ht="21" customHeight="1">
       <c r="B44" s="41" t="s">
@@ -10035,7 +10035,7 @@
       <c r="F44" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G44" s="59"/>
+      <c r="G44" s="65"/>
       <c r="H44" s="41" t="s">
         <v>263</v>
       </c>
@@ -10049,48 +10049,49 @@
       <c r="L44" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M44" s="59"/>
+      <c r="M44" s="65"/>
     </row>
     <row r="45" spans="2:13" ht="21.95" customHeight="1">
-      <c r="B45" s="49" t="s">
+      <c r="B45" s="66" t="s">
         <v>265</v>
       </c>
-      <c r="C45" s="50"/>
-      <c r="D45" s="50"/>
-      <c r="E45" s="50"/>
-      <c r="F45" s="50"/>
-      <c r="G45" s="50"/>
-      <c r="H45" s="50"/>
-      <c r="I45" s="50"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="50"/>
-      <c r="L45" s="50"/>
-      <c r="M45" s="51"/>
+      <c r="C45" s="67"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="67"/>
+      <c r="H45" s="67"/>
+      <c r="I45" s="67"/>
+      <c r="J45" s="67"/>
+      <c r="K45" s="67"/>
+      <c r="L45" s="67"/>
+      <c r="M45" s="68"/>
     </row>
     <row r="46" spans="2:13" ht="23.1" customHeight="1">
-      <c r="B46" s="52"/>
-      <c r="C46" s="53"/>
-      <c r="D46" s="53"/>
-      <c r="E46" s="53"/>
-      <c r="F46" s="53"/>
-      <c r="G46" s="53"/>
-      <c r="H46" s="53"/>
-      <c r="I46" s="53"/>
-      <c r="J46" s="53"/>
-      <c r="K46" s="53"/>
-      <c r="L46" s="53"/>
-      <c r="M46" s="54"/>
+      <c r="B46" s="69"/>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="70"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="70"/>
+      <c r="M46" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="B45:M46"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="G26:G34"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="M29:M36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="G36:G44"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="M38:M44"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="G6:G14"/>
@@ -10101,15 +10102,14 @@
     <mergeCell ref="G16:G19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="G21:G24"/>
-    <mergeCell ref="B45:M46"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="G26:G34"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="M29:M36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="G36:G44"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="M38:M44"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -10168,72 +10168,72 @@
       <c r="B3" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="57" t="s">
         <v>267</v>
       </c>
-      <c r="D3" s="282"/>
+      <c r="D3" s="265"/>
       <c r="E3" s="44" t="s">
         <v>268</v>
       </c>
       <c r="F3" s="45" t="s">
         <v>269</v>
       </c>
-      <c r="G3" s="63" t="s">
+      <c r="G3" s="52" t="s">
         <v>361</v>
       </c>
-      <c r="H3" s="64"/>
-      <c r="I3" s="284" t="s">
+      <c r="H3" s="53"/>
+      <c r="I3" s="266" t="s">
         <v>360</v>
       </c>
-      <c r="J3" s="286"/>
-      <c r="K3" s="285"/>
+      <c r="J3" s="267"/>
+      <c r="K3" s="268"/>
     </row>
     <row r="4" spans="2:11">
       <c r="B4" s="44" t="s">
         <v>270</v>
       </c>
-      <c r="C4" s="284" t="s">
+      <c r="C4" s="266" t="s">
         <v>271</v>
       </c>
-      <c r="D4" s="285"/>
+      <c r="D4" s="268"/>
       <c r="E4" s="44" t="s">
         <v>272</v>
       </c>
       <c r="F4" s="45" t="s">
         <v>273</v>
       </c>
-      <c r="G4" s="63" t="s">
+      <c r="G4" s="52" t="s">
         <v>274</v>
       </c>
-      <c r="H4" s="64"/>
-      <c r="I4" s="68" t="s">
+      <c r="H4" s="53"/>
+      <c r="I4" s="57" t="s">
         <v>275</v>
       </c>
-      <c r="J4" s="69"/>
-      <c r="K4" s="282"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="265"/>
     </row>
     <row r="5" spans="2:11">
       <c r="B5" s="44" t="s">
         <v>276</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="57" t="s">
         <v>277</v>
       </c>
-      <c r="D5" s="282"/>
+      <c r="D5" s="265"/>
       <c r="E5" s="44" t="s">
         <v>278</v>
       </c>
       <c r="F5" s="45" t="s">
         <v>279</v>
       </c>
-      <c r="G5" s="63" t="s">
+      <c r="G5" s="52" t="s">
         <v>280</v>
       </c>
-      <c r="H5" s="64"/>
-      <c r="I5" s="68" t="s">
+      <c r="H5" s="53"/>
+      <c r="I5" s="57" t="s">
         <v>281</v>
       </c>
-      <c r="J5" s="282"/>
+      <c r="J5" s="265"/>
       <c r="K5" s="45" t="s">
         <v>282</v>
       </c>
@@ -10242,635 +10242,635 @@
       <c r="B6" s="44" t="s">
         <v>283</v>
       </c>
-      <c r="C6" s="284" t="s">
+      <c r="C6" s="266" t="s">
         <v>362</v>
       </c>
-      <c r="D6" s="285"/>
+      <c r="D6" s="268"/>
       <c r="E6" s="44" t="s">
         <v>284</v>
       </c>
       <c r="F6" s="45" t="s">
         <v>285</v>
       </c>
-      <c r="G6" s="63" t="s">
+      <c r="G6" s="52" t="s">
         <v>286</v>
       </c>
-      <c r="H6" s="64"/>
-      <c r="I6" s="65" t="s">
+      <c r="H6" s="53"/>
+      <c r="I6" s="54" t="s">
         <v>287</v>
       </c>
-      <c r="J6" s="69"/>
-      <c r="K6" s="282"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="265"/>
     </row>
     <row r="7" spans="2:11" ht="15.95" customHeight="1">
       <c r="B7" s="44" t="s">
         <v>288</v>
       </c>
-      <c r="C7" s="280" t="s">
+      <c r="C7" s="269" t="s">
         <v>353</v>
       </c>
-      <c r="D7" s="281"/>
+      <c r="D7" s="270"/>
       <c r="E7" s="44" t="s">
         <v>289</v>
       </c>
       <c r="F7" s="39" t="s">
         <v>290</v>
       </c>
-      <c r="G7" s="63" t="s">
+      <c r="G7" s="52" t="s">
         <v>291</v>
       </c>
-      <c r="H7" s="64"/>
-      <c r="I7" s="68" t="s">
+      <c r="H7" s="53"/>
+      <c r="I7" s="57" t="s">
         <v>292</v>
       </c>
-      <c r="J7" s="69"/>
-      <c r="K7" s="282"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="265"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="265"/>
-      <c r="C8" s="266"/>
-      <c r="D8" s="266"/>
-      <c r="E8" s="266"/>
-      <c r="F8" s="266"/>
-      <c r="G8" s="266"/>
-      <c r="H8" s="266"/>
-      <c r="I8" s="266"/>
-      <c r="J8" s="266"/>
-      <c r="K8" s="267"/>
+      <c r="B8" s="271"/>
+      <c r="C8" s="272"/>
+      <c r="D8" s="272"/>
+      <c r="E8" s="272"/>
+      <c r="F8" s="272"/>
+      <c r="G8" s="272"/>
+      <c r="H8" s="272"/>
+      <c r="I8" s="272"/>
+      <c r="J8" s="272"/>
+      <c r="K8" s="273"/>
     </row>
     <row r="9" spans="2:11">
       <c r="B9" s="44" t="s">
         <v>293</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="52" t="s">
         <v>294</v>
       </c>
-      <c r="D9" s="283"/>
-      <c r="E9" s="283"/>
-      <c r="F9" s="283"/>
-      <c r="G9" s="283"/>
-      <c r="H9" s="64"/>
+      <c r="D9" s="274"/>
+      <c r="E9" s="274"/>
+      <c r="F9" s="274"/>
+      <c r="G9" s="274"/>
+      <c r="H9" s="53"/>
       <c r="I9" s="44" t="s">
         <v>295</v>
       </c>
-      <c r="J9" s="63" t="s">
+      <c r="J9" s="52" t="s">
         <v>296</v>
       </c>
-      <c r="K9" s="64"/>
+      <c r="K9" s="53"/>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="265" t="s">
+      <c r="B10" s="271" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="266"/>
-      <c r="D10" s="266"/>
-      <c r="E10" s="266"/>
-      <c r="F10" s="266"/>
-      <c r="G10" s="266"/>
-      <c r="H10" s="266"/>
-      <c r="I10" s="266"/>
-      <c r="J10" s="266"/>
-      <c r="K10" s="267"/>
+      <c r="C10" s="272"/>
+      <c r="D10" s="272"/>
+      <c r="E10" s="272"/>
+      <c r="F10" s="272"/>
+      <c r="G10" s="272"/>
+      <c r="H10" s="272"/>
+      <c r="I10" s="272"/>
+      <c r="J10" s="272"/>
+      <c r="K10" s="273"/>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="268" t="s">
+      <c r="B11" s="275" t="s">
         <v>298</v>
       </c>
-      <c r="C11" s="265" t="s">
+      <c r="C11" s="271" t="s">
         <v>299</v>
       </c>
-      <c r="D11" s="266"/>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="267"/>
+      <c r="D11" s="272"/>
+      <c r="E11" s="272"/>
+      <c r="F11" s="272"/>
+      <c r="G11" s="272"/>
+      <c r="H11" s="273"/>
       <c r="I11" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J11" s="265"/>
-      <c r="K11" s="267"/>
+      <c r="J11" s="271"/>
+      <c r="K11" s="273"/>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="269"/>
-      <c r="C12" s="265" t="s">
+      <c r="B12" s="276"/>
+      <c r="C12" s="271" t="s">
         <v>301</v>
       </c>
-      <c r="D12" s="266"/>
-      <c r="E12" s="266"/>
-      <c r="F12" s="266"/>
-      <c r="G12" s="266"/>
-      <c r="H12" s="267"/>
+      <c r="D12" s="272"/>
+      <c r="E12" s="272"/>
+      <c r="F12" s="272"/>
+      <c r="G12" s="272"/>
+      <c r="H12" s="273"/>
       <c r="I12" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="J12" s="265"/>
-      <c r="K12" s="267"/>
+      <c r="J12" s="271"/>
+      <c r="K12" s="273"/>
     </row>
     <row r="13" spans="2:11" ht="25.5" customHeight="1">
-      <c r="B13" s="270"/>
-      <c r="C13" s="265" t="s">
+      <c r="B13" s="277"/>
+      <c r="C13" s="271" t="s">
         <v>303</v>
       </c>
-      <c r="D13" s="266"/>
-      <c r="E13" s="266"/>
-      <c r="F13" s="266"/>
-      <c r="G13" s="266"/>
-      <c r="H13" s="267"/>
+      <c r="D13" s="272"/>
+      <c r="E13" s="272"/>
+      <c r="F13" s="272"/>
+      <c r="G13" s="272"/>
+      <c r="H13" s="273"/>
       <c r="I13" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="J13" s="265"/>
-      <c r="K13" s="267"/>
+      <c r="J13" s="271"/>
+      <c r="K13" s="273"/>
     </row>
     <row r="14" spans="2:11">
-      <c r="B14" s="265" t="s">
+      <c r="B14" s="271" t="s">
         <v>304</v>
       </c>
-      <c r="C14" s="266"/>
-      <c r="D14" s="266"/>
-      <c r="E14" s="266"/>
-      <c r="F14" s="266"/>
-      <c r="G14" s="266"/>
-      <c r="H14" s="266"/>
-      <c r="I14" s="266"/>
-      <c r="J14" s="266"/>
-      <c r="K14" s="267"/>
+      <c r="C14" s="272"/>
+      <c r="D14" s="272"/>
+      <c r="E14" s="272"/>
+      <c r="F14" s="272"/>
+      <c r="G14" s="272"/>
+      <c r="H14" s="272"/>
+      <c r="I14" s="272"/>
+      <c r="J14" s="272"/>
+      <c r="K14" s="273"/>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="268" t="s">
+      <c r="B15" s="275" t="s">
         <v>305</v>
       </c>
-      <c r="C15" s="265" t="s">
+      <c r="C15" s="271" t="s">
         <v>306</v>
       </c>
-      <c r="D15" s="266"/>
-      <c r="E15" s="266"/>
-      <c r="F15" s="266"/>
-      <c r="G15" s="266"/>
-      <c r="H15" s="267"/>
-      <c r="I15" s="271" t="s">
+      <c r="D15" s="272"/>
+      <c r="E15" s="272"/>
+      <c r="F15" s="272"/>
+      <c r="G15" s="272"/>
+      <c r="H15" s="273"/>
+      <c r="I15" s="278" t="s">
         <v>300</v>
       </c>
-      <c r="J15" s="274"/>
-      <c r="K15" s="275"/>
+      <c r="J15" s="280"/>
+      <c r="K15" s="281"/>
     </row>
     <row r="16" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B16" s="270"/>
-      <c r="C16" s="265" t="s">
+      <c r="B16" s="277"/>
+      <c r="C16" s="271" t="s">
         <v>307</v>
       </c>
-      <c r="D16" s="266"/>
-      <c r="E16" s="266"/>
-      <c r="F16" s="266"/>
-      <c r="G16" s="266"/>
-      <c r="H16" s="267"/>
-      <c r="I16" s="273"/>
-      <c r="J16" s="278"/>
-      <c r="K16" s="279"/>
+      <c r="D16" s="272"/>
+      <c r="E16" s="272"/>
+      <c r="F16" s="272"/>
+      <c r="G16" s="272"/>
+      <c r="H16" s="273"/>
+      <c r="I16" s="279"/>
+      <c r="J16" s="282"/>
+      <c r="K16" s="283"/>
     </row>
     <row r="17" spans="2:11" ht="18" customHeight="1">
-      <c r="B17" s="268" t="s">
+      <c r="B17" s="275" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="265" t="s">
+      <c r="C17" s="271" t="s">
         <v>309</v>
       </c>
-      <c r="D17" s="266"/>
-      <c r="E17" s="266"/>
-      <c r="F17" s="266"/>
-      <c r="G17" s="266"/>
-      <c r="H17" s="267"/>
-      <c r="I17" s="271" t="s">
+      <c r="D17" s="272"/>
+      <c r="E17" s="272"/>
+      <c r="F17" s="272"/>
+      <c r="G17" s="272"/>
+      <c r="H17" s="273"/>
+      <c r="I17" s="278" t="s">
         <v>300</v>
       </c>
-      <c r="J17" s="274"/>
-      <c r="K17" s="275"/>
+      <c r="J17" s="280"/>
+      <c r="K17" s="281"/>
     </row>
     <row r="18" spans="2:11" ht="27" customHeight="1">
-      <c r="B18" s="269"/>
-      <c r="C18" s="265" t="s">
+      <c r="B18" s="276"/>
+      <c r="C18" s="271" t="s">
         <v>310</v>
       </c>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="267"/>
-      <c r="I18" s="272"/>
-      <c r="J18" s="276"/>
-      <c r="K18" s="277"/>
+      <c r="D18" s="272"/>
+      <c r="E18" s="272"/>
+      <c r="F18" s="272"/>
+      <c r="G18" s="272"/>
+      <c r="H18" s="273"/>
+      <c r="I18" s="284"/>
+      <c r="J18" s="285"/>
+      <c r="K18" s="286"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="269"/>
-      <c r="C19" s="265" t="s">
+      <c r="B19" s="276"/>
+      <c r="C19" s="271" t="s">
         <v>311</v>
       </c>
-      <c r="D19" s="266"/>
-      <c r="E19" s="266"/>
-      <c r="F19" s="266"/>
-      <c r="G19" s="266"/>
-      <c r="H19" s="267"/>
-      <c r="I19" s="272"/>
-      <c r="J19" s="276"/>
-      <c r="K19" s="277"/>
+      <c r="D19" s="272"/>
+      <c r="E19" s="272"/>
+      <c r="F19" s="272"/>
+      <c r="G19" s="272"/>
+      <c r="H19" s="273"/>
+      <c r="I19" s="284"/>
+      <c r="J19" s="285"/>
+      <c r="K19" s="286"/>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="270"/>
-      <c r="C20" s="265" t="s">
+      <c r="B20" s="277"/>
+      <c r="C20" s="271" t="s">
         <v>312</v>
       </c>
-      <c r="D20" s="266"/>
-      <c r="E20" s="266"/>
-      <c r="F20" s="266"/>
-      <c r="G20" s="266"/>
-      <c r="H20" s="267"/>
-      <c r="I20" s="273"/>
-      <c r="J20" s="278"/>
-      <c r="K20" s="279"/>
+      <c r="D20" s="272"/>
+      <c r="E20" s="272"/>
+      <c r="F20" s="272"/>
+      <c r="G20" s="272"/>
+      <c r="H20" s="273"/>
+      <c r="I20" s="279"/>
+      <c r="J20" s="282"/>
+      <c r="K20" s="283"/>
     </row>
     <row r="21" spans="2:11">
-      <c r="B21" s="265" t="s">
+      <c r="B21" s="271" t="s">
         <v>313</v>
       </c>
-      <c r="C21" s="266"/>
-      <c r="D21" s="266"/>
-      <c r="E21" s="266"/>
-      <c r="F21" s="266"/>
-      <c r="G21" s="266"/>
-      <c r="H21" s="266"/>
-      <c r="I21" s="266"/>
-      <c r="J21" s="266"/>
-      <c r="K21" s="267"/>
+      <c r="C21" s="272"/>
+      <c r="D21" s="272"/>
+      <c r="E21" s="272"/>
+      <c r="F21" s="272"/>
+      <c r="G21" s="272"/>
+      <c r="H21" s="272"/>
+      <c r="I21" s="272"/>
+      <c r="J21" s="272"/>
+      <c r="K21" s="273"/>
     </row>
     <row r="22" spans="2:11" ht="18" customHeight="1">
-      <c r="B22" s="268" t="s">
+      <c r="B22" s="275" t="s">
         <v>314</v>
       </c>
-      <c r="C22" s="265" t="s">
+      <c r="C22" s="271" t="s">
         <v>315</v>
       </c>
-      <c r="D22" s="266"/>
-      <c r="E22" s="266"/>
-      <c r="F22" s="266"/>
-      <c r="G22" s="266"/>
-      <c r="H22" s="267"/>
-      <c r="I22" s="271" t="s">
+      <c r="D22" s="272"/>
+      <c r="E22" s="272"/>
+      <c r="F22" s="272"/>
+      <c r="G22" s="272"/>
+      <c r="H22" s="273"/>
+      <c r="I22" s="278" t="s">
         <v>300</v>
       </c>
-      <c r="J22" s="274"/>
-      <c r="K22" s="275"/>
+      <c r="J22" s="280"/>
+      <c r="K22" s="281"/>
     </row>
     <row r="23" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B23" s="270"/>
-      <c r="C23" s="265" t="s">
+      <c r="B23" s="277"/>
+      <c r="C23" s="271" t="s">
         <v>316</v>
       </c>
-      <c r="D23" s="266"/>
-      <c r="E23" s="266"/>
-      <c r="F23" s="266"/>
-      <c r="G23" s="266"/>
-      <c r="H23" s="267"/>
-      <c r="I23" s="273"/>
-      <c r="J23" s="278"/>
-      <c r="K23" s="279"/>
+      <c r="D23" s="272"/>
+      <c r="E23" s="272"/>
+      <c r="F23" s="272"/>
+      <c r="G23" s="272"/>
+      <c r="H23" s="273"/>
+      <c r="I23" s="279"/>
+      <c r="J23" s="282"/>
+      <c r="K23" s="283"/>
     </row>
     <row r="24" spans="2:11">
-      <c r="B24" s="265" t="s">
+      <c r="B24" s="271" t="s">
         <v>317</v>
       </c>
-      <c r="C24" s="266"/>
-      <c r="D24" s="266"/>
-      <c r="E24" s="266"/>
-      <c r="F24" s="266"/>
-      <c r="G24" s="266"/>
-      <c r="H24" s="266"/>
-      <c r="I24" s="266"/>
-      <c r="J24" s="266"/>
-      <c r="K24" s="267"/>
+      <c r="C24" s="272"/>
+      <c r="D24" s="272"/>
+      <c r="E24" s="272"/>
+      <c r="F24" s="272"/>
+      <c r="G24" s="272"/>
+      <c r="H24" s="272"/>
+      <c r="I24" s="272"/>
+      <c r="J24" s="272"/>
+      <c r="K24" s="273"/>
     </row>
     <row r="25" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B25" s="268" t="s">
+      <c r="B25" s="275" t="s">
         <v>318</v>
       </c>
-      <c r="C25" s="265" t="s">
+      <c r="C25" s="271" t="s">
         <v>319</v>
       </c>
-      <c r="D25" s="266"/>
-      <c r="E25" s="266"/>
-      <c r="F25" s="266"/>
-      <c r="G25" s="266"/>
-      <c r="H25" s="267"/>
-      <c r="I25" s="271" t="s">
+      <c r="D25" s="272"/>
+      <c r="E25" s="272"/>
+      <c r="F25" s="272"/>
+      <c r="G25" s="272"/>
+      <c r="H25" s="273"/>
+      <c r="I25" s="278" t="s">
         <v>300</v>
       </c>
-      <c r="J25" s="274"/>
-      <c r="K25" s="275"/>
+      <c r="J25" s="280"/>
+      <c r="K25" s="281"/>
     </row>
     <row r="26" spans="2:11">
-      <c r="B26" s="270"/>
-      <c r="C26" s="265" t="s">
+      <c r="B26" s="277"/>
+      <c r="C26" s="271" t="s">
         <v>320</v>
       </c>
-      <c r="D26" s="266"/>
-      <c r="E26" s="266"/>
-      <c r="F26" s="266"/>
-      <c r="G26" s="266"/>
-      <c r="H26" s="267"/>
-      <c r="I26" s="273"/>
-      <c r="J26" s="278"/>
-      <c r="K26" s="279"/>
+      <c r="D26" s="272"/>
+      <c r="E26" s="272"/>
+      <c r="F26" s="272"/>
+      <c r="G26" s="272"/>
+      <c r="H26" s="273"/>
+      <c r="I26" s="279"/>
+      <c r="J26" s="282"/>
+      <c r="K26" s="283"/>
     </row>
     <row r="27" spans="2:11" ht="15.95" customHeight="1">
       <c r="B27" s="46" t="s">
         <v>321</v>
       </c>
-      <c r="C27" s="265" t="s">
+      <c r="C27" s="271" t="s">
         <v>322</v>
       </c>
-      <c r="D27" s="266"/>
-      <c r="E27" s="266"/>
-      <c r="F27" s="266"/>
-      <c r="G27" s="266"/>
-      <c r="H27" s="267"/>
+      <c r="D27" s="272"/>
+      <c r="E27" s="272"/>
+      <c r="F27" s="272"/>
+      <c r="G27" s="272"/>
+      <c r="H27" s="273"/>
       <c r="I27" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J27" s="265"/>
-      <c r="K27" s="267"/>
+      <c r="J27" s="271"/>
+      <c r="K27" s="273"/>
     </row>
     <row r="28" spans="2:11">
-      <c r="B28" s="265" t="s">
+      <c r="B28" s="271" t="s">
         <v>323</v>
       </c>
-      <c r="C28" s="266"/>
-      <c r="D28" s="266"/>
-      <c r="E28" s="266"/>
-      <c r="F28" s="266"/>
-      <c r="G28" s="266"/>
-      <c r="H28" s="266"/>
-      <c r="I28" s="266"/>
-      <c r="J28" s="266"/>
-      <c r="K28" s="267"/>
+      <c r="C28" s="272"/>
+      <c r="D28" s="272"/>
+      <c r="E28" s="272"/>
+      <c r="F28" s="272"/>
+      <c r="G28" s="272"/>
+      <c r="H28" s="272"/>
+      <c r="I28" s="272"/>
+      <c r="J28" s="272"/>
+      <c r="K28" s="273"/>
     </row>
     <row r="29" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B29" s="268" t="s">
+      <c r="B29" s="275" t="s">
         <v>324</v>
       </c>
-      <c r="C29" s="265" t="s">
+      <c r="C29" s="271" t="s">
         <v>325</v>
       </c>
-      <c r="D29" s="266"/>
-      <c r="E29" s="266"/>
-      <c r="F29" s="266"/>
-      <c r="G29" s="266"/>
-      <c r="H29" s="267"/>
-      <c r="I29" s="271" t="s">
+      <c r="D29" s="272"/>
+      <c r="E29" s="272"/>
+      <c r="F29" s="272"/>
+      <c r="G29" s="272"/>
+      <c r="H29" s="273"/>
+      <c r="I29" s="278" t="s">
         <v>300</v>
       </c>
-      <c r="J29" s="274"/>
-      <c r="K29" s="275"/>
+      <c r="J29" s="280"/>
+      <c r="K29" s="281"/>
     </row>
     <row r="30" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B30" s="270"/>
-      <c r="C30" s="265" t="s">
+      <c r="B30" s="277"/>
+      <c r="C30" s="271" t="s">
         <v>326</v>
       </c>
-      <c r="D30" s="266"/>
-      <c r="E30" s="266"/>
-      <c r="F30" s="266"/>
-      <c r="G30" s="266"/>
-      <c r="H30" s="267"/>
-      <c r="I30" s="273"/>
-      <c r="J30" s="278"/>
-      <c r="K30" s="279"/>
+      <c r="D30" s="272"/>
+      <c r="E30" s="272"/>
+      <c r="F30" s="272"/>
+      <c r="G30" s="272"/>
+      <c r="H30" s="273"/>
+      <c r="I30" s="279"/>
+      <c r="J30" s="282"/>
+      <c r="K30" s="283"/>
     </row>
     <row r="31" spans="2:11">
-      <c r="B31" s="265" t="s">
+      <c r="B31" s="271" t="s">
         <v>327</v>
       </c>
-      <c r="C31" s="266"/>
-      <c r="D31" s="266"/>
-      <c r="E31" s="266"/>
-      <c r="F31" s="266"/>
-      <c r="G31" s="266"/>
-      <c r="H31" s="266"/>
-      <c r="I31" s="266"/>
-      <c r="J31" s="266"/>
-      <c r="K31" s="267"/>
+      <c r="C31" s="272"/>
+      <c r="D31" s="272"/>
+      <c r="E31" s="272"/>
+      <c r="F31" s="272"/>
+      <c r="G31" s="272"/>
+      <c r="H31" s="272"/>
+      <c r="I31" s="272"/>
+      <c r="J31" s="272"/>
+      <c r="K31" s="273"/>
     </row>
     <row r="32" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B32" s="268" t="s">
+      <c r="B32" s="275" t="s">
         <v>328</v>
       </c>
-      <c r="C32" s="265" t="s">
+      <c r="C32" s="271" t="s">
         <v>329</v>
       </c>
-      <c r="D32" s="266"/>
-      <c r="E32" s="266"/>
-      <c r="F32" s="266"/>
-      <c r="G32" s="266"/>
-      <c r="H32" s="267"/>
-      <c r="I32" s="271" t="s">
+      <c r="D32" s="272"/>
+      <c r="E32" s="272"/>
+      <c r="F32" s="272"/>
+      <c r="G32" s="272"/>
+      <c r="H32" s="273"/>
+      <c r="I32" s="278" t="s">
         <v>300</v>
       </c>
-      <c r="J32" s="274"/>
-      <c r="K32" s="275"/>
+      <c r="J32" s="280"/>
+      <c r="K32" s="281"/>
     </row>
     <row r="33" spans="2:11" ht="18" customHeight="1">
-      <c r="B33" s="269"/>
-      <c r="C33" s="265" t="s">
+      <c r="B33" s="276"/>
+      <c r="C33" s="271" t="s">
         <v>330</v>
       </c>
-      <c r="D33" s="266"/>
-      <c r="E33" s="266"/>
-      <c r="F33" s="266"/>
-      <c r="G33" s="266"/>
-      <c r="H33" s="267"/>
-      <c r="I33" s="272"/>
-      <c r="J33" s="276"/>
-      <c r="K33" s="277"/>
+      <c r="D33" s="272"/>
+      <c r="E33" s="272"/>
+      <c r="F33" s="272"/>
+      <c r="G33" s="272"/>
+      <c r="H33" s="273"/>
+      <c r="I33" s="284"/>
+      <c r="J33" s="285"/>
+      <c r="K33" s="286"/>
     </row>
     <row r="34" spans="2:11" ht="18" customHeight="1">
-      <c r="B34" s="270"/>
-      <c r="C34" s="265" t="s">
+      <c r="B34" s="277"/>
+      <c r="C34" s="271" t="s">
         <v>331</v>
       </c>
-      <c r="D34" s="266"/>
-      <c r="E34" s="266"/>
-      <c r="F34" s="266"/>
-      <c r="G34" s="266"/>
-      <c r="H34" s="267"/>
-      <c r="I34" s="273"/>
-      <c r="J34" s="278"/>
-      <c r="K34" s="279"/>
+      <c r="D34" s="272"/>
+      <c r="E34" s="272"/>
+      <c r="F34" s="272"/>
+      <c r="G34" s="272"/>
+      <c r="H34" s="273"/>
+      <c r="I34" s="279"/>
+      <c r="J34" s="282"/>
+      <c r="K34" s="283"/>
     </row>
     <row r="35" spans="2:11" ht="15.95" customHeight="1">
-      <c r="B35" s="265" t="s">
+      <c r="B35" s="271" t="s">
         <v>332</v>
       </c>
-      <c r="C35" s="266"/>
-      <c r="D35" s="266"/>
-      <c r="E35" s="266"/>
-      <c r="F35" s="266"/>
-      <c r="G35" s="266"/>
-      <c r="H35" s="266"/>
-      <c r="I35" s="266"/>
-      <c r="J35" s="266"/>
-      <c r="K35" s="267"/>
+      <c r="C35" s="272"/>
+      <c r="D35" s="272"/>
+      <c r="E35" s="272"/>
+      <c r="F35" s="272"/>
+      <c r="G35" s="272"/>
+      <c r="H35" s="272"/>
+      <c r="I35" s="272"/>
+      <c r="J35" s="272"/>
+      <c r="K35" s="273"/>
     </row>
     <row r="36" spans="2:11" ht="28.5" customHeight="1">
       <c r="B36" s="46" t="s">
         <v>333</v>
       </c>
-      <c r="C36" s="265" t="s">
+      <c r="C36" s="271" t="s">
         <v>334</v>
       </c>
-      <c r="D36" s="266"/>
-      <c r="E36" s="266"/>
-      <c r="F36" s="266"/>
-      <c r="G36" s="266"/>
-      <c r="H36" s="267"/>
+      <c r="D36" s="272"/>
+      <c r="E36" s="272"/>
+      <c r="F36" s="272"/>
+      <c r="G36" s="272"/>
+      <c r="H36" s="273"/>
       <c r="I36" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J36" s="265"/>
-      <c r="K36" s="267"/>
+      <c r="J36" s="271"/>
+      <c r="K36" s="273"/>
     </row>
     <row r="37" spans="2:11" ht="15.95" customHeight="1">
       <c r="B37" s="46" t="s">
         <v>335</v>
       </c>
-      <c r="C37" s="265" t="s">
+      <c r="C37" s="271" t="s">
         <v>336</v>
       </c>
-      <c r="D37" s="266"/>
-      <c r="E37" s="266"/>
-      <c r="F37" s="266"/>
-      <c r="G37" s="266"/>
-      <c r="H37" s="267"/>
+      <c r="D37" s="272"/>
+      <c r="E37" s="272"/>
+      <c r="F37" s="272"/>
+      <c r="G37" s="272"/>
+      <c r="H37" s="273"/>
       <c r="I37" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="J37" s="265"/>
-      <c r="K37" s="267"/>
+      <c r="J37" s="271"/>
+      <c r="K37" s="273"/>
     </row>
     <row r="38" spans="2:11" ht="18" customHeight="1">
       <c r="B38" s="47" t="s">
         <v>337</v>
       </c>
-      <c r="C38" s="265" t="s">
+      <c r="C38" s="271" t="s">
         <v>338</v>
       </c>
-      <c r="D38" s="266"/>
-      <c r="E38" s="266"/>
-      <c r="F38" s="266"/>
-      <c r="G38" s="266"/>
-      <c r="H38" s="267"/>
+      <c r="D38" s="272"/>
+      <c r="E38" s="272"/>
+      <c r="F38" s="272"/>
+      <c r="G38" s="272"/>
+      <c r="H38" s="273"/>
       <c r="I38" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J38" s="265"/>
-      <c r="K38" s="267"/>
+      <c r="J38" s="271"/>
+      <c r="K38" s="273"/>
     </row>
     <row r="39" spans="2:11" ht="15.95" customHeight="1">
-      <c r="B39" s="265" t="s">
+      <c r="B39" s="271" t="s">
         <v>339</v>
       </c>
-      <c r="C39" s="266"/>
-      <c r="D39" s="266"/>
-      <c r="E39" s="266"/>
-      <c r="F39" s="266"/>
-      <c r="G39" s="266"/>
-      <c r="H39" s="266"/>
-      <c r="I39" s="266"/>
-      <c r="J39" s="266"/>
-      <c r="K39" s="267"/>
+      <c r="C39" s="272"/>
+      <c r="D39" s="272"/>
+      <c r="E39" s="272"/>
+      <c r="F39" s="272"/>
+      <c r="G39" s="272"/>
+      <c r="H39" s="272"/>
+      <c r="I39" s="272"/>
+      <c r="J39" s="272"/>
+      <c r="K39" s="273"/>
     </row>
     <row r="40" spans="2:11" ht="21" customHeight="1">
       <c r="B40" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="C40" s="265" t="s">
+      <c r="C40" s="271" t="s">
         <v>341</v>
       </c>
-      <c r="D40" s="266"/>
-      <c r="E40" s="266"/>
-      <c r="F40" s="266"/>
-      <c r="G40" s="266"/>
-      <c r="H40" s="267"/>
+      <c r="D40" s="272"/>
+      <c r="E40" s="272"/>
+      <c r="F40" s="272"/>
+      <c r="G40" s="272"/>
+      <c r="H40" s="273"/>
       <c r="I40" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J40" s="265"/>
-      <c r="K40" s="267"/>
+      <c r="J40" s="271"/>
+      <c r="K40" s="273"/>
     </row>
     <row r="41" spans="2:11" ht="28.5" customHeight="1">
       <c r="B41" s="46" t="s">
         <v>342</v>
       </c>
-      <c r="C41" s="265" t="s">
+      <c r="C41" s="271" t="s">
         <v>343</v>
       </c>
-      <c r="D41" s="266"/>
-      <c r="E41" s="266"/>
-      <c r="F41" s="266"/>
-      <c r="G41" s="266"/>
-      <c r="H41" s="267"/>
+      <c r="D41" s="272"/>
+      <c r="E41" s="272"/>
+      <c r="F41" s="272"/>
+      <c r="G41" s="272"/>
+      <c r="H41" s="273"/>
       <c r="I41" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J41" s="265"/>
-      <c r="K41" s="267"/>
+      <c r="J41" s="271"/>
+      <c r="K41" s="273"/>
     </row>
     <row r="42" spans="2:11" ht="18.95" customHeight="1">
       <c r="B42" s="46" t="s">
         <v>344</v>
       </c>
-      <c r="C42" s="265" t="s">
+      <c r="C42" s="271" t="s">
         <v>345</v>
       </c>
-      <c r="D42" s="266"/>
-      <c r="E42" s="266"/>
-      <c r="F42" s="266"/>
-      <c r="G42" s="266"/>
-      <c r="H42" s="267"/>
+      <c r="D42" s="272"/>
+      <c r="E42" s="272"/>
+      <c r="F42" s="272"/>
+      <c r="G42" s="272"/>
+      <c r="H42" s="273"/>
       <c r="I42" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J42" s="265"/>
-      <c r="K42" s="267"/>
+      <c r="J42" s="271"/>
+      <c r="K42" s="273"/>
     </row>
     <row r="43" spans="2:11" ht="28.5" customHeight="1">
       <c r="B43" s="46" t="s">
         <v>346</v>
       </c>
-      <c r="C43" s="265" t="s">
+      <c r="C43" s="271" t="s">
         <v>347</v>
       </c>
-      <c r="D43" s="266"/>
-      <c r="E43" s="266"/>
-      <c r="F43" s="266"/>
-      <c r="G43" s="266"/>
-      <c r="H43" s="267"/>
+      <c r="D43" s="272"/>
+      <c r="E43" s="272"/>
+      <c r="F43" s="272"/>
+      <c r="G43" s="272"/>
+      <c r="H43" s="273"/>
       <c r="I43" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J43" s="265"/>
-      <c r="K43" s="267"/>
+      <c r="J43" s="271"/>
+      <c r="K43" s="273"/>
     </row>
     <row r="44" spans="2:11" ht="50.1" customHeight="1">
-      <c r="B44" s="265" t="s">
+      <c r="B44" s="271" t="s">
         <v>348</v>
       </c>
-      <c r="C44" s="266"/>
-      <c r="D44" s="266"/>
-      <c r="E44" s="266"/>
-      <c r="F44" s="266"/>
-      <c r="G44" s="266"/>
-      <c r="H44" s="266"/>
-      <c r="I44" s="266"/>
-      <c r="J44" s="266"/>
-      <c r="K44" s="267"/>
+      <c r="C44" s="272"/>
+      <c r="D44" s="272"/>
+      <c r="E44" s="272"/>
+      <c r="F44" s="272"/>
+      <c r="G44" s="272"/>
+      <c r="H44" s="272"/>
+      <c r="I44" s="272"/>
+      <c r="J44" s="272"/>
+      <c r="K44" s="273"/>
     </row>
     <row r="45" spans="2:11">
       <c r="B45" s="43"/>
@@ -10887,65 +10887,16 @@
     <row r="46" spans="2:11" ht="11.1" customHeight="1"/>
   </sheetData>
   <mergeCells count="83">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="B8:K8"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="B10:K10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="B14:K14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="J15:K16"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="I17:I20"/>
-    <mergeCell ref="J17:K20"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="B21:K21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J22:K23"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="B24:K24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="J25:K26"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="B28:K28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:H29"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="J29:K30"/>
-    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="B44:K44"/>
+    <mergeCell ref="B39:K39"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="J42:K42"/>
     <mergeCell ref="C38:H38"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="B31:K31"/>
@@ -10960,16 +10911,65 @@
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="C37:H37"/>
     <mergeCell ref="J37:K37"/>
-    <mergeCell ref="C43:H43"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="B44:K44"/>
-    <mergeCell ref="B39:K39"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="B28:K28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="J29:K30"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="B24:K24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:K26"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="B21:K21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J22:K23"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="I17:I20"/>
+    <mergeCell ref="J17:K20"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="B14:K14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="J15:K16"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:K4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/public/01.계약서.xlsx
+++ b/public/01.계약서.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\01.AntiGravity\eBro\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01.AntiGravity\eBro\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9FE7B7-2068-44D9-A810-38E1DAA96C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5E02B2-B9FD-4190-92BD-4017DDE146A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9E72163E-9728-43C2-B59D-2067775552E8}"/>
   </bookViews>
@@ -2945,10 +2945,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">■ 3개월 이하: 왕복 운반비 임차인 부담 ■ 5개월 이하: 편도 운반비 임차인 부담 ■ 5개월 초과 : 왕복 운반비 임대인 부담 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">  본사/공장  : 경기도 용인시 처인구 모현읍 갈담로112번길 21-3     영업 사무소: 경기도 용인시 기흥구 기흥로 60-1, C동1004호(기흥ICT밸리)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -2991,6 +2987,10 @@
   </si>
   <si>
     <t>(수량)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>■ {최소기간}개월 이하: 왕복 운반비 임차인 부담 ■ {기준기간}개월 이하: 편도 운반비 임차인 부담 ■ {기준기간}개월 초과 : 왕복 운반비 임대인 부담</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -5559,6 +5559,39 @@
     <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="99" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="100" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="101" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="102" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="103" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="104" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5595,38 +5628,320 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="4" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="44" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="44" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="4" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="10" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="10" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="11" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="5" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="5" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="5" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="6" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="7" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="4" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="4" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="4" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="9" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="9" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="9" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="9" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="9" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="9" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="42" fillId="45" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="11" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="12" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="21" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="28" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="29" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="99" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="100" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="101" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="102" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="103" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="104" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="23" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="24" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="25" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="38" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="43" fillId="45" borderId="39" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="43" fillId="45" borderId="40" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="43" fillId="45" borderId="41" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="43" fillId="45" borderId="39" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="43" fillId="45" borderId="40" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="43" fillId="45" borderId="42" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="31" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="32" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="36" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="37" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="44" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="45" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="46" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="45" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="48" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="30" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="45" borderId="22" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="47" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="30" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="50" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="43" fillId="45" borderId="44" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="43" fillId="45" borderId="27" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="43" fillId="45" borderId="44" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="43" fillId="45" borderId="27" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="45" borderId="52" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5634,11 +5949,158 @@
     <xf numFmtId="0" fontId="46" fillId="45" borderId="27" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="43" fillId="45" borderId="44" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="0" xfId="166" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="38" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="43" fillId="45" borderId="27" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="46" fillId="45" borderId="54" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="46" fillId="45" borderId="56" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="46" fillId="45" borderId="53" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="55" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="57" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="59" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="54" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="56" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="53" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="60" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="54" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="44" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="45" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="45" borderId="46" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="43" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="60" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="54" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="48" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="41" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="51" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="27" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="47" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="46" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="49" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="50" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="46" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="46" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="61" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="53" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="44" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="46" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="62" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="63" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="64" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="65" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="66" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="35" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="67" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="76" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5694,9 +6156,6 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="83" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="68" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5721,12 +6180,6 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="73" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="64" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="65" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="9" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5754,524 +6207,71 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="50" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="43" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="99" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="101" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="105" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="106" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="102" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="104" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="52" fillId="0" borderId="93" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="60" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="54" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="48" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="41" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="51" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="27" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="47" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="46" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="49" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="30" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="50" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="46" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="46" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="44" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="45" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="46" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="61" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="53" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="44" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="46" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="62" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="63" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="66" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="35" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="67" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="60" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="54" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="43" fillId="45" borderId="44" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="43" fillId="45" borderId="27" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="0" xfId="166" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="38" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="13" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="46" fillId="45" borderId="54" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="46" fillId="45" borderId="56" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="46" fillId="45" borderId="53" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="55" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="57" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="59" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="54" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="56" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="53" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="45" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="43" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="48" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="30" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="22" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="43" fillId="45" borderId="22" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="47" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="30" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="50" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="38" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="43" fillId="45" borderId="39" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="43" fillId="45" borderId="40" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="43" fillId="45" borderId="41" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="43" fillId="45" borderId="39" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="43" fillId="45" borderId="40" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="43" fillId="45" borderId="42" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="23" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="25" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="31" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="32" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="36" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="37" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="166" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="44" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="45" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="46" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="166" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="42" fillId="45" borderId="0" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="11" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="12" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="21" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="28" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="29" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="24" xfId="166" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="5" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="5" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="5" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="7" fillId="6" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="7" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="9" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="9" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="9" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="9" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="9" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="9" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="4" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="10" borderId="2" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="10" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="11" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="2" borderId="4" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="2" borderId="3" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="4" borderId="1" xfId="166" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="44" borderId="4" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="44" borderId="3" xfId="166" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="47" borderId="94" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="52" fillId="0" borderId="93" xfId="171" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="93" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="94" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="26" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="47" borderId="94" xfId="171" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="96" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="98" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="99" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="101" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="102" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="104" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="97" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="105" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="106" xfId="171" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="172">
@@ -7259,231 +7259,231 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A1" s="226" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="226"/>
-      <c r="C1" s="260"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
       <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A2" s="226" t="s">
+      <c r="A2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="226"/>
-      <c r="C2" s="261"/>
-      <c r="D2" s="262"/>
-      <c r="E2" s="262"/>
-      <c r="F2" s="263"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="263"/>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="264"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="77"/>
       <c r="P2" s="2"/>
     </row>
     <row r="3" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A3" s="226" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="226"/>
-      <c r="C3" s="248"/>
-      <c r="D3" s="248"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="250"/>
-      <c r="G3" s="250"/>
-      <c r="H3" s="251"/>
-      <c r="I3" s="251"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="253"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="83"/>
       <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A4" s="226" t="s">
+      <c r="A4" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="226"/>
-      <c r="C4" s="248"/>
-      <c r="D4" s="248"/>
-      <c r="E4" s="249"/>
-      <c r="F4" s="250"/>
-      <c r="G4" s="250"/>
-      <c r="H4" s="251"/>
-      <c r="I4" s="251"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="253"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="83"/>
       <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A5" s="226" t="s">
+      <c r="A5" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="226"/>
-      <c r="C5" s="254"/>
-      <c r="D5" s="254"/>
-      <c r="E5" s="255"/>
-      <c r="F5" s="256"/>
-      <c r="G5" s="256"/>
-      <c r="H5" s="257"/>
-      <c r="I5" s="257"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="259"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="86"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="89"/>
       <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A6" s="196" t="s">
+      <c r="A6" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="197"/>
-      <c r="C6" s="237"/>
-      <c r="D6" s="238"/>
-      <c r="E6" s="238"/>
-      <c r="F6" s="238"/>
-      <c r="G6" s="238"/>
-      <c r="H6" s="238"/>
-      <c r="I6" s="238"/>
-      <c r="J6" s="238"/>
-      <c r="K6" s="239"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="101"/>
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A7" s="226" t="s">
+      <c r="A7" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="226"/>
-      <c r="C7" s="240"/>
-      <c r="D7" s="240"/>
-      <c r="E7" s="240"/>
-      <c r="F7" s="240"/>
-      <c r="G7" s="240"/>
-      <c r="H7" s="240"/>
-      <c r="I7" s="240"/>
-      <c r="J7" s="240"/>
-      <c r="K7" s="240"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
       <c r="P7" s="2"/>
     </row>
     <row r="8" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A8" s="230" t="s">
+      <c r="A8" s="90" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="232"/>
-      <c r="D8" s="233"/>
-      <c r="E8" s="233"/>
-      <c r="F8" s="233"/>
-      <c r="G8" s="233"/>
-      <c r="H8" s="233"/>
-      <c r="I8" s="233"/>
-      <c r="J8" s="233"/>
-      <c r="K8" s="234"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="94"/>
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A9" s="241"/>
+      <c r="A9" s="103"/>
       <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="232"/>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="234"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="93"/>
+      <c r="K9" s="94"/>
       <c r="P9" s="2"/>
     </row>
     <row r="10" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A10" s="241"/>
+      <c r="A10" s="103"/>
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="242"/>
-      <c r="D10" s="243"/>
-      <c r="E10" s="243"/>
-      <c r="F10" s="243"/>
-      <c r="G10" s="243"/>
-      <c r="H10" s="243"/>
-      <c r="I10" s="243"/>
-      <c r="J10" s="243"/>
-      <c r="K10" s="244"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="106"/>
       <c r="P10" s="2"/>
     </row>
     <row r="11" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A11" s="231"/>
+      <c r="A11" s="91"/>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="245"/>
-      <c r="D11" s="246"/>
-      <c r="E11" s="246"/>
-      <c r="F11" s="246"/>
-      <c r="G11" s="246"/>
-      <c r="H11" s="246"/>
-      <c r="I11" s="246"/>
-      <c r="J11" s="246"/>
-      <c r="K11" s="247"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="109"/>
       <c r="P11" s="2"/>
     </row>
     <row r="12" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A12" s="230" t="s">
+      <c r="A12" s="90" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="232"/>
-      <c r="D12" s="233"/>
-      <c r="E12" s="233"/>
-      <c r="F12" s="233"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="233"/>
-      <c r="I12" s="233"/>
-      <c r="J12" s="233"/>
-      <c r="K12" s="234"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="94"/>
       <c r="P12" s="2"/>
     </row>
     <row r="13" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A13" s="231"/>
+      <c r="A13" s="91"/>
       <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="232"/>
-      <c r="D13" s="233"/>
-      <c r="E13" s="233"/>
-      <c r="F13" s="233"/>
-      <c r="G13" s="233"/>
-      <c r="H13" s="233"/>
-      <c r="I13" s="233"/>
-      <c r="J13" s="233"/>
-      <c r="K13" s="234"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="93"/>
+      <c r="K13" s="94"/>
       <c r="P13" s="2"/>
     </row>
     <row r="14" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A14" s="226" t="s">
+      <c r="A14" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="226"/>
-      <c r="C14" s="235"/>
-      <c r="D14" s="235"/>
-      <c r="E14" s="235"/>
-      <c r="F14" s="235"/>
-      <c r="G14" s="235"/>
-      <c r="H14" s="235"/>
-      <c r="I14" s="235"/>
-      <c r="J14" s="235"/>
-      <c r="K14" s="235"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
@@ -7493,19 +7493,19 @@
       <c r="R14" s="4"/>
     </row>
     <row r="15" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A15" s="226" t="s">
+      <c r="A15" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="226"/>
-      <c r="C15" s="236"/>
-      <c r="D15" s="236"/>
-      <c r="E15" s="236"/>
-      <c r="F15" s="236"/>
-      <c r="G15" s="236"/>
-      <c r="H15" s="236"/>
-      <c r="I15" s="236"/>
-      <c r="J15" s="236"/>
-      <c r="K15" s="236"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="96"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="96"/>
+      <c r="H15" s="96"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="96"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -7515,19 +7515,19 @@
       <c r="R15" s="4"/>
     </row>
     <row r="16" spans="1:18" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A16" s="226" t="s">
+      <c r="A16" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="226"/>
-      <c r="C16" s="223"/>
-      <c r="D16" s="223"/>
-      <c r="E16" s="223"/>
-      <c r="F16" s="223"/>
-      <c r="G16" s="223"/>
-      <c r="H16" s="223"/>
-      <c r="I16" s="223"/>
-      <c r="J16" s="223"/>
-      <c r="K16" s="223"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="113"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="113"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -7537,123 +7537,123 @@
       <c r="R16" s="4"/>
     </row>
     <row r="17" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A17" s="196" t="s">
+      <c r="A17" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="197"/>
-      <c r="C17" s="223" t="s">
+      <c r="B17" s="98"/>
+      <c r="C17" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="223"/>
-      <c r="E17" s="223"/>
-      <c r="F17" s="223"/>
-      <c r="G17" s="223"/>
-      <c r="H17" s="223"/>
-      <c r="I17" s="223"/>
-      <c r="J17" s="223"/>
-      <c r="K17" s="223"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
     </row>
     <row r="18" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A18" s="196"/>
-      <c r="B18" s="197"/>
-      <c r="C18" s="227" t="s">
+      <c r="A18" s="97"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="228"/>
-      <c r="E18" s="228"/>
-      <c r="F18" s="228"/>
-      <c r="G18" s="228"/>
-      <c r="H18" s="228"/>
-      <c r="I18" s="228"/>
-      <c r="J18" s="228"/>
-      <c r="K18" s="229"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="121"/>
     </row>
     <row r="19" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A19" s="220" t="s">
+      <c r="A19" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="221"/>
-      <c r="C19" s="222" t="s">
+      <c r="B19" s="111"/>
+      <c r="C19" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="222"/>
-      <c r="E19" s="222"/>
-      <c r="F19" s="222"/>
-      <c r="G19" s="222"/>
-      <c r="H19" s="222"/>
-      <c r="I19" s="222"/>
-      <c r="J19" s="222"/>
-      <c r="K19" s="222"/>
+      <c r="D19" s="112"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="112"/>
     </row>
     <row r="20" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A20" s="220" t="s">
+      <c r="A20" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="221"/>
-      <c r="C20" s="222" t="s">
+      <c r="B20" s="111"/>
+      <c r="C20" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="222"/>
-      <c r="E20" s="222"/>
-      <c r="F20" s="222"/>
-      <c r="G20" s="222"/>
-      <c r="H20" s="222"/>
-      <c r="I20" s="222"/>
-      <c r="J20" s="222"/>
-      <c r="K20" s="222"/>
+      <c r="D20" s="112"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="112"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="112"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="112"/>
     </row>
     <row r="21" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A21" s="220" t="s">
+      <c r="A21" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="221"/>
-      <c r="C21" s="223"/>
-      <c r="D21" s="223"/>
-      <c r="E21" s="223"/>
-      <c r="F21" s="223"/>
-      <c r="G21" s="223"/>
-      <c r="H21" s="223"/>
-      <c r="I21" s="223"/>
-      <c r="J21" s="223"/>
-      <c r="K21" s="223"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="113"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="113"/>
     </row>
     <row r="22" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A22" s="196" t="s">
+      <c r="A22" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="197"/>
-      <c r="C22" s="224" t="s">
+      <c r="B22" s="98"/>
+      <c r="C22" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="225"/>
-      <c r="E22" s="200" t="s">
+      <c r="D22" s="115"/>
+      <c r="E22" s="116" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="201"/>
-      <c r="G22" s="201"/>
-      <c r="H22" s="201"/>
-      <c r="I22" s="201"/>
-      <c r="J22" s="201"/>
-      <c r="K22" s="202"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="118"/>
     </row>
     <row r="23" spans="1:16" s="1" customFormat="1" ht="24" hidden="1" customHeight="1" thickBot="1">
-      <c r="A23" s="196" t="s">
+      <c r="A23" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="197"/>
-      <c r="C23" s="198" t="s">
+      <c r="B23" s="98"/>
+      <c r="C23" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="199"/>
-      <c r="E23" s="200" t="s">
+      <c r="D23" s="123"/>
+      <c r="E23" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="201"/>
-      <c r="G23" s="201"/>
-      <c r="H23" s="201"/>
-      <c r="I23" s="201"/>
-      <c r="J23" s="201"/>
-      <c r="K23" s="202"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="118"/>
     </row>
     <row r="24" spans="1:16" ht="12" customHeight="1">
       <c r="P24" s="5"/>
@@ -7662,32 +7662,32 @@
       <c r="P25" s="5"/>
     </row>
     <row r="26" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="203" t="s">
+      <c r="A26" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="203"/>
-      <c r="C26" s="203"/>
-      <c r="D26" s="203"/>
-      <c r="E26" s="203"/>
-      <c r="F26" s="203"/>
-      <c r="G26" s="203"/>
-      <c r="H26" s="203"/>
-      <c r="I26" s="203"/>
-      <c r="J26" s="203"/>
-      <c r="K26" s="203"/>
+      <c r="B26" s="124"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="124"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="124"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="124"/>
+      <c r="I26" s="124"/>
+      <c r="J26" s="124"/>
+      <c r="K26" s="124"/>
     </row>
     <row r="27" spans="1:16" s="6" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A27" s="203"/>
-      <c r="B27" s="203"/>
-      <c r="C27" s="203"/>
-      <c r="D27" s="203"/>
-      <c r="E27" s="203"/>
-      <c r="F27" s="203"/>
-      <c r="G27" s="203"/>
-      <c r="H27" s="203"/>
-      <c r="I27" s="203"/>
-      <c r="J27" s="203"/>
-      <c r="K27" s="203"/>
+      <c r="A27" s="124"/>
+      <c r="B27" s="124"/>
+      <c r="C27" s="124"/>
+      <c r="D27" s="124"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="124"/>
+      <c r="G27" s="124"/>
+      <c r="H27" s="124"/>
+      <c r="I27" s="124"/>
+      <c r="J27" s="124"/>
+      <c r="K27" s="124"/>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
@@ -7695,19 +7695,19 @@
       <c r="P27" s="7"/>
     </row>
     <row r="28" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A28" s="204" t="s">
+      <c r="A28" s="125" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="204"/>
-      <c r="C28" s="204"/>
-      <c r="D28" s="204"/>
-      <c r="E28" s="204"/>
-      <c r="F28" s="204"/>
-      <c r="G28" s="204"/>
-      <c r="H28" s="204"/>
-      <c r="I28" s="204"/>
-      <c r="J28" s="204"/>
-      <c r="K28" s="204"/>
+      <c r="B28" s="125"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
+      <c r="I28" s="125"/>
+      <c r="J28" s="125"/>
+      <c r="K28" s="125"/>
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
@@ -7733,29 +7733,29 @@
       <c r="P29" s="7"/>
     </row>
     <row r="30" spans="1:16" s="6" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A30" s="205" t="s">
+      <c r="A30" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="206"/>
+      <c r="B30" s="127"/>
       <c r="C30" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="211" t="s">
+      <c r="D30" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="212"/>
-      <c r="F30" s="213"/>
-      <c r="G30" s="214" t="s">
+      <c r="E30" s="133"/>
+      <c r="F30" s="134"/>
+      <c r="G30" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="H30" s="206"/>
+      <c r="H30" s="127"/>
       <c r="I30" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="J30" s="217" t="s">
+      <c r="J30" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K30" s="218"/>
+      <c r="K30" s="139"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
@@ -7763,93 +7763,93 @@
       <c r="P30" s="7"/>
     </row>
     <row r="31" spans="1:16" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A31" s="207"/>
-      <c r="B31" s="208"/>
+      <c r="A31" s="128"/>
+      <c r="B31" s="129"/>
       <c r="C31" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="D31" s="183" t="s">
+      <c r="D31" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="219"/>
-      <c r="F31" s="184"/>
-      <c r="G31" s="215"/>
-      <c r="H31" s="208"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="142"/>
+      <c r="G31" s="136"/>
+      <c r="H31" s="129"/>
       <c r="I31" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="J31" s="183" t="s">
+      <c r="J31" s="140" t="s">
         <v>80</v>
       </c>
-      <c r="K31" s="184"/>
+      <c r="K31" s="142"/>
       <c r="P31" s="8"/>
     </row>
     <row r="32" spans="1:16" s="6" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A32" s="209"/>
-      <c r="B32" s="210"/>
+      <c r="A32" s="130"/>
+      <c r="B32" s="131"/>
       <c r="C32" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="185" t="s">
+      <c r="D32" s="153" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="186"/>
-      <c r="F32" s="187"/>
-      <c r="G32" s="216"/>
-      <c r="H32" s="210"/>
+      <c r="E32" s="154"/>
+      <c r="F32" s="155"/>
+      <c r="G32" s="137"/>
+      <c r="H32" s="131"/>
       <c r="I32" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="J32" s="188" t="s">
+      <c r="J32" s="156" t="s">
         <v>81</v>
       </c>
-      <c r="K32" s="189"/>
+      <c r="K32" s="157"/>
       <c r="P32" s="8"/>
     </row>
     <row r="33" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A33" s="190" t="s">
+      <c r="A33" s="158" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="190"/>
-      <c r="C33" s="191"/>
-      <c r="D33" s="191"/>
-      <c r="E33" s="191"/>
-      <c r="F33" s="191"/>
-      <c r="G33" s="191"/>
-      <c r="H33" s="191"/>
-      <c r="I33" s="191"/>
-      <c r="J33" s="191"/>
-      <c r="K33" s="191"/>
+      <c r="B33" s="158"/>
+      <c r="C33" s="159"/>
+      <c r="D33" s="159"/>
+      <c r="E33" s="159"/>
+      <c r="F33" s="159"/>
+      <c r="G33" s="159"/>
+      <c r="H33" s="159"/>
+      <c r="I33" s="159"/>
+      <c r="J33" s="159"/>
+      <c r="K33" s="159"/>
       <c r="P33" s="8"/>
     </row>
     <row r="34" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1">
-      <c r="A34" s="94"/>
-      <c r="B34" s="94"/>
-      <c r="C34" s="94"/>
-      <c r="D34" s="94"/>
-      <c r="E34" s="94"/>
-      <c r="F34" s="94"/>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="94"/>
-      <c r="K34" s="94"/>
+      <c r="A34" s="160"/>
+      <c r="B34" s="160"/>
+      <c r="C34" s="160"/>
+      <c r="D34" s="160"/>
+      <c r="E34" s="160"/>
+      <c r="F34" s="160"/>
+      <c r="G34" s="160"/>
+      <c r="H34" s="160"/>
+      <c r="I34" s="160"/>
+      <c r="J34" s="160"/>
+      <c r="K34" s="160"/>
       <c r="P34" s="8"/>
     </row>
     <row r="35" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A35" s="192" t="s">
+      <c r="A35" s="161" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="192"/>
-      <c r="C35" s="192"/>
-      <c r="D35" s="192"/>
-      <c r="E35" s="192"/>
-      <c r="F35" s="192"/>
-      <c r="G35" s="192"/>
-      <c r="H35" s="192"/>
-      <c r="I35" s="192"/>
-      <c r="J35" s="192"/>
-      <c r="K35" s="192"/>
+      <c r="B35" s="161"/>
+      <c r="C35" s="161"/>
+      <c r="D35" s="161"/>
+      <c r="E35" s="161"/>
+      <c r="F35" s="161"/>
+      <c r="G35" s="161"/>
+      <c r="H35" s="161"/>
+      <c r="I35" s="161"/>
+      <c r="J35" s="161"/>
+      <c r="K35" s="161"/>
       <c r="P35" s="8"/>
     </row>
     <row r="36" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
@@ -7867,61 +7867,61 @@
       <c r="P36" s="8"/>
     </row>
     <row r="37" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A37" s="176" t="s">
+      <c r="A37" s="143" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="156"/>
-      <c r="C37" s="177" t="s">
+      <c r="B37" s="144"/>
+      <c r="C37" s="145" t="s">
         <v>82</v>
       </c>
-      <c r="D37" s="178"/>
-      <c r="E37" s="178"/>
-      <c r="F37" s="178"/>
-      <c r="G37" s="177" t="s">
+      <c r="D37" s="146"/>
+      <c r="E37" s="146"/>
+      <c r="F37" s="146"/>
+      <c r="G37" s="145" t="s">
         <v>69</v>
       </c>
-      <c r="H37" s="179"/>
-      <c r="I37" s="180" t="s">
+      <c r="H37" s="147"/>
+      <c r="I37" s="148" t="s">
         <v>92</v>
       </c>
-      <c r="J37" s="181"/>
-      <c r="K37" s="182"/>
+      <c r="J37" s="149"/>
+      <c r="K37" s="150"/>
     </row>
     <row r="38" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A38" s="168" t="s">
+      <c r="A38" s="151" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="167"/>
-      <c r="C38" s="193" t="s">
+      <c r="B38" s="152"/>
+      <c r="C38" s="162" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="194"/>
-      <c r="E38" s="194"/>
-      <c r="F38" s="194"/>
-      <c r="G38" s="194"/>
-      <c r="H38" s="194"/>
-      <c r="I38" s="194"/>
-      <c r="J38" s="194"/>
-      <c r="K38" s="195"/>
+      <c r="D38" s="163"/>
+      <c r="E38" s="163"/>
+      <c r="F38" s="163"/>
+      <c r="G38" s="163"/>
+      <c r="H38" s="163"/>
+      <c r="I38" s="163"/>
+      <c r="J38" s="163"/>
+      <c r="K38" s="164"/>
       <c r="M38" s="12"/>
     </row>
     <row r="39" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A39" s="166" t="s">
+      <c r="A39" s="165" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="167"/>
+      <c r="B39" s="152"/>
       <c r="C39" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="171" t="s">
+      <c r="D39" s="168" t="s">
         <v>80</v>
       </c>
-      <c r="E39" s="171"/>
-      <c r="F39" s="171"/>
-      <c r="G39" s="171" t="s">
+      <c r="E39" s="168"/>
+      <c r="F39" s="168"/>
+      <c r="G39" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="H39" s="171"/>
+      <c r="H39" s="168"/>
       <c r="I39" s="25"/>
       <c r="J39" s="26" t="s">
         <v>32</v>
@@ -7931,75 +7931,75 @@
       <c r="N39" s="11"/>
     </row>
     <row r="40" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A40" s="168"/>
-      <c r="B40" s="167"/>
+      <c r="A40" s="151"/>
+      <c r="B40" s="152"/>
       <c r="C40" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D40" s="172"/>
-      <c r="E40" s="172"/>
-      <c r="F40" s="172"/>
-      <c r="G40" s="171" t="s">
+      <c r="D40" s="169"/>
+      <c r="E40" s="169"/>
+      <c r="F40" s="169"/>
+      <c r="G40" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="171"/>
-      <c r="I40" s="171"/>
-      <c r="J40" s="171"/>
-      <c r="K40" s="173"/>
+      <c r="H40" s="168"/>
+      <c r="I40" s="168"/>
+      <c r="J40" s="168"/>
+      <c r="K40" s="170"/>
     </row>
     <row r="41" spans="1:16" s="6" customFormat="1" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A41" s="169"/>
-      <c r="B41" s="170"/>
+      <c r="A41" s="166"/>
+      <c r="B41" s="167"/>
       <c r="C41" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="174" t="s">
+      <c r="D41" s="171" t="s">
         <v>85</v>
       </c>
-      <c r="E41" s="174"/>
-      <c r="F41" s="174"/>
-      <c r="G41" s="174" t="s">
+      <c r="E41" s="171"/>
+      <c r="F41" s="171"/>
+      <c r="G41" s="171" t="s">
         <v>9</v>
       </c>
-      <c r="H41" s="174"/>
-      <c r="I41" s="174" t="s">
+      <c r="H41" s="171"/>
+      <c r="I41" s="171" t="s">
         <v>86</v>
       </c>
-      <c r="J41" s="174"/>
-      <c r="K41" s="175"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="172"/>
     </row>
     <row r="42" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A42" s="153"/>
-      <c r="B42" s="153"/>
-      <c r="C42" s="153"/>
-      <c r="D42" s="153"/>
-      <c r="E42" s="153"/>
-      <c r="F42" s="153"/>
-      <c r="G42" s="153"/>
-      <c r="H42" s="153"/>
-      <c r="I42" s="153"/>
-      <c r="J42" s="153"/>
-      <c r="K42" s="153"/>
+      <c r="A42" s="179"/>
+      <c r="B42" s="179"/>
+      <c r="C42" s="179"/>
+      <c r="D42" s="179"/>
+      <c r="E42" s="179"/>
+      <c r="F42" s="179"/>
+      <c r="G42" s="179"/>
+      <c r="H42" s="179"/>
+      <c r="I42" s="179"/>
+      <c r="J42" s="179"/>
+      <c r="K42" s="179"/>
     </row>
     <row r="43" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A43" s="154" t="s">
+      <c r="A43" s="180" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="155"/>
+      <c r="B43" s="181"/>
       <c r="C43" s="29" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="48" t="s">
-        <v>364</v>
-      </c>
-      <c r="E43" s="155" t="s">
+        <v>363</v>
+      </c>
+      <c r="E43" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="F43" s="156"/>
-      <c r="G43" s="156" t="s">
+      <c r="F43" s="144"/>
+      <c r="G43" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="H43" s="156"/>
+      <c r="H43" s="144"/>
       <c r="I43" s="30" t="s">
         <v>74</v>
       </c>
@@ -8012,487 +8012,487 @@
       <c r="P43" s="8"/>
     </row>
     <row r="44" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A44" s="72" t="s">
+      <c r="A44" s="177" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="73"/>
+      <c r="B44" s="178"/>
       <c r="C44" s="26" t="s">
         <v>88</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>363</v>
-      </c>
-      <c r="E44" s="74" t="s">
+        <v>362</v>
+      </c>
+      <c r="E44" s="173" t="s">
         <v>89</v>
       </c>
-      <c r="F44" s="75"/>
-      <c r="G44" s="151" t="s">
+      <c r="F44" s="174"/>
+      <c r="G44" s="175" t="s">
         <v>91</v>
       </c>
-      <c r="H44" s="152"/>
-      <c r="I44" s="163" t="s">
+      <c r="H44" s="176"/>
+      <c r="I44" s="188" t="s">
         <v>73</v>
       </c>
-      <c r="J44" s="157" t="s">
+      <c r="J44" s="182" t="s">
         <v>90</v>
       </c>
-      <c r="K44" s="160" t="s">
+      <c r="K44" s="185" t="s">
         <v>40</v>
       </c>
       <c r="P44" s="8"/>
     </row>
     <row r="45" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A45" s="72" t="s">
+      <c r="A45" s="177" t="s">
+        <v>364</v>
+      </c>
+      <c r="B45" s="178"/>
+      <c r="C45" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="D45" s="32"/>
+      <c r="E45" s="173" t="s">
         <v>365</v>
       </c>
-      <c r="B45" s="73"/>
-      <c r="C45" s="26" t="s">
-        <v>367</v>
-      </c>
-      <c r="D45" s="32"/>
-      <c r="E45" s="74" t="s">
-        <v>366</v>
-      </c>
-      <c r="F45" s="75"/>
-      <c r="G45" s="151" t="s">
+      <c r="F45" s="174"/>
+      <c r="G45" s="175" t="s">
         <v>91</v>
       </c>
-      <c r="H45" s="152"/>
-      <c r="I45" s="164"/>
-      <c r="J45" s="158"/>
-      <c r="K45" s="161"/>
+      <c r="H45" s="176"/>
+      <c r="I45" s="189"/>
+      <c r="J45" s="183"/>
+      <c r="K45" s="186"/>
       <c r="P45" s="8"/>
     </row>
     <row r="46" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A46" s="72"/>
-      <c r="B46" s="73"/>
+      <c r="A46" s="177"/>
+      <c r="B46" s="178"/>
       <c r="C46" s="26"/>
       <c r="D46" s="32"/>
-      <c r="E46" s="74"/>
-      <c r="F46" s="75"/>
-      <c r="G46" s="151"/>
-      <c r="H46" s="152"/>
-      <c r="I46" s="164"/>
-      <c r="J46" s="158"/>
-      <c r="K46" s="161"/>
+      <c r="E46" s="173"/>
+      <c r="F46" s="174"/>
+      <c r="G46" s="175"/>
+      <c r="H46" s="176"/>
+      <c r="I46" s="189"/>
+      <c r="J46" s="183"/>
+      <c r="K46" s="186"/>
       <c r="P46" s="8"/>
     </row>
     <row r="47" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A47" s="72"/>
-      <c r="B47" s="73"/>
+      <c r="A47" s="177"/>
+      <c r="B47" s="178"/>
       <c r="C47" s="26"/>
       <c r="D47" s="32"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="151"/>
-      <c r="H47" s="152"/>
-      <c r="I47" s="164"/>
-      <c r="J47" s="158"/>
-      <c r="K47" s="161"/>
+      <c r="E47" s="173"/>
+      <c r="F47" s="174"/>
+      <c r="G47" s="175"/>
+      <c r="H47" s="176"/>
+      <c r="I47" s="189"/>
+      <c r="J47" s="183"/>
+      <c r="K47" s="186"/>
       <c r="P47" s="8"/>
     </row>
     <row r="48" spans="1:16" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A48" s="72"/>
-      <c r="B48" s="73"/>
+      <c r="A48" s="177"/>
+      <c r="B48" s="178"/>
       <c r="C48" s="26"/>
       <c r="D48" s="32"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="75"/>
-      <c r="G48" s="151"/>
-      <c r="H48" s="152"/>
-      <c r="I48" s="164"/>
-      <c r="J48" s="158"/>
-      <c r="K48" s="161"/>
+      <c r="E48" s="173"/>
+      <c r="F48" s="174"/>
+      <c r="G48" s="175"/>
+      <c r="H48" s="176"/>
+      <c r="I48" s="189"/>
+      <c r="J48" s="183"/>
+      <c r="K48" s="186"/>
       <c r="P48" s="8"/>
     </row>
     <row r="49" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A49" s="72"/>
-      <c r="B49" s="73"/>
+      <c r="A49" s="177"/>
+      <c r="B49" s="178"/>
       <c r="C49" s="26"/>
       <c r="D49" s="32"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="75"/>
-      <c r="G49" s="151"/>
-      <c r="H49" s="152"/>
-      <c r="I49" s="164"/>
-      <c r="J49" s="158"/>
-      <c r="K49" s="161"/>
+      <c r="E49" s="173"/>
+      <c r="F49" s="174"/>
+      <c r="G49" s="175"/>
+      <c r="H49" s="176"/>
+      <c r="I49" s="189"/>
+      <c r="J49" s="183"/>
+      <c r="K49" s="186"/>
       <c r="P49" s="8"/>
     </row>
     <row r="50" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A50" s="72"/>
-      <c r="B50" s="73"/>
+      <c r="A50" s="177"/>
+      <c r="B50" s="178"/>
       <c r="C50" s="26"/>
       <c r="D50" s="32"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="75"/>
-      <c r="G50" s="151"/>
-      <c r="H50" s="152"/>
-      <c r="I50" s="164"/>
-      <c r="J50" s="158"/>
-      <c r="K50" s="161"/>
+      <c r="E50" s="173"/>
+      <c r="F50" s="174"/>
+      <c r="G50" s="175"/>
+      <c r="H50" s="176"/>
+      <c r="I50" s="189"/>
+      <c r="J50" s="183"/>
+      <c r="K50" s="186"/>
       <c r="P50" s="8"/>
     </row>
     <row r="51" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A51" s="72"/>
-      <c r="B51" s="73"/>
+      <c r="A51" s="177"/>
+      <c r="B51" s="178"/>
       <c r="C51" s="26"/>
       <c r="D51" s="32"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="75"/>
-      <c r="G51" s="151"/>
-      <c r="H51" s="152"/>
-      <c r="I51" s="164"/>
-      <c r="J51" s="158"/>
-      <c r="K51" s="161"/>
+      <c r="E51" s="173"/>
+      <c r="F51" s="174"/>
+      <c r="G51" s="175"/>
+      <c r="H51" s="176"/>
+      <c r="I51" s="189"/>
+      <c r="J51" s="183"/>
+      <c r="K51" s="186"/>
       <c r="P51" s="8"/>
     </row>
     <row r="52" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A52" s="72"/>
-      <c r="B52" s="73"/>
+      <c r="A52" s="177"/>
+      <c r="B52" s="178"/>
       <c r="C52" s="26"/>
       <c r="D52" s="32"/>
-      <c r="E52" s="74"/>
-      <c r="F52" s="75"/>
-      <c r="G52" s="151"/>
-      <c r="H52" s="152"/>
-      <c r="I52" s="164"/>
-      <c r="J52" s="158"/>
-      <c r="K52" s="161"/>
+      <c r="E52" s="173"/>
+      <c r="F52" s="174"/>
+      <c r="G52" s="175"/>
+      <c r="H52" s="176"/>
+      <c r="I52" s="189"/>
+      <c r="J52" s="183"/>
+      <c r="K52" s="186"/>
       <c r="P52" s="8"/>
     </row>
     <row r="53" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A53" s="72"/>
-      <c r="B53" s="73"/>
+      <c r="A53" s="177"/>
+      <c r="B53" s="178"/>
       <c r="C53" s="26"/>
       <c r="D53" s="32"/>
-      <c r="E53" s="74"/>
-      <c r="F53" s="75"/>
-      <c r="G53" s="151"/>
-      <c r="H53" s="152"/>
-      <c r="I53" s="164"/>
-      <c r="J53" s="158"/>
-      <c r="K53" s="161"/>
+      <c r="E53" s="173"/>
+      <c r="F53" s="174"/>
+      <c r="G53" s="175"/>
+      <c r="H53" s="176"/>
+      <c r="I53" s="189"/>
+      <c r="J53" s="183"/>
+      <c r="K53" s="186"/>
       <c r="P53" s="8"/>
     </row>
     <row r="54" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A54" s="72"/>
-      <c r="B54" s="73"/>
+      <c r="A54" s="177"/>
+      <c r="B54" s="178"/>
       <c r="C54" s="33"/>
       <c r="D54" s="32"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="75"/>
-      <c r="G54" s="151"/>
-      <c r="H54" s="152"/>
-      <c r="I54" s="164"/>
-      <c r="J54" s="158"/>
-      <c r="K54" s="161"/>
+      <c r="E54" s="173"/>
+      <c r="F54" s="174"/>
+      <c r="G54" s="175"/>
+      <c r="H54" s="176"/>
+      <c r="I54" s="189"/>
+      <c r="J54" s="183"/>
+      <c r="K54" s="186"/>
       <c r="P54" s="8"/>
     </row>
     <row r="55" spans="1:20" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A55" s="72"/>
-      <c r="B55" s="73"/>
+      <c r="A55" s="177"/>
+      <c r="B55" s="178"/>
       <c r="C55" s="24"/>
       <c r="D55" s="32"/>
-      <c r="E55" s="74"/>
-      <c r="F55" s="75"/>
-      <c r="G55" s="151"/>
-      <c r="H55" s="152"/>
-      <c r="I55" s="165"/>
-      <c r="J55" s="159"/>
-      <c r="K55" s="162"/>
-      <c r="N55" s="148"/>
-      <c r="O55" s="148"/>
-      <c r="P55" s="148"/>
-      <c r="Q55" s="148"/>
-      <c r="R55" s="148"/>
-      <c r="S55" s="148"/>
-      <c r="T55" s="148"/>
+      <c r="E55" s="173"/>
+      <c r="F55" s="174"/>
+      <c r="G55" s="175"/>
+      <c r="H55" s="176"/>
+      <c r="I55" s="190"/>
+      <c r="J55" s="184"/>
+      <c r="K55" s="187"/>
+      <c r="N55" s="191"/>
+      <c r="O55" s="191"/>
+      <c r="P55" s="191"/>
+      <c r="Q55" s="191"/>
+      <c r="R55" s="191"/>
+      <c r="S55" s="191"/>
+      <c r="T55" s="191"/>
     </row>
     <row r="56" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A56" s="149" t="s">
+      <c r="A56" s="192" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="150"/>
-      <c r="C56" s="135" t="s">
-        <v>357</v>
-      </c>
-      <c r="D56" s="136"/>
-      <c r="E56" s="136"/>
-      <c r="F56" s="136"/>
-      <c r="G56" s="136"/>
-      <c r="H56" s="136"/>
-      <c r="I56" s="136"/>
-      <c r="J56" s="136"/>
-      <c r="K56" s="137"/>
+      <c r="B56" s="193"/>
+      <c r="C56" s="194" t="s">
+        <v>367</v>
+      </c>
+      <c r="D56" s="195"/>
+      <c r="E56" s="195"/>
+      <c r="F56" s="195"/>
+      <c r="G56" s="195"/>
+      <c r="H56" s="195"/>
+      <c r="I56" s="195"/>
+      <c r="J56" s="195"/>
+      <c r="K56" s="196"/>
       <c r="P56" s="8"/>
     </row>
     <row r="57" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A57" s="133" t="s">
+      <c r="A57" s="216" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="134"/>
-      <c r="C57" s="135"/>
-      <c r="D57" s="136"/>
-      <c r="E57" s="136"/>
-      <c r="F57" s="136"/>
-      <c r="G57" s="136"/>
-      <c r="H57" s="136"/>
-      <c r="I57" s="136"/>
-      <c r="J57" s="136"/>
-      <c r="K57" s="137"/>
+      <c r="B57" s="217"/>
+      <c r="C57" s="194"/>
+      <c r="D57" s="195"/>
+      <c r="E57" s="195"/>
+      <c r="F57" s="195"/>
+      <c r="G57" s="195"/>
+      <c r="H57" s="195"/>
+      <c r="I57" s="195"/>
+      <c r="J57" s="195"/>
+      <c r="K57" s="196"/>
       <c r="M57" s="9"/>
     </row>
     <row r="58" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A58" s="133"/>
-      <c r="B58" s="134"/>
-      <c r="C58" s="135"/>
-      <c r="D58" s="136"/>
-      <c r="E58" s="136"/>
-      <c r="F58" s="136"/>
-      <c r="G58" s="136"/>
-      <c r="H58" s="136"/>
-      <c r="I58" s="136"/>
-      <c r="J58" s="136"/>
-      <c r="K58" s="137"/>
+      <c r="A58" s="216"/>
+      <c r="B58" s="217"/>
+      <c r="C58" s="194"/>
+      <c r="D58" s="195"/>
+      <c r="E58" s="195"/>
+      <c r="F58" s="195"/>
+      <c r="G58" s="195"/>
+      <c r="H58" s="195"/>
+      <c r="I58" s="195"/>
+      <c r="J58" s="195"/>
+      <c r="K58" s="196"/>
     </row>
     <row r="59" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A59" s="138" t="s">
+      <c r="A59" s="218" t="s">
         <v>71</v>
       </c>
-      <c r="B59" s="139"/>
-      <c r="C59" s="140" t="s">
+      <c r="B59" s="219"/>
+      <c r="C59" s="220" t="s">
         <v>77</v>
       </c>
-      <c r="D59" s="141"/>
-      <c r="E59" s="141"/>
-      <c r="F59" s="141"/>
-      <c r="G59" s="141"/>
-      <c r="H59" s="141"/>
-      <c r="I59" s="141"/>
-      <c r="J59" s="141"/>
-      <c r="K59" s="142"/>
+      <c r="D59" s="221"/>
+      <c r="E59" s="221"/>
+      <c r="F59" s="221"/>
+      <c r="G59" s="221"/>
+      <c r="H59" s="221"/>
+      <c r="I59" s="221"/>
+      <c r="J59" s="221"/>
+      <c r="K59" s="222"/>
     </row>
     <row r="60" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A60" s="143" t="s">
+      <c r="A60" s="223" t="s">
         <v>21</v>
       </c>
-      <c r="B60" s="144"/>
-      <c r="C60" s="140" t="s">
-        <v>359</v>
-      </c>
-      <c r="D60" s="141"/>
-      <c r="E60" s="141"/>
-      <c r="F60" s="141"/>
-      <c r="G60" s="141"/>
-      <c r="H60" s="141"/>
-      <c r="I60" s="141"/>
-      <c r="J60" s="141"/>
-      <c r="K60" s="142"/>
+      <c r="B60" s="224"/>
+      <c r="C60" s="220" t="s">
+        <v>358</v>
+      </c>
+      <c r="D60" s="221"/>
+      <c r="E60" s="221"/>
+      <c r="F60" s="221"/>
+      <c r="G60" s="221"/>
+      <c r="H60" s="221"/>
+      <c r="I60" s="221"/>
+      <c r="J60" s="221"/>
+      <c r="K60" s="222"/>
     </row>
     <row r="61" spans="1:20" s="6" customFormat="1" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A61" s="103"/>
-      <c r="B61" s="104"/>
-      <c r="C61" s="145"/>
-      <c r="D61" s="146"/>
-      <c r="E61" s="146"/>
-      <c r="F61" s="146"/>
-      <c r="G61" s="146"/>
-      <c r="H61" s="146"/>
-      <c r="I61" s="146"/>
-      <c r="J61" s="146"/>
-      <c r="K61" s="147"/>
+      <c r="A61" s="225"/>
+      <c r="B61" s="226"/>
+      <c r="C61" s="227"/>
+      <c r="D61" s="228"/>
+      <c r="E61" s="228"/>
+      <c r="F61" s="228"/>
+      <c r="G61" s="228"/>
+      <c r="H61" s="228"/>
+      <c r="I61" s="228"/>
+      <c r="J61" s="228"/>
+      <c r="K61" s="229"/>
     </row>
     <row r="62" spans="1:20" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A62" s="94"/>
-      <c r="B62" s="94"/>
-      <c r="C62" s="94"/>
-      <c r="D62" s="94"/>
-      <c r="E62" s="94"/>
-      <c r="F62" s="94"/>
-      <c r="G62" s="94"/>
-      <c r="H62" s="94"/>
-      <c r="I62" s="94"/>
-      <c r="J62" s="94"/>
-      <c r="K62" s="94"/>
+      <c r="A62" s="160"/>
+      <c r="B62" s="160"/>
+      <c r="C62" s="160"/>
+      <c r="D62" s="160"/>
+      <c r="E62" s="160"/>
+      <c r="F62" s="160"/>
+      <c r="G62" s="160"/>
+      <c r="H62" s="160"/>
+      <c r="I62" s="160"/>
+      <c r="J62" s="160"/>
+      <c r="K62" s="160"/>
       <c r="P62" s="8"/>
     </row>
     <row r="63" spans="1:20" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="114" t="s">
+      <c r="A63" s="197" t="s">
         <v>43</v>
       </c>
-      <c r="B63" s="115"/>
-      <c r="C63" s="122" t="s">
+      <c r="B63" s="198"/>
+      <c r="C63" s="205" t="s">
         <v>78</v>
       </c>
-      <c r="D63" s="123"/>
-      <c r="E63" s="123"/>
-      <c r="F63" s="123"/>
-      <c r="G63" s="123"/>
-      <c r="H63" s="123"/>
-      <c r="I63" s="123"/>
-      <c r="J63" s="123"/>
-      <c r="K63" s="124"/>
+      <c r="D63" s="206"/>
+      <c r="E63" s="206"/>
+      <c r="F63" s="206"/>
+      <c r="G63" s="206"/>
+      <c r="H63" s="206"/>
+      <c r="I63" s="206"/>
+      <c r="J63" s="206"/>
+      <c r="K63" s="207"/>
       <c r="P63" s="8"/>
     </row>
     <row r="64" spans="1:20" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="116"/>
-      <c r="B64" s="117"/>
-      <c r="C64" s="125" t="s">
+      <c r="A64" s="199"/>
+      <c r="B64" s="200"/>
+      <c r="C64" s="208" t="s">
         <v>44</v>
       </c>
-      <c r="D64" s="126"/>
-      <c r="E64" s="126"/>
-      <c r="F64" s="126"/>
-      <c r="G64" s="126"/>
-      <c r="H64" s="126"/>
-      <c r="I64" s="126"/>
-      <c r="J64" s="126"/>
-      <c r="K64" s="127"/>
+      <c r="D64" s="209"/>
+      <c r="E64" s="209"/>
+      <c r="F64" s="209"/>
+      <c r="G64" s="209"/>
+      <c r="H64" s="209"/>
+      <c r="I64" s="209"/>
+      <c r="J64" s="209"/>
+      <c r="K64" s="210"/>
       <c r="P64" s="8"/>
     </row>
     <row r="65" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="116"/>
-      <c r="B65" s="117"/>
-      <c r="C65" s="128" t="s">
+      <c r="A65" s="199"/>
+      <c r="B65" s="200"/>
+      <c r="C65" s="211" t="s">
         <v>45</v>
       </c>
-      <c r="D65" s="128"/>
-      <c r="E65" s="128"/>
-      <c r="F65" s="128"/>
-      <c r="G65" s="128"/>
-      <c r="H65" s="128"/>
-      <c r="I65" s="128"/>
-      <c r="J65" s="128"/>
-      <c r="K65" s="129"/>
+      <c r="D65" s="211"/>
+      <c r="E65" s="211"/>
+      <c r="F65" s="211"/>
+      <c r="G65" s="211"/>
+      <c r="H65" s="211"/>
+      <c r="I65" s="211"/>
+      <c r="J65" s="211"/>
+      <c r="K65" s="212"/>
       <c r="P65" s="8"/>
     </row>
     <row r="66" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="118"/>
-      <c r="B66" s="119"/>
-      <c r="C66" s="128" t="s">
+      <c r="A66" s="201"/>
+      <c r="B66" s="202"/>
+      <c r="C66" s="211" t="s">
         <v>46</v>
       </c>
-      <c r="D66" s="128"/>
-      <c r="E66" s="128"/>
-      <c r="F66" s="128"/>
-      <c r="G66" s="128"/>
-      <c r="H66" s="128"/>
-      <c r="I66" s="128"/>
-      <c r="J66" s="128"/>
-      <c r="K66" s="129"/>
+      <c r="D66" s="211"/>
+      <c r="E66" s="211"/>
+      <c r="F66" s="211"/>
+      <c r="G66" s="211"/>
+      <c r="H66" s="211"/>
+      <c r="I66" s="211"/>
+      <c r="J66" s="211"/>
+      <c r="K66" s="212"/>
       <c r="P66" s="8"/>
     </row>
     <row r="67" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A67" s="120"/>
-      <c r="B67" s="121"/>
-      <c r="C67" s="130" t="s">
+      <c r="A67" s="203"/>
+      <c r="B67" s="204"/>
+      <c r="C67" s="213" t="s">
         <v>47</v>
       </c>
-      <c r="D67" s="131"/>
-      <c r="E67" s="131"/>
-      <c r="F67" s="131"/>
-      <c r="G67" s="131"/>
-      <c r="H67" s="131"/>
-      <c r="I67" s="131"/>
-      <c r="J67" s="131"/>
-      <c r="K67" s="132"/>
+      <c r="D67" s="214"/>
+      <c r="E67" s="214"/>
+      <c r="F67" s="214"/>
+      <c r="G67" s="214"/>
+      <c r="H67" s="214"/>
+      <c r="I67" s="214"/>
+      <c r="J67" s="214"/>
+      <c r="K67" s="215"/>
       <c r="P67" s="8"/>
     </row>
     <row r="68" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A68" s="94"/>
-      <c r="B68" s="94"/>
-      <c r="C68" s="94"/>
-      <c r="D68" s="94"/>
-      <c r="E68" s="94"/>
-      <c r="F68" s="94"/>
-      <c r="G68" s="94"/>
-      <c r="H68" s="94"/>
-      <c r="I68" s="94"/>
-      <c r="J68" s="94"/>
-      <c r="K68" s="94"/>
+      <c r="A68" s="160"/>
+      <c r="B68" s="160"/>
+      <c r="C68" s="160"/>
+      <c r="D68" s="160"/>
+      <c r="E68" s="160"/>
+      <c r="F68" s="160"/>
+      <c r="G68" s="160"/>
+      <c r="H68" s="160"/>
+      <c r="I68" s="160"/>
+      <c r="J68" s="160"/>
+      <c r="K68" s="160"/>
     </row>
     <row r="69" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A69" s="95" t="s">
+      <c r="A69" s="248" t="s">
         <v>48</v>
       </c>
-      <c r="B69" s="96"/>
-      <c r="C69" s="97" t="s">
+      <c r="B69" s="249"/>
+      <c r="C69" s="250" t="s">
         <v>76</v>
       </c>
-      <c r="D69" s="97"/>
-      <c r="E69" s="97"/>
-      <c r="F69" s="97"/>
-      <c r="G69" s="97"/>
-      <c r="H69" s="97"/>
-      <c r="I69" s="97"/>
-      <c r="J69" s="97"/>
-      <c r="K69" s="98"/>
+      <c r="D69" s="250"/>
+      <c r="E69" s="250"/>
+      <c r="F69" s="250"/>
+      <c r="G69" s="250"/>
+      <c r="H69" s="250"/>
+      <c r="I69" s="250"/>
+      <c r="J69" s="250"/>
+      <c r="K69" s="251"/>
       <c r="P69" s="8"/>
     </row>
     <row r="70" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
-      <c r="A70" s="94"/>
-      <c r="B70" s="94"/>
-      <c r="C70" s="94"/>
-      <c r="D70" s="94"/>
-      <c r="E70" s="94"/>
-      <c r="F70" s="94"/>
-      <c r="G70" s="94"/>
-      <c r="H70" s="94"/>
-      <c r="I70" s="94"/>
-      <c r="J70" s="94"/>
-      <c r="K70" s="94"/>
+      <c r="A70" s="160"/>
+      <c r="B70" s="160"/>
+      <c r="C70" s="160"/>
+      <c r="D70" s="160"/>
+      <c r="E70" s="160"/>
+      <c r="F70" s="160"/>
+      <c r="G70" s="160"/>
+      <c r="H70" s="160"/>
+      <c r="I70" s="160"/>
+      <c r="J70" s="160"/>
+      <c r="K70" s="160"/>
     </row>
     <row r="71" spans="1:16" s="6" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="99" t="s">
+      <c r="A71" s="252" t="s">
         <v>49</v>
       </c>
-      <c r="B71" s="100"/>
-      <c r="C71" s="105" t="s">
+      <c r="B71" s="253"/>
+      <c r="C71" s="256" t="s">
         <v>50</v>
       </c>
-      <c r="D71" s="105"/>
-      <c r="E71" s="105"/>
-      <c r="F71" s="105"/>
-      <c r="G71" s="105"/>
-      <c r="H71" s="105"/>
-      <c r="I71" s="105"/>
-      <c r="J71" s="105"/>
-      <c r="K71" s="106"/>
+      <c r="D71" s="256"/>
+      <c r="E71" s="256"/>
+      <c r="F71" s="256"/>
+      <c r="G71" s="256"/>
+      <c r="H71" s="256"/>
+      <c r="I71" s="256"/>
+      <c r="J71" s="256"/>
+      <c r="K71" s="257"/>
     </row>
     <row r="72" spans="1:16" s="6" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A72" s="101"/>
-      <c r="B72" s="102"/>
-      <c r="C72" s="107" t="s">
+      <c r="A72" s="254"/>
+      <c r="B72" s="255"/>
+      <c r="C72" s="258" t="s">
         <v>51</v>
       </c>
-      <c r="D72" s="107"/>
-      <c r="E72" s="107"/>
-      <c r="F72" s="107"/>
-      <c r="G72" s="107"/>
-      <c r="H72" s="107"/>
-      <c r="I72" s="107"/>
-      <c r="J72" s="107"/>
-      <c r="K72" s="108"/>
+      <c r="D72" s="258"/>
+      <c r="E72" s="258"/>
+      <c r="F72" s="258"/>
+      <c r="G72" s="258"/>
+      <c r="H72" s="258"/>
+      <c r="I72" s="258"/>
+      <c r="J72" s="258"/>
+      <c r="K72" s="259"/>
     </row>
     <row r="73" spans="1:16" s="6" customFormat="1" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A73" s="103"/>
-      <c r="B73" s="104"/>
+      <c r="A73" s="225"/>
+      <c r="B73" s="226"/>
       <c r="C73" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D73" s="109" t="s">
+      <c r="D73" s="260" t="s">
         <v>53</v>
       </c>
-      <c r="E73" s="110"/>
-      <c r="F73" s="111"/>
-      <c r="G73" s="112" t="s">
+      <c r="E73" s="261"/>
+      <c r="F73" s="262"/>
+      <c r="G73" s="263" t="s">
         <v>9</v>
       </c>
-      <c r="H73" s="112"/>
-      <c r="I73" s="112"/>
-      <c r="J73" s="112"/>
-      <c r="K73" s="113"/>
+      <c r="H73" s="263"/>
+      <c r="I73" s="263"/>
+      <c r="J73" s="263"/>
+      <c r="K73" s="264"/>
     </row>
     <row r="74" spans="1:16" s="6" customFormat="1" ht="6.95" customHeight="1" thickBot="1">
       <c r="A74" s="35"/>
@@ -8508,53 +8508,53 @@
       <c r="K74" s="35"/>
     </row>
     <row r="75" spans="1:16" ht="25.15" customHeight="1">
-      <c r="A75" s="76" t="s">
-        <v>358</v>
-      </c>
-      <c r="B75" s="77"/>
-      <c r="C75" s="77"/>
-      <c r="D75" s="77"/>
-      <c r="E75" s="77"/>
-      <c r="F75" s="77"/>
-      <c r="G75" s="77"/>
-      <c r="H75" s="77"/>
-      <c r="I75" s="77"/>
-      <c r="J75" s="77"/>
-      <c r="K75" s="78"/>
+      <c r="A75" s="230" t="s">
+        <v>357</v>
+      </c>
+      <c r="B75" s="231"/>
+      <c r="C75" s="231"/>
+      <c r="D75" s="231"/>
+      <c r="E75" s="231"/>
+      <c r="F75" s="231"/>
+      <c r="G75" s="231"/>
+      <c r="H75" s="231"/>
+      <c r="I75" s="231"/>
+      <c r="J75" s="231"/>
+      <c r="K75" s="232"/>
     </row>
     <row r="76" spans="1:16" s="6" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A76" s="79" t="s">
+      <c r="A76" s="233" t="s">
         <v>356</v>
       </c>
-      <c r="B76" s="80"/>
-      <c r="C76" s="81"/>
-      <c r="D76" s="85" t="s">
+      <c r="B76" s="234"/>
+      <c r="C76" s="235"/>
+      <c r="D76" s="239" t="s">
         <v>72</v>
       </c>
-      <c r="E76" s="86"/>
-      <c r="F76" s="86"/>
-      <c r="G76" s="86"/>
-      <c r="H76" s="89" t="s">
+      <c r="E76" s="240"/>
+      <c r="F76" s="240"/>
+      <c r="G76" s="240"/>
+      <c r="H76" s="243" t="s">
         <v>354</v>
       </c>
-      <c r="I76" s="89"/>
-      <c r="J76" s="91" t="s">
+      <c r="I76" s="243"/>
+      <c r="J76" s="245" t="s">
         <v>355</v>
       </c>
-      <c r="K76" s="92"/>
+      <c r="K76" s="246"/>
     </row>
     <row r="77" spans="1:16" s="6" customFormat="1" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A77" s="82"/>
-      <c r="B77" s="83"/>
-      <c r="C77" s="84"/>
-      <c r="D77" s="87"/>
-      <c r="E77" s="88"/>
-      <c r="F77" s="88"/>
-      <c r="G77" s="88"/>
-      <c r="H77" s="90"/>
-      <c r="I77" s="90"/>
-      <c r="J77" s="87"/>
-      <c r="K77" s="93"/>
+      <c r="A77" s="236"/>
+      <c r="B77" s="237"/>
+      <c r="C77" s="238"/>
+      <c r="D77" s="241"/>
+      <c r="E77" s="242"/>
+      <c r="F77" s="242"/>
+      <c r="G77" s="242"/>
+      <c r="H77" s="244"/>
+      <c r="I77" s="244"/>
+      <c r="J77" s="241"/>
+      <c r="K77" s="247"/>
     </row>
     <row r="78" spans="1:16">
       <c r="D78" s="5" t="s">
@@ -8563,87 +8563,58 @@
     </row>
   </sheetData>
   <mergeCells count="157">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="C9:K9"/>
-    <mergeCell ref="C10:K10"/>
-    <mergeCell ref="C11:K11"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:K20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:K21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:K22"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:K17"/>
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:K19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:K23"/>
-    <mergeCell ref="A26:K27"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A30:B32"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:H32"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="C38:K38"/>
-    <mergeCell ref="A39:B41"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A76:C77"/>
+    <mergeCell ref="D76:G77"/>
+    <mergeCell ref="H76:I77"/>
+    <mergeCell ref="J76:K77"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:K69"/>
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A71:B73"/>
+    <mergeCell ref="C71:K71"/>
+    <mergeCell ref="C72:K72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="A62:K62"/>
+    <mergeCell ref="A63:B67"/>
+    <mergeCell ref="C63:K63"/>
+    <mergeCell ref="C64:K64"/>
+    <mergeCell ref="C65:K65"/>
+    <mergeCell ref="C66:K66"/>
+    <mergeCell ref="C67:K67"/>
+    <mergeCell ref="A57:B58"/>
+    <mergeCell ref="C57:K57"/>
+    <mergeCell ref="C58:K58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:K59"/>
+    <mergeCell ref="A60:B61"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="C61:K61"/>
+    <mergeCell ref="N55:T55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:K56"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G55:H55"/>
     <mergeCell ref="E50:F50"/>
     <mergeCell ref="G50:H50"/>
     <mergeCell ref="A51:B51"/>
@@ -8668,58 +8639,87 @@
     <mergeCell ref="G47:H47"/>
     <mergeCell ref="G48:H48"/>
     <mergeCell ref="G49:H49"/>
-    <mergeCell ref="N55:T55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:K56"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="A62:K62"/>
-    <mergeCell ref="A63:B67"/>
-    <mergeCell ref="C63:K63"/>
-    <mergeCell ref="C64:K64"/>
-    <mergeCell ref="C65:K65"/>
-    <mergeCell ref="C66:K66"/>
-    <mergeCell ref="C67:K67"/>
-    <mergeCell ref="A57:B58"/>
-    <mergeCell ref="C57:K57"/>
-    <mergeCell ref="C58:K58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C59:K59"/>
-    <mergeCell ref="A60:B61"/>
-    <mergeCell ref="C60:K60"/>
-    <mergeCell ref="C61:K61"/>
-    <mergeCell ref="A75:K75"/>
-    <mergeCell ref="A76:C77"/>
-    <mergeCell ref="D76:G77"/>
-    <mergeCell ref="H76:I77"/>
-    <mergeCell ref="J76:K77"/>
-    <mergeCell ref="A68:K68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:K69"/>
-    <mergeCell ref="A70:K70"/>
-    <mergeCell ref="A71:B73"/>
-    <mergeCell ref="C71:K71"/>
-    <mergeCell ref="C72:K72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="A39:B41"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="C38:K38"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:K23"/>
+    <mergeCell ref="A26:K27"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A30:B32"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:H32"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:K21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:K22"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:K17"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:K19"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="C9:K9"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:K2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
@@ -8759,79 +8759,79 @@
   <sheetData>
     <row r="1" spans="2:14" ht="41.25" customHeight="1"/>
     <row r="2" spans="2:14" ht="33.950000000000003" customHeight="1">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="60" t="s">
         <v>349</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="51"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="62"/>
     </row>
     <row r="3" spans="2:14" ht="21" customHeight="1">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="63" t="s">
         <v>350</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="54" t="s">
+      <c r="C3" s="64"/>
+      <c r="D3" s="65" t="s">
         <v>351</v>
       </c>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="56"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
       <c r="H3" s="38"/>
       <c r="I3" s="37" t="s">
         <v>291</v>
       </c>
-      <c r="J3" s="57" t="s">
+      <c r="J3" s="68" t="s">
         <v>352</v>
       </c>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
       <c r="N3" s="40"/>
     </row>
     <row r="4" spans="2:14" ht="21.95" customHeight="1">
       <c r="B4" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="60"/>
-      <c r="E4" s="59" t="s">
+      <c r="D4" s="71"/>
+      <c r="E4" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="F4" s="60"/>
+      <c r="F4" s="71"/>
       <c r="G4" s="42" t="s">
         <v>96</v>
       </c>
       <c r="H4" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="I4" s="59" t="s">
+      <c r="I4" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="J4" s="60"/>
-      <c r="K4" s="59" t="s">
+      <c r="J4" s="71"/>
+      <c r="K4" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="L4" s="60"/>
+      <c r="L4" s="71"/>
       <c r="M4" s="42" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="21" customHeight="1">
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="62"/>
+      <c r="C5" s="56"/>
       <c r="D5" s="42" t="s">
         <v>102</v>
       </c>
@@ -8844,10 +8844,10 @@
       <c r="G5" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="H5" s="61" t="s">
+      <c r="H5" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="I5" s="62"/>
+      <c r="I5" s="56"/>
       <c r="J5" s="42" t="s">
         <v>102</v>
       </c>
@@ -8875,7 +8875,7 @@
       <c r="F6" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G6" s="63" t="s">
+      <c r="G6" s="57" t="s">
         <v>111</v>
       </c>
       <c r="H6" s="41" t="s">
@@ -8891,7 +8891,7 @@
       <c r="L6" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M6" s="63" t="s">
+      <c r="M6" s="57" t="s">
         <v>115</v>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       <c r="F7" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="64"/>
+      <c r="G7" s="58"/>
       <c r="H7" s="41" t="s">
         <v>119</v>
       </c>
@@ -8923,7 +8923,7 @@
       <c r="L7" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M7" s="64"/>
+      <c r="M7" s="58"/>
     </row>
     <row r="8" spans="2:14" ht="21" customHeight="1">
       <c r="B8" s="41" t="s">
@@ -8939,7 +8939,7 @@
       <c r="F8" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G8" s="64"/>
+      <c r="G8" s="58"/>
       <c r="H8" s="41" t="s">
         <v>123</v>
       </c>
@@ -8953,7 +8953,7 @@
       <c r="L8" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M8" s="64"/>
+      <c r="M8" s="58"/>
     </row>
     <row r="9" spans="2:14" ht="21" customHeight="1">
       <c r="B9" s="41" t="s">
@@ -8969,7 +8969,7 @@
       <c r="F9" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G9" s="64"/>
+      <c r="G9" s="58"/>
       <c r="H9" s="41" t="s">
         <v>128</v>
       </c>
@@ -8985,7 +8985,7 @@
       <c r="L9" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="M9" s="64"/>
+      <c r="M9" s="58"/>
     </row>
     <row r="10" spans="2:14" ht="21" customHeight="1">
       <c r="B10" s="41" t="s">
@@ -9001,7 +9001,7 @@
       <c r="F10" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="64"/>
+      <c r="G10" s="58"/>
       <c r="H10" s="41" t="s">
         <v>135</v>
       </c>
@@ -9015,7 +9015,7 @@
       <c r="L10" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M10" s="64"/>
+      <c r="M10" s="58"/>
     </row>
     <row r="11" spans="2:14" ht="21" customHeight="1">
       <c r="B11" s="41" t="s">
@@ -9031,7 +9031,7 @@
       <c r="F11" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="64"/>
+      <c r="G11" s="58"/>
       <c r="H11" s="41" t="s">
         <v>139</v>
       </c>
@@ -9045,7 +9045,7 @@
       <c r="L11" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M11" s="64"/>
+      <c r="M11" s="58"/>
     </row>
     <row r="12" spans="2:14" ht="21" customHeight="1">
       <c r="B12" s="41" t="s">
@@ -9061,7 +9061,7 @@
       <c r="F12" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G12" s="64"/>
+      <c r="G12" s="58"/>
       <c r="H12" s="41" t="s">
         <v>143</v>
       </c>
@@ -9075,7 +9075,7 @@
       <c r="L12" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M12" s="65"/>
+      <c r="M12" s="59"/>
     </row>
     <row r="13" spans="2:14" ht="21" customHeight="1">
       <c r="B13" s="41" t="s">
@@ -9091,11 +9091,11 @@
       <c r="F13" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G13" s="64"/>
-      <c r="H13" s="61" t="s">
+      <c r="G13" s="58"/>
+      <c r="H13" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="I13" s="62"/>
+      <c r="I13" s="56"/>
       <c r="J13" s="42"/>
       <c r="K13" s="42" t="s">
         <v>103</v>
@@ -9121,7 +9121,7 @@
       <c r="F14" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="65"/>
+      <c r="G14" s="59"/>
       <c r="H14" s="41" t="s">
         <v>150</v>
       </c>
@@ -9135,15 +9135,15 @@
       <c r="L14" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M14" s="63" t="s">
+      <c r="M14" s="57" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="21" customHeight="1">
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="C15" s="62"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="42"/>
       <c r="E15" s="42" t="s">
         <v>103</v>
@@ -9167,7 +9167,7 @@
       <c r="L15" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M15" s="64"/>
+      <c r="M15" s="58"/>
     </row>
     <row r="16" spans="2:14" ht="21" customHeight="1">
       <c r="B16" s="41" t="s">
@@ -9183,7 +9183,7 @@
       <c r="F16" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G16" s="63" t="s">
+      <c r="G16" s="57" t="s">
         <v>111</v>
       </c>
       <c r="H16" s="41" t="s">
@@ -9199,7 +9199,7 @@
       <c r="L16" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M16" s="64"/>
+      <c r="M16" s="58"/>
     </row>
     <row r="17" spans="2:13" ht="21" customHeight="1">
       <c r="B17" s="41" t="s">
@@ -9215,7 +9215,7 @@
       <c r="F17" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G17" s="64"/>
+      <c r="G17" s="58"/>
       <c r="H17" s="41" t="s">
         <v>162</v>
       </c>
@@ -9229,7 +9229,7 @@
       <c r="L17" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M17" s="64"/>
+      <c r="M17" s="58"/>
     </row>
     <row r="18" spans="2:13" ht="21" customHeight="1">
       <c r="B18" s="41" t="s">
@@ -9245,7 +9245,7 @@
       <c r="F18" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G18" s="64"/>
+      <c r="G18" s="58"/>
       <c r="H18" s="41" t="s">
         <v>166</v>
       </c>
@@ -9259,7 +9259,7 @@
       <c r="L18" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M18" s="64"/>
+      <c r="M18" s="58"/>
     </row>
     <row r="19" spans="2:13" ht="21" customHeight="1">
       <c r="B19" s="41" t="s">
@@ -9275,7 +9275,7 @@
       <c r="F19" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G19" s="65"/>
+      <c r="G19" s="59"/>
       <c r="H19" s="41" t="s">
         <v>170</v>
       </c>
@@ -9289,13 +9289,13 @@
       <c r="L19" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M19" s="64"/>
+      <c r="M19" s="58"/>
     </row>
     <row r="20" spans="2:13" ht="21" customHeight="1">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="55" t="s">
         <v>172</v>
       </c>
-      <c r="C20" s="62"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="42"/>
       <c r="E20" s="42" t="s">
         <v>103</v>
@@ -9319,7 +9319,7 @@
       <c r="L20" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="M20" s="64"/>
+      <c r="M20" s="58"/>
     </row>
     <row r="21" spans="2:13" ht="21" customHeight="1">
       <c r="B21" s="41" t="s">
@@ -9335,7 +9335,7 @@
       <c r="F21" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="63" t="s">
+      <c r="G21" s="57" t="s">
         <v>111</v>
       </c>
       <c r="H21" s="41" t="s">
@@ -9351,7 +9351,7 @@
       <c r="L21" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M21" s="64"/>
+      <c r="M21" s="58"/>
     </row>
     <row r="22" spans="2:13" ht="21" customHeight="1">
       <c r="B22" s="41" t="s">
@@ -9367,7 +9367,7 @@
       <c r="F22" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="64"/>
+      <c r="G22" s="58"/>
       <c r="H22" s="41" t="s">
         <v>180</v>
       </c>
@@ -9381,7 +9381,7 @@
       <c r="L22" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M22" s="64"/>
+      <c r="M22" s="58"/>
     </row>
     <row r="23" spans="2:13" ht="21" customHeight="1">
       <c r="B23" s="41" t="s">
@@ -9397,7 +9397,7 @@
       <c r="F23" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="64"/>
+      <c r="G23" s="58"/>
       <c r="H23" s="41" t="s">
         <v>184</v>
       </c>
@@ -9411,7 +9411,7 @@
       <c r="L23" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M23" s="64"/>
+      <c r="M23" s="58"/>
     </row>
     <row r="24" spans="2:13" ht="21" customHeight="1">
       <c r="B24" s="41" t="s">
@@ -9427,7 +9427,7 @@
       <c r="F24" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G24" s="65"/>
+      <c r="G24" s="59"/>
       <c r="H24" s="41" t="s">
         <v>188</v>
       </c>
@@ -9441,13 +9441,13 @@
       <c r="L24" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M24" s="64"/>
+      <c r="M24" s="58"/>
     </row>
     <row r="25" spans="2:13" ht="21" customHeight="1">
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="55" t="s">
         <v>190</v>
       </c>
-      <c r="C25" s="62"/>
+      <c r="C25" s="56"/>
       <c r="D25" s="42"/>
       <c r="E25" s="42" t="s">
         <v>103</v>
@@ -9471,7 +9471,7 @@
       <c r="L25" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M25" s="64"/>
+      <c r="M25" s="58"/>
     </row>
     <row r="26" spans="2:13" ht="21" customHeight="1">
       <c r="B26" s="41" t="s">
@@ -9487,7 +9487,7 @@
       <c r="F26" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G26" s="63" t="s">
+      <c r="G26" s="57" t="s">
         <v>111</v>
       </c>
       <c r="H26" s="41" t="s">
@@ -9503,7 +9503,7 @@
       <c r="L26" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M26" s="64"/>
+      <c r="M26" s="58"/>
     </row>
     <row r="27" spans="2:13" ht="21" customHeight="1">
       <c r="B27" s="41" t="s">
@@ -9519,7 +9519,7 @@
       <c r="F27" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G27" s="64"/>
+      <c r="G27" s="58"/>
       <c r="H27" s="41" t="s">
         <v>199</v>
       </c>
@@ -9533,7 +9533,7 @@
       <c r="L27" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M27" s="65"/>
+      <c r="M27" s="59"/>
     </row>
     <row r="28" spans="2:13" ht="21" customHeight="1">
       <c r="B28" s="41" t="s">
@@ -9549,11 +9549,11 @@
       <c r="F28" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G28" s="64"/>
-      <c r="H28" s="61" t="s">
+      <c r="G28" s="58"/>
+      <c r="H28" s="55" t="s">
         <v>203</v>
       </c>
-      <c r="I28" s="62"/>
+      <c r="I28" s="56"/>
       <c r="J28" s="42"/>
       <c r="K28" s="42" t="s">
         <v>103</v>
@@ -9579,7 +9579,7 @@
       <c r="F29" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G29" s="64"/>
+      <c r="G29" s="58"/>
       <c r="H29" s="41" t="s">
         <v>206</v>
       </c>
@@ -9593,7 +9593,7 @@
       <c r="L29" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M29" s="63" t="s">
+      <c r="M29" s="57" t="s">
         <v>115</v>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       <c r="F30" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G30" s="64"/>
+      <c r="G30" s="58"/>
       <c r="H30" s="41" t="s">
         <v>210</v>
       </c>
@@ -9625,7 +9625,7 @@
       <c r="L30" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M30" s="64"/>
+      <c r="M30" s="58"/>
     </row>
     <row r="31" spans="2:13" ht="21" customHeight="1">
       <c r="B31" s="41" t="s">
@@ -9641,7 +9641,7 @@
       <c r="F31" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G31" s="64"/>
+      <c r="G31" s="58"/>
       <c r="H31" s="41" t="s">
         <v>214</v>
       </c>
@@ -9655,7 +9655,7 @@
       <c r="L31" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M31" s="64"/>
+      <c r="M31" s="58"/>
     </row>
     <row r="32" spans="2:13" ht="21" customHeight="1">
       <c r="B32" s="41" t="s">
@@ -9671,7 +9671,7 @@
       <c r="F32" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G32" s="64"/>
+      <c r="G32" s="58"/>
       <c r="H32" s="41" t="s">
         <v>218</v>
       </c>
@@ -9685,7 +9685,7 @@
       <c r="L32" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="M32" s="64"/>
+      <c r="M32" s="58"/>
     </row>
     <row r="33" spans="2:13" ht="21" customHeight="1">
       <c r="B33" s="41" t="s">
@@ -9701,7 +9701,7 @@
       <c r="F33" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G33" s="64"/>
+      <c r="G33" s="58"/>
       <c r="H33" s="41" t="s">
         <v>222</v>
       </c>
@@ -9715,7 +9715,7 @@
       <c r="L33" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M33" s="64"/>
+      <c r="M33" s="58"/>
     </row>
     <row r="34" spans="2:13" ht="21" customHeight="1">
       <c r="B34" s="41" t="s">
@@ -9731,7 +9731,7 @@
       <c r="F34" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G34" s="65"/>
+      <c r="G34" s="59"/>
       <c r="H34" s="41" t="s">
         <v>226</v>
       </c>
@@ -9745,13 +9745,13 @@
       <c r="L34" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M34" s="64"/>
+      <c r="M34" s="58"/>
     </row>
     <row r="35" spans="2:13" ht="21" customHeight="1">
-      <c r="B35" s="61" t="s">
+      <c r="B35" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="62"/>
+      <c r="C35" s="56"/>
       <c r="D35" s="42"/>
       <c r="E35" s="42" t="s">
         <v>103</v>
@@ -9775,7 +9775,7 @@
       <c r="L35" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M35" s="64"/>
+      <c r="M35" s="58"/>
     </row>
     <row r="36" spans="2:13" ht="21" customHeight="1">
       <c r="B36" s="41" t="s">
@@ -9791,7 +9791,7 @@
       <c r="F36" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G36" s="63" t="s">
+      <c r="G36" s="57" t="s">
         <v>111</v>
       </c>
       <c r="H36" s="41" t="s">
@@ -9807,7 +9807,7 @@
       <c r="L36" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M36" s="65"/>
+      <c r="M36" s="59"/>
     </row>
     <row r="37" spans="2:13" ht="21" customHeight="1">
       <c r="B37" s="41" t="s">
@@ -9823,11 +9823,11 @@
       <c r="F37" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G37" s="64"/>
-      <c r="H37" s="61" t="s">
+      <c r="G37" s="58"/>
+      <c r="H37" s="55" t="s">
         <v>235</v>
       </c>
-      <c r="I37" s="62"/>
+      <c r="I37" s="56"/>
       <c r="J37" s="42"/>
       <c r="K37" s="42" t="s">
         <v>103</v>
@@ -9853,7 +9853,7 @@
       <c r="F38" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G38" s="64"/>
+      <c r="G38" s="58"/>
       <c r="H38" s="41" t="s">
         <v>238</v>
       </c>
@@ -9867,7 +9867,7 @@
       <c r="L38" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M38" s="63" t="s">
+      <c r="M38" s="57" t="s">
         <v>115</v>
       </c>
     </row>
@@ -9885,7 +9885,7 @@
       <c r="F39" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G39" s="64"/>
+      <c r="G39" s="58"/>
       <c r="H39" s="41" t="s">
         <v>242</v>
       </c>
@@ -9899,7 +9899,7 @@
       <c r="L39" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M39" s="64"/>
+      <c r="M39" s="58"/>
     </row>
     <row r="40" spans="2:13" ht="21" customHeight="1">
       <c r="B40" s="41" t="s">
@@ -9915,7 +9915,7 @@
       <c r="F40" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G40" s="64"/>
+      <c r="G40" s="58"/>
       <c r="H40" s="41" t="s">
         <v>246</v>
       </c>
@@ -9929,7 +9929,7 @@
       <c r="L40" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M40" s="64"/>
+      <c r="M40" s="58"/>
     </row>
     <row r="41" spans="2:13" ht="21" customHeight="1">
       <c r="B41" s="41" t="s">
@@ -9945,7 +9945,7 @@
       <c r="F41" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G41" s="64"/>
+      <c r="G41" s="58"/>
       <c r="H41" s="41" t="s">
         <v>250</v>
       </c>
@@ -9959,7 +9959,7 @@
       <c r="L41" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="M41" s="64"/>
+      <c r="M41" s="58"/>
     </row>
     <row r="42" spans="2:13" ht="21" customHeight="1">
       <c r="B42" s="41" t="s">
@@ -9975,7 +9975,7 @@
       <c r="F42" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G42" s="64"/>
+      <c r="G42" s="58"/>
       <c r="H42" s="41" t="s">
         <v>254</v>
       </c>
@@ -9989,7 +9989,7 @@
       <c r="L42" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M42" s="64"/>
+      <c r="M42" s="58"/>
     </row>
     <row r="43" spans="2:13" ht="21" customHeight="1">
       <c r="B43" s="41" t="s">
@@ -10005,7 +10005,7 @@
       <c r="F43" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="G43" s="64"/>
+      <c r="G43" s="58"/>
       <c r="H43" s="41" t="s">
         <v>258</v>
       </c>
@@ -10019,7 +10019,7 @@
       <c r="L43" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M43" s="64"/>
+      <c r="M43" s="58"/>
     </row>
     <row r="44" spans="2:13" ht="21" customHeight="1">
       <c r="B44" s="41" t="s">
@@ -10035,7 +10035,7 @@
       <c r="F44" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="G44" s="65"/>
+      <c r="G44" s="59"/>
       <c r="H44" s="41" t="s">
         <v>263</v>
       </c>
@@ -10049,49 +10049,48 @@
       <c r="L44" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="M44" s="65"/>
+      <c r="M44" s="59"/>
     </row>
     <row r="45" spans="2:13" ht="21.95" customHeight="1">
-      <c r="B45" s="66" t="s">
+      <c r="B45" s="49" t="s">
         <v>265</v>
       </c>
-      <c r="C45" s="67"/>
-      <c r="D45" s="67"/>
-      <c r="E45" s="67"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
-      <c r="H45" s="67"/>
-      <c r="I45" s="67"/>
-      <c r="J45" s="67"/>
-      <c r="K45" s="67"/>
-      <c r="L45" s="67"/>
-      <c r="M45" s="68"/>
+      <c r="C45" s="50"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="50"/>
+      <c r="G45" s="50"/>
+      <c r="H45" s="50"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="50"/>
+      <c r="K45" s="50"/>
+      <c r="L45" s="50"/>
+      <c r="M45" s="51"/>
     </row>
     <row r="46" spans="2:13" ht="23.1" customHeight="1">
-      <c r="B46" s="69"/>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="70"/>
-      <c r="H46" s="70"/>
-      <c r="I46" s="70"/>
-      <c r="J46" s="70"/>
-      <c r="K46" s="70"/>
-      <c r="L46" s="70"/>
-      <c r="M46" s="71"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="53"/>
+      <c r="L46" s="53"/>
+      <c r="M46" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B45:M46"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="G26:G34"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="M29:M36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="G36:G44"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="M38:M44"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="G6:G14"/>
@@ -10102,14 +10101,15 @@
     <mergeCell ref="G16:G19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="G21:G24"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="B45:M46"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="G26:G34"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="M29:M36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="G36:G44"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="M38:M44"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -10168,72 +10168,72 @@
       <c r="B3" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="68" t="s">
         <v>267</v>
       </c>
-      <c r="D3" s="265"/>
+      <c r="D3" s="282"/>
       <c r="E3" s="44" t="s">
         <v>268</v>
       </c>
       <c r="F3" s="45" t="s">
         <v>269</v>
       </c>
-      <c r="G3" s="52" t="s">
-        <v>361</v>
-      </c>
-      <c r="H3" s="53"/>
-      <c r="I3" s="266" t="s">
+      <c r="G3" s="63" t="s">
         <v>360</v>
       </c>
-      <c r="J3" s="267"/>
-      <c r="K3" s="268"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="284" t="s">
+        <v>359</v>
+      </c>
+      <c r="J3" s="286"/>
+      <c r="K3" s="285"/>
     </row>
     <row r="4" spans="2:11">
       <c r="B4" s="44" t="s">
         <v>270</v>
       </c>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="284" t="s">
         <v>271</v>
       </c>
-      <c r="D4" s="268"/>
+      <c r="D4" s="285"/>
       <c r="E4" s="44" t="s">
         <v>272</v>
       </c>
       <c r="F4" s="45" t="s">
         <v>273</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="63" t="s">
         <v>274</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="I4" s="57" t="s">
+      <c r="H4" s="64"/>
+      <c r="I4" s="68" t="s">
         <v>275</v>
       </c>
-      <c r="J4" s="58"/>
-      <c r="K4" s="265"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="282"/>
     </row>
     <row r="5" spans="2:11">
       <c r="B5" s="44" t="s">
         <v>276</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="68" t="s">
         <v>277</v>
       </c>
-      <c r="D5" s="265"/>
+      <c r="D5" s="282"/>
       <c r="E5" s="44" t="s">
         <v>278</v>
       </c>
       <c r="F5" s="45" t="s">
         <v>279</v>
       </c>
-      <c r="G5" s="52" t="s">
+      <c r="G5" s="63" t="s">
         <v>280</v>
       </c>
-      <c r="H5" s="53"/>
-      <c r="I5" s="57" t="s">
+      <c r="H5" s="64"/>
+      <c r="I5" s="68" t="s">
         <v>281</v>
       </c>
-      <c r="J5" s="265"/>
+      <c r="J5" s="282"/>
       <c r="K5" s="45" t="s">
         <v>282</v>
       </c>
@@ -10242,635 +10242,635 @@
       <c r="B6" s="44" t="s">
         <v>283</v>
       </c>
-      <c r="C6" s="266" t="s">
-        <v>362</v>
-      </c>
-      <c r="D6" s="268"/>
+      <c r="C6" s="284" t="s">
+        <v>361</v>
+      </c>
+      <c r="D6" s="285"/>
       <c r="E6" s="44" t="s">
         <v>284</v>
       </c>
       <c r="F6" s="45" t="s">
         <v>285</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="63" t="s">
         <v>286</v>
       </c>
-      <c r="H6" s="53"/>
-      <c r="I6" s="54" t="s">
+      <c r="H6" s="64"/>
+      <c r="I6" s="65" t="s">
         <v>287</v>
       </c>
-      <c r="J6" s="58"/>
-      <c r="K6" s="265"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="282"/>
     </row>
     <row r="7" spans="2:11" ht="15.95" customHeight="1">
       <c r="B7" s="44" t="s">
         <v>288</v>
       </c>
-      <c r="C7" s="269" t="s">
+      <c r="C7" s="280" t="s">
         <v>353</v>
       </c>
-      <c r="D7" s="270"/>
+      <c r="D7" s="281"/>
       <c r="E7" s="44" t="s">
         <v>289</v>
       </c>
       <c r="F7" s="39" t="s">
         <v>290</v>
       </c>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="63" t="s">
         <v>291</v>
       </c>
-      <c r="H7" s="53"/>
-      <c r="I7" s="57" t="s">
+      <c r="H7" s="64"/>
+      <c r="I7" s="68" t="s">
         <v>292</v>
       </c>
-      <c r="J7" s="58"/>
-      <c r="K7" s="265"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="282"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="271"/>
-      <c r="C8" s="272"/>
-      <c r="D8" s="272"/>
-      <c r="E8" s="272"/>
-      <c r="F8" s="272"/>
-      <c r="G8" s="272"/>
-      <c r="H8" s="272"/>
-      <c r="I8" s="272"/>
-      <c r="J8" s="272"/>
-      <c r="K8" s="273"/>
+      <c r="B8" s="265"/>
+      <c r="C8" s="266"/>
+      <c r="D8" s="266"/>
+      <c r="E8" s="266"/>
+      <c r="F8" s="266"/>
+      <c r="G8" s="266"/>
+      <c r="H8" s="266"/>
+      <c r="I8" s="266"/>
+      <c r="J8" s="266"/>
+      <c r="K8" s="267"/>
     </row>
     <row r="9" spans="2:11">
       <c r="B9" s="44" t="s">
         <v>293</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="63" t="s">
         <v>294</v>
       </c>
-      <c r="D9" s="274"/>
-      <c r="E9" s="274"/>
-      <c r="F9" s="274"/>
-      <c r="G9" s="274"/>
-      <c r="H9" s="53"/>
+      <c r="D9" s="283"/>
+      <c r="E9" s="283"/>
+      <c r="F9" s="283"/>
+      <c r="G9" s="283"/>
+      <c r="H9" s="64"/>
       <c r="I9" s="44" t="s">
         <v>295</v>
       </c>
-      <c r="J9" s="52" t="s">
+      <c r="J9" s="63" t="s">
         <v>296</v>
       </c>
-      <c r="K9" s="53"/>
+      <c r="K9" s="64"/>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="271" t="s">
+      <c r="B10" s="265" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="272"/>
-      <c r="D10" s="272"/>
-      <c r="E10" s="272"/>
-      <c r="F10" s="272"/>
-      <c r="G10" s="272"/>
-      <c r="H10" s="272"/>
-      <c r="I10" s="272"/>
-      <c r="J10" s="272"/>
-      <c r="K10" s="273"/>
+      <c r="C10" s="266"/>
+      <c r="D10" s="266"/>
+      <c r="E10" s="266"/>
+      <c r="F10" s="266"/>
+      <c r="G10" s="266"/>
+      <c r="H10" s="266"/>
+      <c r="I10" s="266"/>
+      <c r="J10" s="266"/>
+      <c r="K10" s="267"/>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="275" t="s">
+      <c r="B11" s="268" t="s">
         <v>298</v>
       </c>
-      <c r="C11" s="271" t="s">
+      <c r="C11" s="265" t="s">
         <v>299</v>
       </c>
-      <c r="D11" s="272"/>
-      <c r="E11" s="272"/>
-      <c r="F11" s="272"/>
-      <c r="G11" s="272"/>
-      <c r="H11" s="273"/>
+      <c r="D11" s="266"/>
+      <c r="E11" s="266"/>
+      <c r="F11" s="266"/>
+      <c r="G11" s="266"/>
+      <c r="H11" s="267"/>
       <c r="I11" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J11" s="271"/>
-      <c r="K11" s="273"/>
+      <c r="J11" s="265"/>
+      <c r="K11" s="267"/>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="276"/>
-      <c r="C12" s="271" t="s">
+      <c r="B12" s="269"/>
+      <c r="C12" s="265" t="s">
         <v>301</v>
       </c>
-      <c r="D12" s="272"/>
-      <c r="E12" s="272"/>
-      <c r="F12" s="272"/>
-      <c r="G12" s="272"/>
-      <c r="H12" s="273"/>
+      <c r="D12" s="266"/>
+      <c r="E12" s="266"/>
+      <c r="F12" s="266"/>
+      <c r="G12" s="266"/>
+      <c r="H12" s="267"/>
       <c r="I12" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="J12" s="271"/>
-      <c r="K12" s="273"/>
+      <c r="J12" s="265"/>
+      <c r="K12" s="267"/>
     </row>
     <row r="13" spans="2:11" ht="25.5" customHeight="1">
-      <c r="B13" s="277"/>
-      <c r="C13" s="271" t="s">
+      <c r="B13" s="270"/>
+      <c r="C13" s="265" t="s">
         <v>303</v>
       </c>
-      <c r="D13" s="272"/>
-      <c r="E13" s="272"/>
-      <c r="F13" s="272"/>
-      <c r="G13" s="272"/>
-      <c r="H13" s="273"/>
+      <c r="D13" s="266"/>
+      <c r="E13" s="266"/>
+      <c r="F13" s="266"/>
+      <c r="G13" s="266"/>
+      <c r="H13" s="267"/>
       <c r="I13" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="J13" s="271"/>
-      <c r="K13" s="273"/>
+      <c r="J13" s="265"/>
+      <c r="K13" s="267"/>
     </row>
     <row r="14" spans="2:11">
-      <c r="B14" s="271" t="s">
+      <c r="B14" s="265" t="s">
         <v>304</v>
       </c>
-      <c r="C14" s="272"/>
-      <c r="D14" s="272"/>
-      <c r="E14" s="272"/>
-      <c r="F14" s="272"/>
-      <c r="G14" s="272"/>
-      <c r="H14" s="272"/>
-      <c r="I14" s="272"/>
-      <c r="J14" s="272"/>
-      <c r="K14" s="273"/>
+      <c r="C14" s="266"/>
+      <c r="D14" s="266"/>
+      <c r="E14" s="266"/>
+      <c r="F14" s="266"/>
+      <c r="G14" s="266"/>
+      <c r="H14" s="266"/>
+      <c r="I14" s="266"/>
+      <c r="J14" s="266"/>
+      <c r="K14" s="267"/>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="275" t="s">
+      <c r="B15" s="268" t="s">
         <v>305</v>
       </c>
-      <c r="C15" s="271" t="s">
+      <c r="C15" s="265" t="s">
         <v>306</v>
       </c>
-      <c r="D15" s="272"/>
-      <c r="E15" s="272"/>
-      <c r="F15" s="272"/>
-      <c r="G15" s="272"/>
-      <c r="H15" s="273"/>
-      <c r="I15" s="278" t="s">
+      <c r="D15" s="266"/>
+      <c r="E15" s="266"/>
+      <c r="F15" s="266"/>
+      <c r="G15" s="266"/>
+      <c r="H15" s="267"/>
+      <c r="I15" s="271" t="s">
         <v>300</v>
       </c>
-      <c r="J15" s="280"/>
-      <c r="K15" s="281"/>
+      <c r="J15" s="274"/>
+      <c r="K15" s="275"/>
     </row>
     <row r="16" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B16" s="277"/>
-      <c r="C16" s="271" t="s">
+      <c r="B16" s="270"/>
+      <c r="C16" s="265" t="s">
         <v>307</v>
       </c>
-      <c r="D16" s="272"/>
-      <c r="E16" s="272"/>
-      <c r="F16" s="272"/>
-      <c r="G16" s="272"/>
-      <c r="H16" s="273"/>
-      <c r="I16" s="279"/>
-      <c r="J16" s="282"/>
-      <c r="K16" s="283"/>
+      <c r="D16" s="266"/>
+      <c r="E16" s="266"/>
+      <c r="F16" s="266"/>
+      <c r="G16" s="266"/>
+      <c r="H16" s="267"/>
+      <c r="I16" s="273"/>
+      <c r="J16" s="278"/>
+      <c r="K16" s="279"/>
     </row>
     <row r="17" spans="2:11" ht="18" customHeight="1">
-      <c r="B17" s="275" t="s">
+      <c r="B17" s="268" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="271" t="s">
+      <c r="C17" s="265" t="s">
         <v>309</v>
       </c>
-      <c r="D17" s="272"/>
-      <c r="E17" s="272"/>
-      <c r="F17" s="272"/>
-      <c r="G17" s="272"/>
-      <c r="H17" s="273"/>
-      <c r="I17" s="278" t="s">
+      <c r="D17" s="266"/>
+      <c r="E17" s="266"/>
+      <c r="F17" s="266"/>
+      <c r="G17" s="266"/>
+      <c r="H17" s="267"/>
+      <c r="I17" s="271" t="s">
         <v>300</v>
       </c>
-      <c r="J17" s="280"/>
-      <c r="K17" s="281"/>
+      <c r="J17" s="274"/>
+      <c r="K17" s="275"/>
     </row>
     <row r="18" spans="2:11" ht="27" customHeight="1">
-      <c r="B18" s="276"/>
-      <c r="C18" s="271" t="s">
+      <c r="B18" s="269"/>
+      <c r="C18" s="265" t="s">
         <v>310</v>
       </c>
-      <c r="D18" s="272"/>
-      <c r="E18" s="272"/>
-      <c r="F18" s="272"/>
-      <c r="G18" s="272"/>
-      <c r="H18" s="273"/>
-      <c r="I18" s="284"/>
-      <c r="J18" s="285"/>
-      <c r="K18" s="286"/>
+      <c r="D18" s="266"/>
+      <c r="E18" s="266"/>
+      <c r="F18" s="266"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="272"/>
+      <c r="J18" s="276"/>
+      <c r="K18" s="277"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="276"/>
-      <c r="C19" s="271" t="s">
+      <c r="B19" s="269"/>
+      <c r="C19" s="265" t="s">
         <v>311</v>
       </c>
-      <c r="D19" s="272"/>
-      <c r="E19" s="272"/>
-      <c r="F19" s="272"/>
-      <c r="G19" s="272"/>
-      <c r="H19" s="273"/>
-      <c r="I19" s="284"/>
-      <c r="J19" s="285"/>
-      <c r="K19" s="286"/>
+      <c r="D19" s="266"/>
+      <c r="E19" s="266"/>
+      <c r="F19" s="266"/>
+      <c r="G19" s="266"/>
+      <c r="H19" s="267"/>
+      <c r="I19" s="272"/>
+      <c r="J19" s="276"/>
+      <c r="K19" s="277"/>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="277"/>
-      <c r="C20" s="271" t="s">
+      <c r="B20" s="270"/>
+      <c r="C20" s="265" t="s">
         <v>312</v>
       </c>
-      <c r="D20" s="272"/>
-      <c r="E20" s="272"/>
-      <c r="F20" s="272"/>
-      <c r="G20" s="272"/>
-      <c r="H20" s="273"/>
-      <c r="I20" s="279"/>
-      <c r="J20" s="282"/>
-      <c r="K20" s="283"/>
+      <c r="D20" s="266"/>
+      <c r="E20" s="266"/>
+      <c r="F20" s="266"/>
+      <c r="G20" s="266"/>
+      <c r="H20" s="267"/>
+      <c r="I20" s="273"/>
+      <c r="J20" s="278"/>
+      <c r="K20" s="279"/>
     </row>
     <row r="21" spans="2:11">
-      <c r="B21" s="271" t="s">
+      <c r="B21" s="265" t="s">
         <v>313</v>
       </c>
-      <c r="C21" s="272"/>
-      <c r="D21" s="272"/>
-      <c r="E21" s="272"/>
-      <c r="F21" s="272"/>
-      <c r="G21" s="272"/>
-      <c r="H21" s="272"/>
-      <c r="I21" s="272"/>
-      <c r="J21" s="272"/>
-      <c r="K21" s="273"/>
+      <c r="C21" s="266"/>
+      <c r="D21" s="266"/>
+      <c r="E21" s="266"/>
+      <c r="F21" s="266"/>
+      <c r="G21" s="266"/>
+      <c r="H21" s="266"/>
+      <c r="I21" s="266"/>
+      <c r="J21" s="266"/>
+      <c r="K21" s="267"/>
     </row>
     <row r="22" spans="2:11" ht="18" customHeight="1">
-      <c r="B22" s="275" t="s">
+      <c r="B22" s="268" t="s">
         <v>314</v>
       </c>
-      <c r="C22" s="271" t="s">
+      <c r="C22" s="265" t="s">
         <v>315</v>
       </c>
-      <c r="D22" s="272"/>
-      <c r="E22" s="272"/>
-      <c r="F22" s="272"/>
-      <c r="G22" s="272"/>
-      <c r="H22" s="273"/>
-      <c r="I22" s="278" t="s">
+      <c r="D22" s="266"/>
+      <c r="E22" s="266"/>
+      <c r="F22" s="266"/>
+      <c r="G22" s="266"/>
+      <c r="H22" s="267"/>
+      <c r="I22" s="271" t="s">
         <v>300</v>
       </c>
-      <c r="J22" s="280"/>
-      <c r="K22" s="281"/>
+      <c r="J22" s="274"/>
+      <c r="K22" s="275"/>
     </row>
     <row r="23" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B23" s="277"/>
-      <c r="C23" s="271" t="s">
+      <c r="B23" s="270"/>
+      <c r="C23" s="265" t="s">
         <v>316</v>
       </c>
-      <c r="D23" s="272"/>
-      <c r="E23" s="272"/>
-      <c r="F23" s="272"/>
-      <c r="G23" s="272"/>
-      <c r="H23" s="273"/>
-      <c r="I23" s="279"/>
-      <c r="J23" s="282"/>
-      <c r="K23" s="283"/>
+      <c r="D23" s="266"/>
+      <c r="E23" s="266"/>
+      <c r="F23" s="266"/>
+      <c r="G23" s="266"/>
+      <c r="H23" s="267"/>
+      <c r="I23" s="273"/>
+      <c r="J23" s="278"/>
+      <c r="K23" s="279"/>
     </row>
     <row r="24" spans="2:11">
-      <c r="B24" s="271" t="s">
+      <c r="B24" s="265" t="s">
         <v>317</v>
       </c>
-      <c r="C24" s="272"/>
-      <c r="D24" s="272"/>
-      <c r="E24" s="272"/>
-      <c r="F24" s="272"/>
-      <c r="G24" s="272"/>
-      <c r="H24" s="272"/>
-      <c r="I24" s="272"/>
-      <c r="J24" s="272"/>
-      <c r="K24" s="273"/>
+      <c r="C24" s="266"/>
+      <c r="D24" s="266"/>
+      <c r="E24" s="266"/>
+      <c r="F24" s="266"/>
+      <c r="G24" s="266"/>
+      <c r="H24" s="266"/>
+      <c r="I24" s="266"/>
+      <c r="J24" s="266"/>
+      <c r="K24" s="267"/>
     </row>
     <row r="25" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B25" s="275" t="s">
+      <c r="B25" s="268" t="s">
         <v>318</v>
       </c>
-      <c r="C25" s="271" t="s">
+      <c r="C25" s="265" t="s">
         <v>319</v>
       </c>
-      <c r="D25" s="272"/>
-      <c r="E25" s="272"/>
-      <c r="F25" s="272"/>
-      <c r="G25" s="272"/>
-      <c r="H25" s="273"/>
-      <c r="I25" s="278" t="s">
+      <c r="D25" s="266"/>
+      <c r="E25" s="266"/>
+      <c r="F25" s="266"/>
+      <c r="G25" s="266"/>
+      <c r="H25" s="267"/>
+      <c r="I25" s="271" t="s">
         <v>300</v>
       </c>
-      <c r="J25" s="280"/>
-      <c r="K25" s="281"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="275"/>
     </row>
     <row r="26" spans="2:11">
-      <c r="B26" s="277"/>
-      <c r="C26" s="271" t="s">
+      <c r="B26" s="270"/>
+      <c r="C26" s="265" t="s">
         <v>320</v>
       </c>
-      <c r="D26" s="272"/>
-      <c r="E26" s="272"/>
-      <c r="F26" s="272"/>
-      <c r="G26" s="272"/>
-      <c r="H26" s="273"/>
-      <c r="I26" s="279"/>
-      <c r="J26" s="282"/>
-      <c r="K26" s="283"/>
+      <c r="D26" s="266"/>
+      <c r="E26" s="266"/>
+      <c r="F26" s="266"/>
+      <c r="G26" s="266"/>
+      <c r="H26" s="267"/>
+      <c r="I26" s="273"/>
+      <c r="J26" s="278"/>
+      <c r="K26" s="279"/>
     </row>
     <row r="27" spans="2:11" ht="15.95" customHeight="1">
       <c r="B27" s="46" t="s">
         <v>321</v>
       </c>
-      <c r="C27" s="271" t="s">
+      <c r="C27" s="265" t="s">
         <v>322</v>
       </c>
-      <c r="D27" s="272"/>
-      <c r="E27" s="272"/>
-      <c r="F27" s="272"/>
-      <c r="G27" s="272"/>
-      <c r="H27" s="273"/>
+      <c r="D27" s="266"/>
+      <c r="E27" s="266"/>
+      <c r="F27" s="266"/>
+      <c r="G27" s="266"/>
+      <c r="H27" s="267"/>
       <c r="I27" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J27" s="271"/>
-      <c r="K27" s="273"/>
+      <c r="J27" s="265"/>
+      <c r="K27" s="267"/>
     </row>
     <row r="28" spans="2:11">
-      <c r="B28" s="271" t="s">
+      <c r="B28" s="265" t="s">
         <v>323</v>
       </c>
-      <c r="C28" s="272"/>
-      <c r="D28" s="272"/>
-      <c r="E28" s="272"/>
-      <c r="F28" s="272"/>
-      <c r="G28" s="272"/>
-      <c r="H28" s="272"/>
-      <c r="I28" s="272"/>
-      <c r="J28" s="272"/>
-      <c r="K28" s="273"/>
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
+      <c r="F28" s="266"/>
+      <c r="G28" s="266"/>
+      <c r="H28" s="266"/>
+      <c r="I28" s="266"/>
+      <c r="J28" s="266"/>
+      <c r="K28" s="267"/>
     </row>
     <row r="29" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B29" s="275" t="s">
+      <c r="B29" s="268" t="s">
         <v>324</v>
       </c>
-      <c r="C29" s="271" t="s">
+      <c r="C29" s="265" t="s">
         <v>325</v>
       </c>
-      <c r="D29" s="272"/>
-      <c r="E29" s="272"/>
-      <c r="F29" s="272"/>
-      <c r="G29" s="272"/>
-      <c r="H29" s="273"/>
-      <c r="I29" s="278" t="s">
+      <c r="D29" s="266"/>
+      <c r="E29" s="266"/>
+      <c r="F29" s="266"/>
+      <c r="G29" s="266"/>
+      <c r="H29" s="267"/>
+      <c r="I29" s="271" t="s">
         <v>300</v>
       </c>
-      <c r="J29" s="280"/>
-      <c r="K29" s="281"/>
+      <c r="J29" s="274"/>
+      <c r="K29" s="275"/>
     </row>
     <row r="30" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B30" s="277"/>
-      <c r="C30" s="271" t="s">
+      <c r="B30" s="270"/>
+      <c r="C30" s="265" t="s">
         <v>326</v>
       </c>
-      <c r="D30" s="272"/>
-      <c r="E30" s="272"/>
-      <c r="F30" s="272"/>
-      <c r="G30" s="272"/>
-      <c r="H30" s="273"/>
-      <c r="I30" s="279"/>
-      <c r="J30" s="282"/>
-      <c r="K30" s="283"/>
+      <c r="D30" s="266"/>
+      <c r="E30" s="266"/>
+      <c r="F30" s="266"/>
+      <c r="G30" s="266"/>
+      <c r="H30" s="267"/>
+      <c r="I30" s="273"/>
+      <c r="J30" s="278"/>
+      <c r="K30" s="279"/>
     </row>
     <row r="31" spans="2:11">
-      <c r="B31" s="271" t="s">
+      <c r="B31" s="265" t="s">
         <v>327</v>
       </c>
-      <c r="C31" s="272"/>
-      <c r="D31" s="272"/>
-      <c r="E31" s="272"/>
-      <c r="F31" s="272"/>
-      <c r="G31" s="272"/>
-      <c r="H31" s="272"/>
-      <c r="I31" s="272"/>
-      <c r="J31" s="272"/>
-      <c r="K31" s="273"/>
+      <c r="C31" s="266"/>
+      <c r="D31" s="266"/>
+      <c r="E31" s="266"/>
+      <c r="F31" s="266"/>
+      <c r="G31" s="266"/>
+      <c r="H31" s="266"/>
+      <c r="I31" s="266"/>
+      <c r="J31" s="266"/>
+      <c r="K31" s="267"/>
     </row>
     <row r="32" spans="2:11" ht="28.5" customHeight="1">
-      <c r="B32" s="275" t="s">
+      <c r="B32" s="268" t="s">
         <v>328</v>
       </c>
-      <c r="C32" s="271" t="s">
+      <c r="C32" s="265" t="s">
         <v>329</v>
       </c>
-      <c r="D32" s="272"/>
-      <c r="E32" s="272"/>
-      <c r="F32" s="272"/>
-      <c r="G32" s="272"/>
-      <c r="H32" s="273"/>
-      <c r="I32" s="278" t="s">
+      <c r="D32" s="266"/>
+      <c r="E32" s="266"/>
+      <c r="F32" s="266"/>
+      <c r="G32" s="266"/>
+      <c r="H32" s="267"/>
+      <c r="I32" s="271" t="s">
         <v>300</v>
       </c>
-      <c r="J32" s="280"/>
-      <c r="K32" s="281"/>
+      <c r="J32" s="274"/>
+      <c r="K32" s="275"/>
     </row>
     <row r="33" spans="2:11" ht="18" customHeight="1">
-      <c r="B33" s="276"/>
-      <c r="C33" s="271" t="s">
+      <c r="B33" s="269"/>
+      <c r="C33" s="265" t="s">
         <v>330</v>
       </c>
-      <c r="D33" s="272"/>
-      <c r="E33" s="272"/>
-      <c r="F33" s="272"/>
-      <c r="G33" s="272"/>
-      <c r="H33" s="273"/>
-      <c r="I33" s="284"/>
-      <c r="J33" s="285"/>
-      <c r="K33" s="286"/>
+      <c r="D33" s="266"/>
+      <c r="E33" s="266"/>
+      <c r="F33" s="266"/>
+      <c r="G33" s="266"/>
+      <c r="H33" s="267"/>
+      <c r="I33" s="272"/>
+      <c r="J33" s="276"/>
+      <c r="K33" s="277"/>
     </row>
     <row r="34" spans="2:11" ht="18" customHeight="1">
-      <c r="B34" s="277"/>
-      <c r="C34" s="271" t="s">
+      <c r="B34" s="270"/>
+      <c r="C34" s="265" t="s">
         <v>331</v>
       </c>
-      <c r="D34" s="272"/>
-      <c r="E34" s="272"/>
-      <c r="F34" s="272"/>
-      <c r="G34" s="272"/>
-      <c r="H34" s="273"/>
-      <c r="I34" s="279"/>
-      <c r="J34" s="282"/>
-      <c r="K34" s="283"/>
+      <c r="D34" s="266"/>
+      <c r="E34" s="266"/>
+      <c r="F34" s="266"/>
+      <c r="G34" s="266"/>
+      <c r="H34" s="267"/>
+      <c r="I34" s="273"/>
+      <c r="J34" s="278"/>
+      <c r="K34" s="279"/>
     </row>
     <row r="35" spans="2:11" ht="15.95" customHeight="1">
-      <c r="B35" s="271" t="s">
+      <c r="B35" s="265" t="s">
         <v>332</v>
       </c>
-      <c r="C35" s="272"/>
-      <c r="D35" s="272"/>
-      <c r="E35" s="272"/>
-      <c r="F35" s="272"/>
-      <c r="G35" s="272"/>
-      <c r="H35" s="272"/>
-      <c r="I35" s="272"/>
-      <c r="J35" s="272"/>
-      <c r="K35" s="273"/>
+      <c r="C35" s="266"/>
+      <c r="D35" s="266"/>
+      <c r="E35" s="266"/>
+      <c r="F35" s="266"/>
+      <c r="G35" s="266"/>
+      <c r="H35" s="266"/>
+      <c r="I35" s="266"/>
+      <c r="J35" s="266"/>
+      <c r="K35" s="267"/>
     </row>
     <row r="36" spans="2:11" ht="28.5" customHeight="1">
       <c r="B36" s="46" t="s">
         <v>333</v>
       </c>
-      <c r="C36" s="271" t="s">
+      <c r="C36" s="265" t="s">
         <v>334</v>
       </c>
-      <c r="D36" s="272"/>
-      <c r="E36" s="272"/>
-      <c r="F36" s="272"/>
-      <c r="G36" s="272"/>
-      <c r="H36" s="273"/>
+      <c r="D36" s="266"/>
+      <c r="E36" s="266"/>
+      <c r="F36" s="266"/>
+      <c r="G36" s="266"/>
+      <c r="H36" s="267"/>
       <c r="I36" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J36" s="271"/>
-      <c r="K36" s="273"/>
+      <c r="J36" s="265"/>
+      <c r="K36" s="267"/>
     </row>
     <row r="37" spans="2:11" ht="15.95" customHeight="1">
       <c r="B37" s="46" t="s">
         <v>335</v>
       </c>
-      <c r="C37" s="271" t="s">
+      <c r="C37" s="265" t="s">
         <v>336</v>
       </c>
-      <c r="D37" s="272"/>
-      <c r="E37" s="272"/>
-      <c r="F37" s="272"/>
-      <c r="G37" s="272"/>
-      <c r="H37" s="273"/>
+      <c r="D37" s="266"/>
+      <c r="E37" s="266"/>
+      <c r="F37" s="266"/>
+      <c r="G37" s="266"/>
+      <c r="H37" s="267"/>
       <c r="I37" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="J37" s="271"/>
-      <c r="K37" s="273"/>
+      <c r="J37" s="265"/>
+      <c r="K37" s="267"/>
     </row>
     <row r="38" spans="2:11" ht="18" customHeight="1">
       <c r="B38" s="47" t="s">
         <v>337</v>
       </c>
-      <c r="C38" s="271" t="s">
+      <c r="C38" s="265" t="s">
         <v>338</v>
       </c>
-      <c r="D38" s="272"/>
-      <c r="E38" s="272"/>
-      <c r="F38" s="272"/>
-      <c r="G38" s="272"/>
-      <c r="H38" s="273"/>
+      <c r="D38" s="266"/>
+      <c r="E38" s="266"/>
+      <c r="F38" s="266"/>
+      <c r="G38" s="266"/>
+      <c r="H38" s="267"/>
       <c r="I38" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J38" s="271"/>
-      <c r="K38" s="273"/>
+      <c r="J38" s="265"/>
+      <c r="K38" s="267"/>
     </row>
     <row r="39" spans="2:11" ht="15.95" customHeight="1">
-      <c r="B39" s="271" t="s">
+      <c r="B39" s="265" t="s">
         <v>339</v>
       </c>
-      <c r="C39" s="272"/>
-      <c r="D39" s="272"/>
-      <c r="E39" s="272"/>
-      <c r="F39" s="272"/>
-      <c r="G39" s="272"/>
-      <c r="H39" s="272"/>
-      <c r="I39" s="272"/>
-      <c r="J39" s="272"/>
-      <c r="K39" s="273"/>
+      <c r="C39" s="266"/>
+      <c r="D39" s="266"/>
+      <c r="E39" s="266"/>
+      <c r="F39" s="266"/>
+      <c r="G39" s="266"/>
+      <c r="H39" s="266"/>
+      <c r="I39" s="266"/>
+      <c r="J39" s="266"/>
+      <c r="K39" s="267"/>
     </row>
     <row r="40" spans="2:11" ht="21" customHeight="1">
       <c r="B40" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="C40" s="271" t="s">
+      <c r="C40" s="265" t="s">
         <v>341</v>
       </c>
-      <c r="D40" s="272"/>
-      <c r="E40" s="272"/>
-      <c r="F40" s="272"/>
-      <c r="G40" s="272"/>
-      <c r="H40" s="273"/>
+      <c r="D40" s="266"/>
+      <c r="E40" s="266"/>
+      <c r="F40" s="266"/>
+      <c r="G40" s="266"/>
+      <c r="H40" s="267"/>
       <c r="I40" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J40" s="271"/>
-      <c r="K40" s="273"/>
+      <c r="J40" s="265"/>
+      <c r="K40" s="267"/>
     </row>
     <row r="41" spans="2:11" ht="28.5" customHeight="1">
       <c r="B41" s="46" t="s">
         <v>342</v>
       </c>
-      <c r="C41" s="271" t="s">
+      <c r="C41" s="265" t="s">
         <v>343</v>
       </c>
-      <c r="D41" s="272"/>
-      <c r="E41" s="272"/>
-      <c r="F41" s="272"/>
-      <c r="G41" s="272"/>
-      <c r="H41" s="273"/>
+      <c r="D41" s="266"/>
+      <c r="E41" s="266"/>
+      <c r="F41" s="266"/>
+      <c r="G41" s="266"/>
+      <c r="H41" s="267"/>
       <c r="I41" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J41" s="271"/>
-      <c r="K41" s="273"/>
+      <c r="J41" s="265"/>
+      <c r="K41" s="267"/>
     </row>
     <row r="42" spans="2:11" ht="18.95" customHeight="1">
       <c r="B42" s="46" t="s">
         <v>344</v>
       </c>
-      <c r="C42" s="271" t="s">
+      <c r="C42" s="265" t="s">
         <v>345</v>
       </c>
-      <c r="D42" s="272"/>
-      <c r="E42" s="272"/>
-      <c r="F42" s="272"/>
-      <c r="G42" s="272"/>
-      <c r="H42" s="273"/>
+      <c r="D42" s="266"/>
+      <c r="E42" s="266"/>
+      <c r="F42" s="266"/>
+      <c r="G42" s="266"/>
+      <c r="H42" s="267"/>
       <c r="I42" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J42" s="271"/>
-      <c r="K42" s="273"/>
+      <c r="J42" s="265"/>
+      <c r="K42" s="267"/>
     </row>
     <row r="43" spans="2:11" ht="28.5" customHeight="1">
       <c r="B43" s="46" t="s">
         <v>346</v>
       </c>
-      <c r="C43" s="271" t="s">
+      <c r="C43" s="265" t="s">
         <v>347</v>
       </c>
-      <c r="D43" s="272"/>
-      <c r="E43" s="272"/>
-      <c r="F43" s="272"/>
-      <c r="G43" s="272"/>
-      <c r="H43" s="273"/>
+      <c r="D43" s="266"/>
+      <c r="E43" s="266"/>
+      <c r="F43" s="266"/>
+      <c r="G43" s="266"/>
+      <c r="H43" s="267"/>
       <c r="I43" s="45" t="s">
         <v>300</v>
       </c>
-      <c r="J43" s="271"/>
-      <c r="K43" s="273"/>
+      <c r="J43" s="265"/>
+      <c r="K43" s="267"/>
     </row>
     <row r="44" spans="2:11" ht="50.1" customHeight="1">
-      <c r="B44" s="271" t="s">
+      <c r="B44" s="265" t="s">
         <v>348</v>
       </c>
-      <c r="C44" s="272"/>
-      <c r="D44" s="272"/>
-      <c r="E44" s="272"/>
-      <c r="F44" s="272"/>
-      <c r="G44" s="272"/>
-      <c r="H44" s="272"/>
-      <c r="I44" s="272"/>
-      <c r="J44" s="272"/>
-      <c r="K44" s="273"/>
+      <c r="C44" s="266"/>
+      <c r="D44" s="266"/>
+      <c r="E44" s="266"/>
+      <c r="F44" s="266"/>
+      <c r="G44" s="266"/>
+      <c r="H44" s="266"/>
+      <c r="I44" s="266"/>
+      <c r="J44" s="266"/>
+      <c r="K44" s="267"/>
     </row>
     <row r="45" spans="2:11">
       <c r="B45" s="43"/>
@@ -10887,16 +10887,65 @@
     <row r="46" spans="2:11" ht="11.1" customHeight="1"/>
   </sheetData>
   <mergeCells count="83">
-    <mergeCell ref="C43:H43"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="B44:K44"/>
-    <mergeCell ref="B39:K39"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="B14:K14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="J15:K16"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="I17:I20"/>
+    <mergeCell ref="J17:K20"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="B21:K21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J22:K23"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="B24:K24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:K26"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="B28:K28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="J29:K30"/>
+    <mergeCell ref="C30:H30"/>
     <mergeCell ref="C38:H38"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="B31:K31"/>
@@ -10911,65 +10960,16 @@
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="C37:H37"/>
     <mergeCell ref="J37:K37"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="B28:K28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:H29"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="J29:K30"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="B24:K24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="J25:K26"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="B21:K21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J22:K23"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="I17:I20"/>
-    <mergeCell ref="J17:K20"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="B14:K14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="J15:K16"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="B10:K10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="B8:K8"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="B44:K44"/>
+    <mergeCell ref="B39:K39"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="J42:K42"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
